--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -1,742 +1,782 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHaskins\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735C5355-D956-453D-B4BF-35FBDDB3FD30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
-  <si>
-    <t xml:space="preserve">topic.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topic.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metric.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metric.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metrics.definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metrics.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.notes.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.notes.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.date_range.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.date_range.end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vintage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Economy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overall-economy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 12-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-12-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="250">
+  <si>
+    <t>topic.name</t>
+  </si>
+  <si>
+    <t>topic.key</t>
+  </si>
+  <si>
+    <t>metric.name</t>
+  </si>
+  <si>
+    <t>metric.key</t>
+  </si>
+  <si>
+    <t>metrics.definition</t>
+  </si>
+  <si>
+    <t>metrics.source</t>
+  </si>
+  <si>
+    <t>level.name</t>
+  </si>
+  <si>
+    <t>level.key</t>
+  </si>
+  <si>
+    <t>level.interval</t>
+  </si>
+  <si>
+    <t>level.format.base</t>
+  </si>
+  <si>
+    <t>level.format.change</t>
+  </si>
+  <si>
+    <t>level.format.notes.name</t>
+  </si>
+  <si>
+    <t>level.format.notes.key</t>
+  </si>
+  <si>
+    <t>level.date_range.start</t>
+  </si>
+  <si>
+    <t>level.date_range.end</t>
+  </si>
+  <si>
+    <t>level.map</t>
+  </si>
+  <si>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>Overall Economy</t>
+  </si>
+  <si>
+    <t>overall-economy</t>
+  </si>
+  <si>
+    <t>Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t>business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t>Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t>Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>0.[0]</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>Rolling 12-month total</t>
+  </si>
+  <si>
+    <t>rolling-12-sum</t>
+  </si>
+  <si>
+    <t>2024Q2</t>
+  </si>
+  <si>
+    <t>2025Q2</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-09</t>
+  </si>
+  <si>
+    <t>Federal obligations</t>
+  </si>
+  <si>
+    <t>federal-obligations</t>
+  </si>
+  <si>
+    <t>Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t>USASpending</t>
+  </si>
+  <si>
+    <t>Federal obligations, total</t>
+  </si>
+  <si>
+    <t>federal-obligations-total</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>$123k</t>
+  </si>
+  <si>
+    <t>2024M11</t>
+  </si>
+  <si>
+    <t>2025M11</t>
+  </si>
+  <si>
+    <t>DMV-2025-12-11</t>
+  </si>
+  <si>
+    <t>Federal obligations, grants</t>
+  </si>
+  <si>
+    <t>federal-obligations-grants</t>
+  </si>
+  <si>
+    <t>Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t>federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>innovation</t>
+  </si>
+  <si>
+    <t>Academic research funding</t>
+  </si>
+  <si>
+    <t>research-hd</t>
+  </si>
+  <si>
+    <t>Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t>Academic research funding obligated</t>
+  </si>
+  <si>
+    <t>Utility patents</t>
+  </si>
+  <si>
+    <t>patents</t>
+  </si>
+  <si>
+    <t>Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t>United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t>Utility patent applications filed</t>
+  </si>
+  <si>
+    <t>patents-filed</t>
+  </si>
+  <si>
+    <t>123k</t>
+  </si>
+  <si>
+    <t>2024M12</t>
+  </si>
+  <si>
+    <t>2025M12</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-18</t>
+  </si>
+  <si>
+    <t>Venture capital</t>
+  </si>
+  <si>
+    <t>venture-capital</t>
+  </si>
+  <si>
+    <t>Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t>Crunchbase</t>
+  </si>
+  <si>
+    <t>Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t>venture-capital-volume</t>
+  </si>
+  <si>
+    <t>Venture capital deals</t>
+  </si>
+  <si>
+    <t>venture-capital-deals</t>
+  </si>
+  <si>
+    <t>Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t>labor-market</t>
+  </si>
+  <si>
+    <t>Unemployment rate</t>
+  </si>
+  <si>
+    <t>unempr-sa</t>
   </si>
   <si>
     <t xml:space="preserve">Percentage of labor force not currently employed  </t>
   </si>
   <si>
-    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-02-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active residential for-sale listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median price of for-sale residential listings on the market in a given month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
+    <t>Lightcast and U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t>Unemployment rate, total</t>
+  </si>
+  <si>
+    <t>unempr-sa-total</t>
+  </si>
+  <si>
+    <t>0.[00]%</t>
+  </si>
+  <si>
+    <t>pct_diff</t>
+  </si>
+  <si>
+    <t>Rolling 3-month average</t>
+  </si>
+  <si>
+    <t>rolling-3-mean</t>
+  </si>
+  <si>
+    <t>DMV-2025-02-07</t>
+  </si>
+  <si>
+    <t>Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t>unempr-sa-white</t>
+  </si>
+  <si>
+    <t>Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t>unempr-sa-black</t>
+  </si>
+  <si>
+    <t>Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t>unempr-sa-poc</t>
+  </si>
+  <si>
+    <t>Unemployment rate, men</t>
+  </si>
+  <si>
+    <t>unempr-sa-male</t>
+  </si>
+  <si>
+    <t>Unemployment rate, female</t>
+  </si>
+  <si>
+    <t>unempr-sa-female</t>
+  </si>
+  <si>
+    <t>Job postings</t>
+  </si>
+  <si>
+    <t>unique-postings-fte</t>
+  </si>
+  <si>
+    <t>Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t>Lightcast</t>
+  </si>
+  <si>
+    <t>Total job postings, full-time</t>
+  </si>
+  <si>
+    <t>unique-postings-total</t>
+  </si>
+  <si>
+    <t>Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t>unique-postings-private</t>
+  </si>
+  <si>
+    <t>Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t>unique-postings-public</t>
+  </si>
+  <si>
+    <t>Internship postings</t>
+  </si>
+  <si>
+    <t>unique-postings-internships</t>
+  </si>
+  <si>
+    <t>Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t>real-estate</t>
+  </si>
+  <si>
+    <t>Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t>commercial-occupancy</t>
+  </si>
+  <si>
+    <t>Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t>CoStar</t>
+  </si>
+  <si>
+    <t>Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t>commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t>0.[0]%</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-27</t>
+  </si>
+  <si>
+    <t>Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t>commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t>Active residential for-sale listings</t>
+  </si>
+  <si>
+    <t>active-listings</t>
+  </si>
+  <si>
+    <t>Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
+  </si>
+  <si>
+    <t>Realtor.com Economic Research</t>
+  </si>
+  <si>
+    <t>Median residential listing price</t>
+  </si>
+  <si>
+    <t>median-listing-price</t>
+  </si>
+  <si>
+    <t>Median price of for-sale residential listings on the market in a given month</t>
+  </si>
+  <si>
+    <t>Observed rental index</t>
+  </si>
+  <si>
+    <t>rent-index</t>
+  </si>
+  <si>
+    <t>Zillow observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t>Zillow</t>
+  </si>
+  <si>
+    <t>Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t>destination-travel</t>
+  </si>
+  <si>
+    <t>Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t>hotel-revpar</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
   </si>
   <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNAP participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snap-participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-prime consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-nearprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severely credit-constrained consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-subprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">personal-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About the DMV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">about</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total-population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attainment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eduatt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less than high school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less-than-hs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school or equivalent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high-school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some college or associate's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some-college-aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bachelors-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduate or professional degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">graduate-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hs-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign-born</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+    <t>$0.[00]</t>
+  </si>
+  <si>
+    <t>Overnight visitors</t>
+  </si>
+  <si>
+    <t>overnight-visitors</t>
+  </si>
+  <si>
+    <t>DataFy</t>
+  </si>
+  <si>
+    <t>2024M9</t>
+  </si>
+  <si>
+    <t>2025M9</t>
+  </si>
+  <si>
+    <t>Visitor spending</t>
+  </si>
+  <si>
+    <t>visitor-spending</t>
+  </si>
+  <si>
+    <t>Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t>Visitor spending, total</t>
+  </si>
+  <si>
+    <t>visitor-spending-total</t>
+  </si>
+  <si>
+    <t>Municipal Services</t>
+  </si>
+  <si>
+    <t>municipal-services</t>
+  </si>
+  <si>
+    <t>Transit ridership</t>
+  </si>
+  <si>
+    <t>transit-ridership</t>
+  </si>
+  <si>
+    <t>Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t>U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t>Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t>transit-vrm</t>
+  </si>
+  <si>
+    <t>0.[00]</t>
+  </si>
+  <si>
+    <t>Rolling 3-month total</t>
+  </si>
+  <si>
+    <t>rolling-3-sum</t>
+  </si>
+  <si>
+    <t>Crime rate</t>
+  </si>
+  <si>
+    <t>crime-rate</t>
+  </si>
+  <si>
+    <t>Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t>Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t>Total, all major crimes</t>
+  </si>
+  <si>
+    <t>crime-rate-total</t>
+  </si>
+  <si>
+    <t>Violent crimes</t>
+  </si>
+  <si>
+    <t>crime-rate-violent</t>
+  </si>
+  <si>
+    <t>Property crimes</t>
+  </si>
+  <si>
+    <t>crime-rate-property</t>
+  </si>
+  <si>
+    <t>Mass layoff notifications</t>
+  </si>
+  <si>
+    <t>warn-notices</t>
+  </si>
+  <si>
+    <t>Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t>WarnTracker.com</t>
+  </si>
+  <si>
+    <t>Household Wellbeing</t>
+  </si>
+  <si>
+    <t>household-wellbeing</t>
+  </si>
+  <si>
+    <t>Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t>medicaid-enrollment</t>
+  </si>
+  <si>
+    <t>Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t>State agency reporting</t>
+  </si>
+  <si>
+    <t>2024M10</t>
+  </si>
+  <si>
+    <t>2025M10</t>
+  </si>
+  <si>
+    <t>SNAP participation</t>
+  </si>
+  <si>
+    <t>snap-participation</t>
+  </si>
+  <si>
+    <t>Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
+  </si>
+  <si>
+    <t>Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t>credit-constrained</t>
+  </si>
+  <si>
+    <t>Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t>Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t>Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t>credit-constrained-total</t>
+  </si>
+  <si>
+    <t>2024Q1</t>
+  </si>
+  <si>
+    <t>2025Q1</t>
+  </si>
+  <si>
+    <t>Near-prime consumers</t>
+  </si>
+  <si>
+    <t>credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t>Severely credit-constrained consumers</t>
+  </si>
+  <si>
+    <t>credit-constrained-subprime</t>
+  </si>
+  <si>
+    <t>Personal bankruptcy rate</t>
+  </si>
+  <si>
+    <t>personal-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t>Non-business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t>Resident spending</t>
+  </si>
+  <si>
+    <t>resident-spending</t>
+  </si>
+  <si>
+    <t>Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t>Resident spending, total</t>
+  </si>
+  <si>
+    <t>resident-spending-total</t>
+  </si>
+  <si>
+    <t>About the DMV</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>total-population</t>
+  </si>
+  <si>
+    <t>Total population</t>
+  </si>
+  <si>
+    <t>U.S. Census Bureau and Lightcast</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>2024A1</t>
+  </si>
+  <si>
+    <t>Educational attainment</t>
+  </si>
+  <si>
+    <t>eduatt</t>
+  </si>
+  <si>
+    <t>Educational attaintment for population aged 25 and older</t>
+  </si>
+  <si>
+    <t>Less than high school</t>
+  </si>
+  <si>
+    <t>less-than-hs</t>
+  </si>
+  <si>
+    <t>High school or equivalent</t>
+  </si>
+  <si>
+    <t>high-school</t>
+  </si>
+  <si>
+    <t>Some college or associate's degree</t>
+  </si>
+  <si>
+    <t>some-college-aa</t>
+  </si>
+  <si>
+    <t>Bachelor's degree</t>
+  </si>
+  <si>
+    <t>bachelors-degree</t>
+  </si>
+  <si>
+    <t>Graduate or professional degree</t>
+  </si>
+  <si>
+    <t>graduate-degree</t>
+  </si>
+  <si>
+    <t>High school degree or higher, total</t>
+  </si>
+  <si>
+    <t>hs-plus</t>
+  </si>
+  <si>
+    <t>Bachelor's degree or higher, total</t>
+  </si>
+  <si>
+    <t>ba-plus</t>
+  </si>
+  <si>
+    <t>Share of foreign-born population (%)</t>
+  </si>
+  <si>
+    <t>foreign-born</t>
+  </si>
+  <si>
+    <t>Total air passengers served</t>
+  </si>
+  <si>
+    <t>air-travel</t>
+  </si>
+  <si>
+    <t>Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t>U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t>air-passengers</t>
+  </si>
+  <si>
+    <t>Consumer prices</t>
+  </si>
+  <si>
+    <t>cpi-total</t>
+  </si>
+  <si>
+    <t>Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t>U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t>Jobs</t>
+  </si>
+  <si>
+    <t>jobs</t>
+  </si>
+  <si>
+    <t>Total nonfarm payroll jobs, measured at location of employment</t>
+  </si>
+  <si>
+    <t>Total jobs</t>
+  </si>
+  <si>
+    <t>jobs-total</t>
+  </si>
+  <si>
+    <t>2024M8</t>
+  </si>
+  <si>
+    <t>2025M8</t>
+  </si>
+  <si>
+    <t>Private sector jobs</t>
+  </si>
+  <si>
+    <t>jobs-private</t>
+  </si>
+  <si>
+    <t>Federal government jobs</t>
+  </si>
+  <si>
+    <t>jobs-federal</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -765,13 +805,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1053,11 +1105,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q53"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1162,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1118,52 +1170,52 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>240</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>241</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" t="s">
-        <v>24</v>
+        <v>37</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="K2" t="s">
         <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>244</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" t="n">
+        <v>245</v>
+      </c>
+      <c r="P2" s="1">
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1171,52 +1223,52 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
       <c r="F3" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>246</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>247</v>
       </c>
       <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="J3" t="s">
-        <v>38</v>
+      <c r="J3" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="K3" t="s">
         <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>244</v>
       </c>
       <c r="O3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" t="n">
+        <v>245</v>
+      </c>
+      <c r="P3" s="1">
         <v>1</v>
       </c>
       <c r="Q3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1224,52 +1276,52 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>239</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>240</v>
       </c>
       <c r="E4" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
       <c r="F4" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>42</v>
+        <v>248</v>
       </c>
       <c r="H4" t="s">
-        <v>43</v>
+        <v>249</v>
       </c>
       <c r="I4" t="s">
         <v>37</v>
       </c>
-      <c r="J4" t="s">
-        <v>38</v>
+      <c r="J4" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="M4" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N4" t="s">
-        <v>39</v>
+        <v>244</v>
       </c>
       <c r="O4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" t="n">
+        <v>245</v>
+      </c>
+      <c r="P4" s="1">
         <v>1</v>
       </c>
       <c r="Q4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1277,28 +1329,28 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K5" t="s">
         <v>25</v>
@@ -1310,42 +1362,42 @@
         <v>27</v>
       </c>
       <c r="N5" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="O5" t="s">
-        <v>40</v>
-      </c>
-      <c r="P5" t="n">
+        <v>29</v>
+      </c>
+      <c r="P5">
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
         <v>34</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
         <v>37</v>
@@ -1368,43 +1420,43 @@
       <c r="O6" t="s">
         <v>40</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
         <v>37</v>
       </c>
       <c r="J7" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
@@ -1416,42 +1468,42 @@
         <v>27</v>
       </c>
       <c r="N7" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="O7" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" t="n">
+        <v>40</v>
+      </c>
+      <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
         <v>37</v>
@@ -1474,14 +1526,14 @@
       <c r="O8" t="s">
         <v>40</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>46</v>
       </c>
@@ -1489,28 +1541,28 @@
         <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="I9" t="s">
         <v>37</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="K9" t="s">
         <v>25</v>
@@ -1527,105 +1579,105 @@
       <c r="O9" t="s">
         <v>40</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>74</v>
+        <v>54</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="I10" t="s">
         <v>37</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="K10" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="M10" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="N10" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O10" t="s">
-        <v>40</v>
-      </c>
-      <c r="P10" t="n">
+        <v>60</v>
+      </c>
+      <c r="P10">
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I11" t="s">
         <v>37</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="N11" t="s">
         <v>39</v>
@@ -1633,52 +1685,52 @@
       <c r="O11" t="s">
         <v>40</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="I12" t="s">
         <v>37</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>80</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="N12" t="s">
         <v>39</v>
@@ -1686,14 +1738,14 @@
       <c r="O12" t="s">
         <v>40</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>70</v>
       </c>
@@ -1713,10 +1765,10 @@
         <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s">
         <v>37</v>
@@ -1739,14 +1791,14 @@
       <c r="O13" t="s">
         <v>40</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>1</v>
       </c>
       <c r="Q13" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1766,10 +1818,10 @@
         <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s">
         <v>37</v>
@@ -1792,14 +1844,14 @@
       <c r="O14" t="s">
         <v>40</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -1819,10 +1871,10 @@
         <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s">
         <v>37</v>
@@ -1845,14 +1897,14 @@
       <c r="O15" t="s">
         <v>40</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>70</v>
       </c>
@@ -1860,31 +1912,31 @@
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s">
         <v>37</v>
       </c>
       <c r="J16" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="K16" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L16" t="s">
         <v>80</v>
@@ -1893,19 +1945,19 @@
         <v>81</v>
       </c>
       <c r="N16" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="O16" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" t="n">
+        <v>40</v>
+      </c>
+      <c r="P16">
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>70</v>
       </c>
@@ -1913,31 +1965,31 @@
         <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I17" t="s">
         <v>37</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="K17" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L17" t="s">
         <v>80</v>
@@ -1946,19 +1998,19 @@
         <v>81</v>
       </c>
       <c r="N17" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="O17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P17" t="n">
+        <v>40</v>
+      </c>
+      <c r="P17">
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -1966,31 +2018,31 @@
         <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="E18" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="I18" t="s">
         <v>37</v>
       </c>
       <c r="J18" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L18" t="s">
         <v>80</v>
@@ -1999,19 +2051,19 @@
         <v>81</v>
       </c>
       <c r="N18" t="s">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="O18" t="s">
-        <v>60</v>
-      </c>
-      <c r="P18" t="n">
+        <v>40</v>
+      </c>
+      <c r="P18">
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>70</v>
       </c>
@@ -2031,10 +2083,10 @@
         <v>96</v>
       </c>
       <c r="G19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="H19" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I19" t="s">
         <v>37</v>
@@ -2057,158 +2109,158 @@
       <c r="O19" t="s">
         <v>60</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>1</v>
       </c>
       <c r="Q19" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="M20" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N20" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="O20" t="s">
-        <v>29</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="P20">
+        <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J21" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="M21" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N21" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="O21" t="s">
-        <v>29</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
+        <v>60</v>
+      </c>
+      <c r="P21">
+        <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>94</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>95</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="H22" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="I22" t="s">
         <v>37</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="K22" t="s">
         <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="M22" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N22" t="s">
         <v>59</v>
@@ -2216,14 +2268,14 @@
       <c r="O22" t="s">
         <v>60</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>1</v>
       </c>
       <c r="Q22" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>105</v>
       </c>
@@ -2231,31 +2283,31 @@
         <v>106</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L23" t="s">
         <v>114</v>
@@ -2264,19 +2316,19 @@
         <v>115</v>
       </c>
       <c r="N23" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="O23" t="s">
-        <v>60</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>105</v>
       </c>
@@ -2284,31 +2336,31 @@
         <v>106</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="E24" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G24" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="H24" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="I24" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J24" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L24" t="s">
         <v>114</v>
@@ -2317,48 +2369,48 @@
         <v>115</v>
       </c>
       <c r="N24" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="O24" t="s">
-        <v>60</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
+        <v>29</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="F25" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="G25" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="H25" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="I25" t="s">
         <v>37</v>
       </c>
       <c r="J25" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="K25" t="s">
         <v>25</v>
@@ -2375,90 +2427,90 @@
       <c r="O25" t="s">
         <v>60</v>
       </c>
-      <c r="P25" t="n">
-        <v>0</v>
+      <c r="P25">
+        <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="I26" t="s">
         <v>37</v>
       </c>
       <c r="J26" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="K26" t="s">
         <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="M26" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="N26" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="O26" t="s">
-        <v>140</v>
-      </c>
-      <c r="P26" t="n">
+        <v>60</v>
+      </c>
+      <c r="P26">
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="I27" t="s">
         <v>37</v>
@@ -2470,63 +2522,63 @@
         <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="M27" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="O27" t="s">
-        <v>140</v>
-      </c>
-      <c r="P27" t="n">
+        <v>60</v>
+      </c>
+      <c r="P27">
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="G28" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="H28" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="I28" t="s">
         <v>37</v>
       </c>
       <c r="J28" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="K28" t="s">
         <v>25</v>
       </c>
       <c r="L28" t="s">
-        <v>155</v>
+        <v>114</v>
       </c>
       <c r="M28" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="N28" t="s">
         <v>59</v>
@@ -2534,120 +2586,120 @@
       <c r="O28" t="s">
         <v>60</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B29" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="F29" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G29" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="H29" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="I29" t="s">
         <v>37</v>
       </c>
       <c r="J29" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="K29" t="s">
         <v>25</v>
       </c>
       <c r="L29" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="M29" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N29" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
-        <v>40</v>
-      </c>
-      <c r="P29" t="n">
+        <v>140</v>
+      </c>
+      <c r="P29">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="E30" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="F30" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G30" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="H30" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="I30" t="s">
         <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="K30" t="s">
         <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="M30" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N30" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="O30" t="s">
-        <v>40</v>
-      </c>
-      <c r="P30" t="n">
+        <v>140</v>
+      </c>
+      <c r="P30">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>146</v>
       </c>
@@ -2655,75 +2707,75 @@
         <v>147</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E31" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="G31" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="H31" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="I31" t="s">
         <v>37</v>
       </c>
       <c r="J31" t="s">
-        <v>24</v>
+        <v>154</v>
       </c>
       <c r="K31" t="s">
         <v>25</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="N31" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O31" t="s">
-        <v>40</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="P31">
+        <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>146</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>147</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F32" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="G32" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="H32" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="I32" t="s">
         <v>37</v>
@@ -2735,10 +2787,10 @@
         <v>25</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="M32" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N32" t="s">
         <v>39</v>
@@ -2746,43 +2798,43 @@
       <c r="O32" t="s">
         <v>40</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32">
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="F33" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="G33" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="H33" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="I33" t="s">
         <v>37</v>
       </c>
       <c r="J33" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="K33" t="s">
         <v>25</v>
@@ -2794,48 +2846,48 @@
         <v>115</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
       <c r="O33" t="s">
-        <v>178</v>
-      </c>
-      <c r="P33" t="n">
+        <v>40</v>
+      </c>
+      <c r="P33">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="F34" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="G34" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H34" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="I34" t="s">
         <v>37</v>
       </c>
       <c r="J34" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="K34" t="s">
         <v>25</v>
@@ -2847,72 +2899,72 @@
         <v>115</v>
       </c>
       <c r="N34" t="s">
-        <v>177</v>
+        <v>39</v>
       </c>
       <c r="O34" t="s">
-        <v>178</v>
-      </c>
-      <c r="P34" t="n">
+        <v>40</v>
+      </c>
+      <c r="P34">
         <v>1</v>
       </c>
       <c r="Q34" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>171</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E35" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="F35" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>167</v>
       </c>
       <c r="H35" t="s">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J35" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="K35" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L35" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="M35" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="N35" t="s">
-        <v>188</v>
+        <v>39</v>
       </c>
       <c r="O35" t="s">
-        <v>189</v>
-      </c>
-      <c r="P35" t="n">
+        <v>40</v>
+      </c>
+      <c r="P35">
         <v>1</v>
       </c>
       <c r="Q35" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>171</v>
       </c>
@@ -2920,31 +2972,31 @@
         <v>172</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="D36" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F36" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G36" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="H36" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="K36" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L36" t="s">
         <v>114</v>
@@ -2953,19 +3005,19 @@
         <v>115</v>
       </c>
       <c r="N36" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="O36" t="s">
-        <v>189</v>
-      </c>
-      <c r="P36" t="n">
+        <v>178</v>
+      </c>
+      <c r="P36">
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>171</v>
       </c>
@@ -2973,31 +3025,31 @@
         <v>172</v>
       </c>
       <c r="C37" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F37" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G37" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="H37" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J37" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="K37" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="L37" t="s">
         <v>114</v>
@@ -3006,19 +3058,19 @@
         <v>115</v>
       </c>
       <c r="N37" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="O37" t="s">
-        <v>189</v>
-      </c>
-      <c r="P37" t="n">
+        <v>178</v>
+      </c>
+      <c r="P37">
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>171</v>
       </c>
@@ -3026,137 +3078,137 @@
         <v>172</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="D38" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="E38" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>185</v>
       </c>
       <c r="G38" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="H38" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="I38" t="s">
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="M38" t="s">
-        <v>27</v>
+        <v>115</v>
       </c>
       <c r="N38" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="O38" t="s">
-        <v>29</v>
-      </c>
-      <c r="P38" t="n">
+        <v>189</v>
+      </c>
+      <c r="P38">
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>171</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="C39" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="G39" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H39" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="I39" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="J39" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="L39" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="M39" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="O39" t="s">
-        <v>140</v>
-      </c>
-      <c r="P39" t="n">
+        <v>189</v>
+      </c>
+      <c r="P39">
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="D40" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="H40" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="I40" t="s">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="J40" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s">
-        <v>209</v>
+        <v>79</v>
       </c>
       <c r="L40" t="s">
         <v>114</v>
@@ -3165,125 +3217,125 @@
         <v>115</v>
       </c>
       <c r="N40" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="O40" t="s">
-        <v>210</v>
-      </c>
-      <c r="P40" t="n">
+        <v>189</v>
+      </c>
+      <c r="P40">
         <v>1</v>
       </c>
       <c r="Q40" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="C41" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="D41" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E41" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="F41" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="G41" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="H41" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="I41" t="s">
-        <v>208</v>
+        <v>23</v>
       </c>
       <c r="J41" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="K41" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="L41" t="s">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="M41" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="N41" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="O41" t="s">
-        <v>210</v>
-      </c>
-      <c r="P41" t="n">
+        <v>29</v>
+      </c>
+      <c r="P41">
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D42" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="E42" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>138</v>
       </c>
       <c r="G42" t="s">
-        <v>216</v>
+        <v>200</v>
       </c>
       <c r="H42" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="I42" t="s">
-        <v>208</v>
+        <v>37</v>
       </c>
       <c r="J42" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="K42" t="s">
-        <v>209</v>
+        <v>25</v>
       </c>
       <c r="L42" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="M42" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="N42" t="s">
-        <v>210</v>
+        <v>139</v>
       </c>
       <c r="O42" t="s">
-        <v>210</v>
-      </c>
-      <c r="P42" t="n">
+        <v>140</v>
+      </c>
+      <c r="P42">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>202</v>
       </c>
@@ -3291,28 +3343,28 @@
         <v>203</v>
       </c>
       <c r="C43" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s">
         <v>207</v>
       </c>
       <c r="G43" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="H43" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="I43" t="s">
         <v>208</v>
       </c>
       <c r="J43" t="s">
-        <v>113</v>
+        <v>58</v>
       </c>
       <c r="K43" t="s">
         <v>209</v>
@@ -3329,14 +3381,14 @@
       <c r="O43" t="s">
         <v>210</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>202</v>
       </c>
@@ -3356,10 +3408,10 @@
         <v>207</v>
       </c>
       <c r="G44" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H44" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I44" t="s">
         <v>208</v>
@@ -3382,14 +3434,14 @@
       <c r="O44" t="s">
         <v>210</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>202</v>
       </c>
@@ -3409,10 +3461,10 @@
         <v>207</v>
       </c>
       <c r="G45" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="H45" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="I45" t="s">
         <v>208</v>
@@ -3435,14 +3487,14 @@
       <c r="O45" t="s">
         <v>210</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45">
         <v>1</v>
       </c>
       <c r="Q45" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>202</v>
       </c>
@@ -3462,10 +3514,10 @@
         <v>207</v>
       </c>
       <c r="G46" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H46" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I46" t="s">
         <v>208</v>
@@ -3488,14 +3540,14 @@
       <c r="O46" t="s">
         <v>210</v>
       </c>
-      <c r="P46" t="n">
+      <c r="P46">
         <v>1</v>
       </c>
       <c r="Q46" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>202</v>
       </c>
@@ -3515,10 +3567,10 @@
         <v>207</v>
       </c>
       <c r="G47" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="H47" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="I47" t="s">
         <v>208</v>
@@ -3541,14 +3593,14 @@
       <c r="O47" t="s">
         <v>210</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P47">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -3556,22 +3608,22 @@
         <v>203</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E48" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="F48" t="s">
         <v>207</v>
       </c>
       <c r="G48" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H48" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I48" t="s">
         <v>208</v>
@@ -3594,46 +3646,46 @@
       <c r="O48" t="s">
         <v>210</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P48">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>202</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="E49" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="F49" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="G49" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="H49" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="I49" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="J49" t="s">
-        <v>58</v>
+        <v>113</v>
       </c>
       <c r="K49" t="s">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="L49" t="s">
         <v>114</v>
@@ -3642,51 +3694,51 @@
         <v>115</v>
       </c>
       <c r="N49" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="O49" t="s">
-        <v>178</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
+        <v>210</v>
+      </c>
+      <c r="P49">
+        <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>202</v>
       </c>
       <c r="B50" t="s">
-        <v>18</v>
+        <v>203</v>
       </c>
       <c r="C50" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="D50" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="E50" t="s">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="F50" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="G50" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="H50" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="I50" t="s">
-        <v>37</v>
+        <v>208</v>
       </c>
       <c r="J50" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="K50" t="s">
-        <v>25</v>
+        <v>209</v>
       </c>
       <c r="L50" t="s">
         <v>114</v>
@@ -3695,20 +3747,185 @@
         <v>115</v>
       </c>
       <c r="N50" t="s">
+        <v>210</v>
+      </c>
+      <c r="O50" t="s">
+        <v>210</v>
+      </c>
+      <c r="P50">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>202</v>
+      </c>
+      <c r="B51" t="s">
+        <v>203</v>
+      </c>
+      <c r="C51" t="s">
+        <v>204</v>
+      </c>
+      <c r="D51" t="s">
+        <v>205</v>
+      </c>
+      <c r="E51" t="s">
+        <v>206</v>
+      </c>
+      <c r="F51" t="s">
+        <v>207</v>
+      </c>
+      <c r="G51" t="s">
+        <v>228</v>
+      </c>
+      <c r="H51" t="s">
+        <v>229</v>
+      </c>
+      <c r="I51" t="s">
+        <v>208</v>
+      </c>
+      <c r="J51" t="s">
+        <v>113</v>
+      </c>
+      <c r="K51" t="s">
+        <v>209</v>
+      </c>
+      <c r="L51" t="s">
+        <v>114</v>
+      </c>
+      <c r="M51" t="s">
+        <v>115</v>
+      </c>
+      <c r="N51" t="s">
+        <v>210</v>
+      </c>
+      <c r="O51" t="s">
+        <v>210</v>
+      </c>
+      <c r="P51">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" t="s">
+        <v>131</v>
+      </c>
+      <c r="C52" t="s">
+        <v>230</v>
+      </c>
+      <c r="D52" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" t="s">
+        <v>232</v>
+      </c>
+      <c r="F52" t="s">
+        <v>233</v>
+      </c>
+      <c r="G52" t="s">
+        <v>230</v>
+      </c>
+      <c r="H52" t="s">
+        <v>234</v>
+      </c>
+      <c r="I52" t="s">
+        <v>37</v>
+      </c>
+      <c r="J52" t="s">
+        <v>58</v>
+      </c>
+      <c r="K52" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" t="s">
+        <v>114</v>
+      </c>
+      <c r="M52" t="s">
+        <v>115</v>
+      </c>
+      <c r="N52" t="s">
+        <v>177</v>
+      </c>
+      <c r="O52" t="s">
+        <v>178</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>236</v>
+      </c>
+      <c r="E53" t="s">
+        <v>237</v>
+      </c>
+      <c r="F53" t="s">
+        <v>238</v>
+      </c>
+      <c r="G53" t="s">
+        <v>235</v>
+      </c>
+      <c r="H53" t="s">
+        <v>236</v>
+      </c>
+      <c r="I53" t="s">
+        <v>37</v>
+      </c>
+      <c r="J53" t="s">
+        <v>154</v>
+      </c>
+      <c r="K53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L53" t="s">
+        <v>114</v>
+      </c>
+      <c r="M53" t="s">
+        <v>115</v>
+      </c>
+      <c r="N53" t="s">
         <v>39</v>
       </c>
-      <c r="O50" t="s">
+      <c r="O53" t="s">
         <v>40</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P53">
         <v>0</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="Q53" t="s">
         <v>116</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a6274e99-f707-4183-90a3-28f81526dfab}" enabled="1" method="Standard" siteId="{0a02388e-6178-4513-9b82-88b9dc6bf457}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -71,6 +71,60 @@
     <t xml:space="preserve">overall-economy</t>
   </si>
   <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total nonfarm payroll jobs, measured at location of employment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Commercial bankruptcy rate</t>
   </si>
   <si>
@@ -89,9 +143,6 @@
     <t xml:space="preserve">0.[0]</t>
   </si>
   <si>
-    <t xml:space="preserve">pct</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rolling 12-month total</t>
   </si>
   <si>
@@ -125,9 +176,6 @@
     <t xml:space="preserve">federal-obligations-total</t>
   </si>
   <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
     <t xml:space="preserve">$123k</t>
   </si>
   <si>
@@ -188,15 +236,6 @@
     <t xml:space="preserve">patents-filed</t>
   </si>
   <si>
-    <t xml:space="preserve">123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
     <t xml:space="preserve">DMV-2026-02-18</t>
   </si>
   <si>
@@ -239,9 +278,6 @@
     <t xml:space="preserve">Percentage of labor force not currently employed  </t>
   </si>
   <si>
-    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
     <t xml:space="preserve">Unemployment rate, total</t>
   </si>
   <si>
@@ -354,12 +390,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level</t>
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-02-27</t>
@@ -1130,37 +1160,37 @@
         <v>22</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -1171,49 +1201,49 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3" t="s">
+        <v>27</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="s">
         <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -1224,49 +1254,49 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" t="s">
+        <v>27</v>
+      </c>
+      <c r="L4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
+      </c>
+      <c r="N4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="s">
         <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" t="s">
-        <v>40</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -1277,57 +1307,57 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M5" t="s">
         <v>44</v>
       </c>
-      <c r="H5" t="s">
+      <c r="N5" t="s">
         <v>45</v>
       </c>
-      <c r="I5" t="s">
-        <v>37</v>
-      </c>
-      <c r="J5" t="s">
-        <v>38</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" t="s">
-        <v>39</v>
-      </c>
       <c r="O5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
@@ -1339,749 +1369,749 @@
         <v>50</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="M6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O6" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s">
         <v>54</v>
       </c>
-      <c r="F7" t="s">
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7" t="s">
         <v>55</v>
       </c>
-      <c r="G7" t="s">
+      <c r="O7" t="s">
         <v>56</v>
       </c>
-      <c r="H7" t="s">
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="s">
         <v>57</v>
-      </c>
-      <c r="I7" t="s">
-        <v>37</v>
-      </c>
-      <c r="J7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" t="s">
-        <v>59</v>
-      </c>
-      <c r="O7" t="s">
-        <v>60</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="F8" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="I8" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="M8" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N8" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O8" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
         <v>65</v>
       </c>
-      <c r="G9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="M9" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O9" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" t="s">
         <v>70</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>71</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
         <v>72</v>
       </c>
-      <c r="D10" t="s">
+      <c r="H10" t="s">
         <v>73</v>
       </c>
-      <c r="E10" t="s">
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
+      </c>
+      <c r="O10" t="s">
+        <v>31</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="s">
         <v>74</v>
-      </c>
-      <c r="F10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I10" t="s">
-        <v>37</v>
-      </c>
-      <c r="J10" t="s">
-        <v>78</v>
-      </c>
-      <c r="K10" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" t="s">
-        <v>80</v>
-      </c>
-      <c r="M10" t="s">
-        <v>81</v>
-      </c>
-      <c r="N10" t="s">
-        <v>39</v>
-      </c>
-      <c r="O10" t="s">
-        <v>40</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="M11" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="N11" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O11" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="K12" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="M12" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="N12" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O12" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L13" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="N13" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O13" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s">
         <v>90</v>
       </c>
-      <c r="I14" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" t="s">
-        <v>78</v>
-      </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M14" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="N14" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O14" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="G15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" t="s">
         <v>91</v>
       </c>
-      <c r="H15" t="s">
+      <c r="L15" t="s">
         <v>92</v>
       </c>
-      <c r="I15" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" t="s">
-        <v>78</v>
-      </c>
-      <c r="K15" t="s">
-        <v>79</v>
-      </c>
-      <c r="L15" t="s">
-        <v>80</v>
-      </c>
       <c r="M15" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="N15" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O15" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" t="s">
+        <v>92</v>
+      </c>
+      <c r="M16" t="s">
         <v>93</v>
       </c>
-      <c r="D16" t="s">
+      <c r="N16" t="s">
+        <v>55</v>
+      </c>
+      <c r="O16" t="s">
+        <v>56</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="s">
         <v>94</v>
-      </c>
-      <c r="E16" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" t="s">
-        <v>96</v>
-      </c>
-      <c r="G16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" t="s">
-        <v>98</v>
-      </c>
-      <c r="I16" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" t="s">
-        <v>80</v>
-      </c>
-      <c r="M16" t="s">
-        <v>81</v>
-      </c>
-      <c r="N16" t="s">
-        <v>59</v>
-      </c>
-      <c r="O16" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" t="s">
+        <v>90</v>
+      </c>
+      <c r="K17" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" t="s">
+        <v>92</v>
+      </c>
+      <c r="M17" t="s">
         <v>93</v>
       </c>
-      <c r="D17" t="s">
+      <c r="N17" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" t="s">
+        <v>56</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="s">
         <v>94</v>
-      </c>
-      <c r="E17" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G17" t="s">
-        <v>99</v>
-      </c>
-      <c r="H17" t="s">
-        <v>100</v>
-      </c>
-      <c r="I17" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" t="s">
-        <v>24</v>
-      </c>
-      <c r="K17" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" t="s">
-        <v>80</v>
-      </c>
-      <c r="M17" t="s">
-        <v>81</v>
-      </c>
-      <c r="N17" t="s">
-        <v>59</v>
-      </c>
-      <c r="O17" t="s">
-        <v>60</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" t="s">
+        <v>90</v>
+      </c>
+      <c r="K18" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" t="s">
+        <v>92</v>
+      </c>
+      <c r="M18" t="s">
         <v>93</v>
       </c>
-      <c r="D18" t="s">
+      <c r="N18" t="s">
+        <v>55</v>
+      </c>
+      <c r="O18" t="s">
+        <v>56</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="s">
         <v>94</v>
-      </c>
-      <c r="E18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" t="s">
-        <v>101</v>
-      </c>
-      <c r="H18" t="s">
-        <v>102</v>
-      </c>
-      <c r="I18" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" t="s">
-        <v>25</v>
-      </c>
-      <c r="L18" t="s">
-        <v>80</v>
-      </c>
-      <c r="M18" t="s">
-        <v>81</v>
-      </c>
-      <c r="N18" t="s">
-        <v>59</v>
-      </c>
-      <c r="O18" t="s">
-        <v>60</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" t="s">
+        <v>42</v>
+      </c>
+      <c r="K19" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" t="s">
+        <v>92</v>
+      </c>
+      <c r="M19" t="s">
         <v>93</v>
       </c>
-      <c r="D19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" t="s">
-        <v>96</v>
-      </c>
-      <c r="G19" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" t="s">
-        <v>37</v>
-      </c>
-      <c r="J19" t="s">
-        <v>24</v>
-      </c>
-      <c r="K19" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" t="s">
-        <v>80</v>
-      </c>
-      <c r="M19" t="s">
-        <v>81</v>
-      </c>
       <c r="N19" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="O19" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="s">
         <v>105</v>
       </c>
-      <c r="B20" t="s">
+      <c r="D20" t="s">
         <v>106</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E20" t="s">
         <v>107</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F20" t="s">
         <v>108</v>
-      </c>
-      <c r="E20" t="s">
-        <v>109</v>
-      </c>
-      <c r="F20" t="s">
-        <v>110</v>
       </c>
       <c r="G20" t="s">
         <v>111</v>
@@ -2090,154 +2120,154 @@
         <v>112</v>
       </c>
       <c r="I20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L20" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M20" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="N20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O20" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" t="s">
         <v>105</v>
       </c>
-      <c r="B21" t="s">
+      <c r="D21" t="s">
         <v>106</v>
       </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
         <v>107</v>
       </c>
-      <c r="D21" t="s">
+      <c r="F21" t="s">
         <v>108</v>
       </c>
-      <c r="E21" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" t="s">
-        <v>110</v>
-      </c>
       <c r="G21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I21" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="K21" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M21" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="N21" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="O21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
+        <v>83</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
         <v>105</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" t="s">
         <v>106</v>
       </c>
-      <c r="C22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" t="s">
-        <v>120</v>
-      </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="G22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I22" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M22" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="O22" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D23" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F23" t="s">
         <v>122</v>
@@ -2249,463 +2279,463 @@
         <v>124</v>
       </c>
       <c r="I23" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M23" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N23" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="O23" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" t="s">
+        <v>121</v>
+      </c>
+      <c r="F24" t="s">
+        <v>122</v>
+      </c>
+      <c r="G24" t="s">
+        <v>127</v>
+      </c>
+      <c r="H24" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" t="s">
+        <v>125</v>
+      </c>
+      <c r="K24" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" t="s">
+        <v>28</v>
+      </c>
+      <c r="M24" t="s">
+        <v>29</v>
+      </c>
+      <c r="N24" t="s">
+        <v>45</v>
+      </c>
+      <c r="O24" t="s">
+        <v>46</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="s">
         <v>126</v>
-      </c>
-      <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" t="s">
-        <v>128</v>
-      </c>
-      <c r="F24" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24" t="s">
-        <v>126</v>
-      </c>
-      <c r="H24" t="s">
-        <v>127</v>
-      </c>
-      <c r="I24" t="s">
-        <v>37</v>
-      </c>
-      <c r="J24" t="s">
-        <v>38</v>
-      </c>
-      <c r="K24" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" t="s">
-        <v>114</v>
-      </c>
-      <c r="M24" t="s">
-        <v>115</v>
-      </c>
-      <c r="N24" t="s">
-        <v>59</v>
-      </c>
-      <c r="O24" t="s">
-        <v>60</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D25" t="s">
         <v>130</v>
       </c>
-      <c r="B25" t="s">
+      <c r="E25" t="s">
         <v>131</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>132</v>
       </c>
-      <c r="D25" t="s">
-        <v>133</v>
-      </c>
-      <c r="E25" t="s">
-        <v>134</v>
-      </c>
-      <c r="F25" t="s">
-        <v>110</v>
-      </c>
       <c r="G25" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H25" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="I25" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L25" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M25" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="O25" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E26" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="H26" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="I26" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L26" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="M26" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="N26" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="O26" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="B27" t="s">
-        <v>131</v>
+        <v>118</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F27" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G27" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="H27" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="I27" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="K27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L27" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="M27" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>139</v>
+        <v>30</v>
       </c>
       <c r="O27" t="s">
-        <v>140</v>
+        <v>31</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F28" t="s">
-        <v>151</v>
+        <v>122</v>
       </c>
       <c r="G28" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="H28" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="K28" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L28" t="s">
-        <v>155</v>
+        <v>28</v>
       </c>
       <c r="M28" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="N28" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="O28" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>61</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>140</v>
+      </c>
+      <c r="B29" t="s">
+        <v>141</v>
+      </c>
+      <c r="C29" t="s">
         <v>146</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" t="s">
         <v>147</v>
       </c>
-      <c r="C29" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" t="s">
-        <v>158</v>
-      </c>
       <c r="E29" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="F29" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="G29" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="H29" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L29" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M29" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="N29" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="O29" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B30" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D30" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E30" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F30" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="G30" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="H30" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L30" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M30" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="N30" t="s">
-        <v>39</v>
+        <v>149</v>
       </c>
       <c r="O30" t="s">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G31" t="s">
+        <v>162</v>
+      </c>
+      <c r="H31" t="s">
+        <v>163</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J31" t="s">
+        <v>164</v>
+      </c>
+      <c r="K31" t="s">
+        <v>27</v>
+      </c>
+      <c r="L31" t="s">
         <v>165</v>
       </c>
-      <c r="H31" t="s">
+      <c r="M31" t="s">
         <v>166</v>
       </c>
-      <c r="I31" t="s">
-        <v>37</v>
-      </c>
-      <c r="J31" t="s">
-        <v>24</v>
-      </c>
-      <c r="K31" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" t="s">
-        <v>114</v>
-      </c>
-      <c r="M31" t="s">
-        <v>115</v>
-      </c>
       <c r="N31" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="O31" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>156</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="C32" t="s">
         <v>167</v>
@@ -2720,57 +2750,57 @@
         <v>170</v>
       </c>
       <c r="G32" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H32" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I32" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="K32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="O32" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B33" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="D33" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E33" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
         <v>173</v>
@@ -2779,316 +2809,316 @@
         <v>174</v>
       </c>
       <c r="I33" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="K33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L33" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M33" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="O33" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
+        <v>170</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
         <v>176</v>
       </c>
-      <c r="G34" t="s">
-        <v>179</v>
-      </c>
-      <c r="H34" t="s">
-        <v>180</v>
-      </c>
       <c r="I34" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L34" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M34" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N34" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="O34" t="s">
-        <v>178</v>
+        <v>56</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="B35" t="s">
-        <v>172</v>
+        <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D35" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="E35" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F35" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H35" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="I35" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="K35" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="M35" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="N35" t="s">
-        <v>188</v>
+        <v>55</v>
       </c>
       <c r="O35" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>185</v>
+      </c>
+      <c r="F36" t="s">
+        <v>186</v>
+      </c>
+      <c r="G36" t="s">
         <v>183</v>
       </c>
-      <c r="E36" t="s">
+      <c r="H36" t="s">
         <v>184</v>
       </c>
-      <c r="F36" t="s">
-        <v>185</v>
-      </c>
-      <c r="G36" t="s">
-        <v>190</v>
-      </c>
-      <c r="H36" t="s">
-        <v>191</v>
-      </c>
       <c r="I36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="K36" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L36" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M36" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N36" t="s">
+        <v>187</v>
+      </c>
+      <c r="O36" t="s">
         <v>188</v>
       </c>
-      <c r="O36" t="s">
-        <v>189</v>
-      </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B37" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C37" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D37" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E37" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G37" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H37" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="I37" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J37" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="K37" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="L37" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M37" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N37" t="s">
+        <v>187</v>
+      </c>
+      <c r="O37" t="s">
         <v>188</v>
       </c>
-      <c r="O37" t="s">
-        <v>189</v>
-      </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="C38" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
         <v>194</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>195</v>
       </c>
-      <c r="E38" t="s">
+      <c r="G38" t="s">
         <v>196</v>
       </c>
-      <c r="F38" t="s">
-        <v>22</v>
-      </c>
-      <c r="G38" t="s">
-        <v>194</v>
-      </c>
       <c r="H38" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I38" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="K38" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="O38" t="s">
-        <v>29</v>
+        <v>199</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>181</v>
       </c>
       <c r="B39" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="C39" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E39" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F39" t="s">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="G39" t="s">
         <v>200</v>
@@ -3097,614 +3127,773 @@
         <v>201</v>
       </c>
       <c r="I39" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="J39" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
       <c r="L39" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="M39" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="O39" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>116</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>181</v>
+      </c>
+      <c r="B40" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" t="s">
+        <v>193</v>
+      </c>
+      <c r="E40" t="s">
+        <v>194</v>
+      </c>
+      <c r="F40" t="s">
+        <v>195</v>
+      </c>
+      <c r="G40" t="s">
         <v>202</v>
       </c>
-      <c r="B40" t="s">
+      <c r="H40" t="s">
         <v>203</v>
       </c>
-      <c r="C40" t="s">
-        <v>204</v>
-      </c>
-      <c r="D40" t="s">
-        <v>205</v>
-      </c>
-      <c r="E40" t="s">
-        <v>206</v>
-      </c>
-      <c r="F40" t="s">
-        <v>207</v>
-      </c>
-      <c r="G40" t="s">
-        <v>206</v>
-      </c>
-      <c r="H40" t="s">
-        <v>205</v>
-      </c>
       <c r="I40" t="s">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="J40" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="K40" t="s">
-        <v>209</v>
+        <v>91</v>
       </c>
       <c r="L40" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M40" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="O40" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="C41" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="D41" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E41" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F41" t="s">
-        <v>207</v>
+        <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="H41" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="I41" t="s">
-        <v>208</v>
+        <v>41</v>
       </c>
       <c r="J41" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="K41" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="L41" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="M41" t="s">
-        <v>115</v>
+        <v>44</v>
       </c>
       <c r="N41" t="s">
-        <v>210</v>
+        <v>45</v>
       </c>
       <c r="O41" t="s">
-        <v>210</v>
+        <v>46</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
+        <v>207</v>
+      </c>
+      <c r="D42" t="s">
+        <v>208</v>
+      </c>
+      <c r="E42" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" t="s">
+        <v>148</v>
+      </c>
+      <c r="G42" t="s">
+        <v>210</v>
+      </c>
+      <c r="H42" t="s">
         <v>211</v>
       </c>
-      <c r="D42" t="s">
-        <v>212</v>
-      </c>
-      <c r="E42" t="s">
-        <v>213</v>
-      </c>
-      <c r="F42" t="s">
-        <v>207</v>
-      </c>
-      <c r="G42" t="s">
-        <v>216</v>
-      </c>
-      <c r="H42" t="s">
-        <v>217</v>
-      </c>
       <c r="I42" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="K42" t="s">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="L42" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="M42" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="N42" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="O42" t="s">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>41</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C43" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D43" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E43" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F43" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G43" t="s">
+        <v>216</v>
+      </c>
+      <c r="H43" t="s">
+        <v>215</v>
+      </c>
+      <c r="I43" t="s">
         <v>218</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
+        <v>26</v>
+      </c>
+      <c r="K43" t="s">
         <v>219</v>
       </c>
-      <c r="I43" t="s">
-        <v>208</v>
-      </c>
-      <c r="J43" t="s">
-        <v>113</v>
-      </c>
-      <c r="K43" t="s">
-        <v>209</v>
-      </c>
       <c r="L43" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M43" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O43" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C44" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D44" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F44" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G44" t="s">
+        <v>224</v>
+      </c>
+      <c r="H44" t="s">
+        <v>225</v>
+      </c>
+      <c r="I44" t="s">
+        <v>218</v>
+      </c>
+      <c r="J44" t="s">
+        <v>125</v>
+      </c>
+      <c r="K44" t="s">
+        <v>219</v>
+      </c>
+      <c r="L44" t="s">
+        <v>28</v>
+      </c>
+      <c r="M44" t="s">
+        <v>29</v>
+      </c>
+      <c r="N44" t="s">
         <v>220</v>
       </c>
-      <c r="H44" t="s">
-        <v>221</v>
-      </c>
-      <c r="I44" t="s">
-        <v>208</v>
-      </c>
-      <c r="J44" t="s">
-        <v>113</v>
-      </c>
-      <c r="K44" t="s">
-        <v>209</v>
-      </c>
-      <c r="L44" t="s">
-        <v>114</v>
-      </c>
-      <c r="M44" t="s">
-        <v>115</v>
-      </c>
-      <c r="N44" t="s">
-        <v>210</v>
-      </c>
       <c r="O44" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C45" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D45" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F45" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G45" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H45" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="I45" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="J45" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K45" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L45" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M45" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N45" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O45" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B46" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C46" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D46" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F46" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G46" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="H46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I46" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="J46" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K46" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L46" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M46" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N46" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O46" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C47" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D47" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="E47" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="F47" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G47" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H47" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="I47" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="J47" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K47" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L47" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M47" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N47" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O47" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="D48" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="E48" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="F48" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G48" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H48" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="I48" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="J48" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K48" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L48" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M48" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="O48" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
-        <v>131</v>
+        <v>213</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D49" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="E49" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F49" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="G49" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I49" t="s">
-        <v>37</v>
+        <v>218</v>
       </c>
       <c r="J49" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="K49" t="s">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="L49" t="s">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="M49" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>177</v>
+        <v>220</v>
       </c>
       <c r="O49" t="s">
-        <v>178</v>
+        <v>220</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>30</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>212</v>
+      </c>
+      <c r="B50" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" t="s">
+        <v>221</v>
+      </c>
+      <c r="D50" t="s">
+        <v>222</v>
+      </c>
+      <c r="E50" t="s">
+        <v>223</v>
+      </c>
+      <c r="F50" t="s">
+        <v>217</v>
+      </c>
+      <c r="G50" t="s">
+        <v>236</v>
+      </c>
+      <c r="H50" t="s">
+        <v>237</v>
+      </c>
+      <c r="I50" t="s">
+        <v>218</v>
+      </c>
+      <c r="J50" t="s">
+        <v>125</v>
+      </c>
+      <c r="K50" t="s">
+        <v>219</v>
+      </c>
+      <c r="L50" t="s">
+        <v>28</v>
+      </c>
+      <c r="M50" t="s">
+        <v>29</v>
+      </c>
+      <c r="N50" t="s">
+        <v>220</v>
+      </c>
+      <c r="O50" t="s">
+        <v>220</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>212</v>
+      </c>
+      <c r="B51" t="s">
+        <v>213</v>
+      </c>
+      <c r="C51" t="s">
+        <v>214</v>
+      </c>
+      <c r="D51" t="s">
+        <v>215</v>
+      </c>
+      <c r="E51" t="s">
+        <v>216</v>
+      </c>
+      <c r="F51" t="s">
+        <v>217</v>
+      </c>
+      <c r="G51" t="s">
+        <v>238</v>
+      </c>
+      <c r="H51" t="s">
+        <v>239</v>
+      </c>
+      <c r="I51" t="s">
+        <v>218</v>
+      </c>
+      <c r="J51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K51" t="s">
+        <v>219</v>
+      </c>
+      <c r="L51" t="s">
+        <v>28</v>
+      </c>
+      <c r="M51" t="s">
+        <v>29</v>
+      </c>
+      <c r="N51" t="s">
+        <v>220</v>
+      </c>
+      <c r="O51" t="s">
+        <v>220</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>140</v>
+      </c>
+      <c r="B52" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" t="s">
+        <v>240</v>
+      </c>
+      <c r="D52" t="s">
+        <v>241</v>
+      </c>
+      <c r="E52" t="s">
+        <v>242</v>
+      </c>
+      <c r="F52" t="s">
+        <v>243</v>
+      </c>
+      <c r="G52" t="s">
+        <v>240</v>
+      </c>
+      <c r="H52" t="s">
+        <v>244</v>
+      </c>
+      <c r="I52" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" t="s">
+        <v>26</v>
+      </c>
+      <c r="K52" t="s">
+        <v>27</v>
+      </c>
+      <c r="L52" t="s">
+        <v>28</v>
+      </c>
+      <c r="M52" t="s">
+        <v>29</v>
+      </c>
+      <c r="N52" t="s">
+        <v>187</v>
+      </c>
+      <c r="O52" t="s">
+        <v>188</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
         <v>17</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B53" t="s">
         <v>18</v>
       </c>
-      <c r="C50" t="s">
-        <v>235</v>
-      </c>
-      <c r="D50" t="s">
-        <v>236</v>
-      </c>
-      <c r="E50" t="s">
-        <v>237</v>
-      </c>
-      <c r="F50" t="s">
-        <v>238</v>
-      </c>
-      <c r="G50" t="s">
-        <v>235</v>
-      </c>
-      <c r="H50" t="s">
-        <v>236</v>
-      </c>
-      <c r="I50" t="s">
-        <v>37</v>
-      </c>
-      <c r="J50" t="s">
-        <v>154</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="C53" t="s">
+        <v>245</v>
+      </c>
+      <c r="D53" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" t="s">
+        <v>247</v>
+      </c>
+      <c r="F53" t="s">
+        <v>248</v>
+      </c>
+      <c r="G53" t="s">
+        <v>245</v>
+      </c>
+      <c r="H53" t="s">
+        <v>246</v>
+      </c>
+      <c r="I53" t="s">
         <v>25</v>
       </c>
-      <c r="L50" t="s">
-        <v>114</v>
-      </c>
-      <c r="M50" t="s">
-        <v>115</v>
-      </c>
-      <c r="N50" t="s">
-        <v>39</v>
-      </c>
-      <c r="O50" t="s">
-        <v>40</v>
-      </c>
-      <c r="P50" t="n">
+      <c r="J53" t="s">
+        <v>164</v>
+      </c>
+      <c r="K53" t="s">
+        <v>27</v>
+      </c>
+      <c r="L53" t="s">
+        <v>28</v>
+      </c>
+      <c r="M53" t="s">
+        <v>29</v>
+      </c>
+      <c r="N53" t="s">
+        <v>55</v>
+      </c>
+      <c r="O53" t="s">
+        <v>56</v>
+      </c>
+      <c r="P53" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="s">
-        <v>116</v>
+      <c r="Q53" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -149,114 +149,117 @@
     <t xml:space="preserve">rolling-12-sum</t>
   </si>
   <si>
-    <t xml:space="preserve">2024Q2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q2</t>
+    <t xml:space="preserve">2024Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-03-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USASpending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2025-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-02-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
     <t xml:space="preserve">Venture capital deals</t>
   </si>
   <si>
@@ -392,64 +395,64 @@
     <t xml:space="preserve">0.[0]%</t>
   </si>
   <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active residential for-sale listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active-listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential listing price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-listing-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median price of for-sale residential listings on the market in a given month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
     <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active residential for-sale listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median price of for-sale residential listings on the market in a given month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
   </si>
   <si>
     <t xml:space="preserve">Overnight visitors</t>
@@ -1667,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12">
@@ -1690,10 +1693,10 @@
         <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I12" t="s">
         <v>25</v>
@@ -1720,48 +1723,48 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F13" t="s">
         <v>22</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s">
         <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N13" t="s">
         <v>55</v>
@@ -1773,48 +1776,48 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
         <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N14" t="s">
         <v>55</v>
@@ -1826,48 +1829,48 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N15" t="s">
         <v>55</v>
@@ -1879,48 +1882,48 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" t="s">
         <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N16" t="s">
         <v>55</v>
@@ -1932,48 +1935,48 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F17" t="s">
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" t="s">
         <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N17" t="s">
         <v>55</v>
@@ -1985,48 +1988,48 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F18" t="s">
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I18" t="s">
         <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N18" t="s">
         <v>55</v>
@@ -2038,33 +2041,33 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I19" t="s">
         <v>25</v>
@@ -2076,10 +2079,10 @@
         <v>27</v>
       </c>
       <c r="L19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N19" t="s">
         <v>30</v>
@@ -2096,28 +2099,28 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I20" t="s">
         <v>25</v>
@@ -2129,10 +2132,10 @@
         <v>27</v>
       </c>
       <c r="L20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N20" t="s">
         <v>30</v>
@@ -2149,28 +2152,28 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
         <v>25</v>
@@ -2182,10 +2185,10 @@
         <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N21" t="s">
         <v>30</v>
@@ -2202,28 +2205,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s">
         <v>25</v>
@@ -2235,10 +2238,10 @@
         <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N22" t="s">
         <v>30</v>
@@ -2255,37 +2258,37 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L23" t="s">
         <v>28</v>
@@ -2303,27 +2306,27 @@
         <v>0</v>
       </c>
       <c r="Q23" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
         <v>127</v>
@@ -2335,10 +2338,10 @@
         <v>41</v>
       </c>
       <c r="J24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L24" t="s">
         <v>28</v>
@@ -2356,15 +2359,15 @@
         <v>0</v>
       </c>
       <c r="Q24" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
         <v>129</v>
@@ -2414,10 +2417,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
         <v>133</v>
@@ -2467,10 +2470,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C27" t="s">
         <v>136</v>
@@ -2535,7 +2538,7 @@
         <v>144</v>
       </c>
       <c r="F28" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G28" t="s">
         <v>142</v>
@@ -2568,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29">
@@ -2579,22 +2582,22 @@
         <v>141</v>
       </c>
       <c r="C29" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" t="s">
         <v>147</v>
       </c>
-      <c r="E29" t="s">
-        <v>146</v>
-      </c>
       <c r="F29" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" t="s">
+        <v>147</v>
+      </c>
+      <c r="H29" t="s">
         <v>148</v>
-      </c>
-      <c r="G29" t="s">
-        <v>146</v>
-      </c>
-      <c r="H29" t="s">
-        <v>147</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
@@ -2606,22 +2609,22 @@
         <v>27</v>
       </c>
       <c r="L29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30">
@@ -2632,22 +2635,22 @@
         <v>141</v>
       </c>
       <c r="C30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H30" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
@@ -2659,63 +2662,63 @@
         <v>27</v>
       </c>
       <c r="L30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O30" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D31" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G31" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K31" t="s">
         <v>27</v>
       </c>
       <c r="L31" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -2732,28 +2735,28 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C32" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F32" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H32" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
@@ -2780,33 +2783,33 @@
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
@@ -2833,33 +2836,33 @@
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D34" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
@@ -2886,33 +2889,33 @@
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
+        <v>179</v>
+      </c>
+      <c r="E35" t="s">
+        <v>180</v>
+      </c>
+      <c r="F35" t="s">
+        <v>181</v>
+      </c>
+      <c r="G35" t="s">
         <v>178</v>
       </c>
-      <c r="E35" t="s">
+      <c r="H35" t="s">
         <v>179</v>
-      </c>
-      <c r="F35" t="s">
-        <v>180</v>
-      </c>
-      <c r="G35" t="s">
-        <v>177</v>
-      </c>
-      <c r="H35" t="s">
-        <v>178</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
@@ -2944,28 +2947,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D36" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" t="s">
         <v>184</v>
       </c>
-      <c r="E36" t="s">
+      <c r="H36" t="s">
         <v>185</v>
-      </c>
-      <c r="F36" t="s">
-        <v>186</v>
-      </c>
-      <c r="G36" t="s">
-        <v>183</v>
-      </c>
-      <c r="H36" t="s">
-        <v>184</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
@@ -2983,42 +2986,42 @@
         <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D37" t="s">
+        <v>191</v>
+      </c>
+      <c r="E37" t="s">
+        <v>192</v>
+      </c>
+      <c r="F37" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" t="s">
         <v>190</v>
       </c>
-      <c r="E37" t="s">
+      <c r="H37" t="s">
         <v>191</v>
-      </c>
-      <c r="F37" t="s">
-        <v>186</v>
-      </c>
-      <c r="G37" t="s">
-        <v>189</v>
-      </c>
-      <c r="H37" t="s">
-        <v>190</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -3036,51 +3039,51 @@
         <v>29</v>
       </c>
       <c r="N37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F38" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G38" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H38" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I38" t="s">
         <v>41</v>
       </c>
       <c r="J38" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L38" t="s">
         <v>28</v>
@@ -3089,10 +3092,10 @@
         <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3103,37 +3106,37 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B39" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C39" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G39" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H39" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I39" t="s">
         <v>41</v>
       </c>
       <c r="J39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K39" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L39" t="s">
         <v>28</v>
@@ -3142,10 +3145,10 @@
         <v>29</v>
       </c>
       <c r="N39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O39" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3156,37 +3159,37 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I40" t="s">
         <v>41</v>
       </c>
       <c r="J40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L40" t="s">
         <v>28</v>
@@ -3195,10 +3198,10 @@
         <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3209,28 +3212,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B41" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F41" t="s">
         <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I41" t="s">
         <v>41</v>
@@ -3268,22 +3271,22 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
@@ -3295,57 +3298,57 @@
         <v>27</v>
       </c>
       <c r="L42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E43" t="s">
+        <v>217</v>
+      </c>
+      <c r="F43" t="s">
+        <v>218</v>
+      </c>
+      <c r="G43" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" t="s">
         <v>216</v>
       </c>
-      <c r="F43" t="s">
-        <v>217</v>
-      </c>
-      <c r="G43" t="s">
-        <v>216</v>
-      </c>
-      <c r="H43" t="s">
-        <v>215</v>
-      </c>
       <c r="I43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J43" t="s">
         <v>26</v>
       </c>
       <c r="K43" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L43" t="s">
         <v>28</v>
@@ -3354,10 +3357,10 @@
         <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O43" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3368,37 +3371,37 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C44" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D44" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G44" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H44" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J44" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L44" t="s">
         <v>28</v>
@@ -3407,10 +3410,10 @@
         <v>29</v>
       </c>
       <c r="N44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O44" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3421,37 +3424,37 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E45" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G45" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H45" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J45" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L45" t="s">
         <v>28</v>
@@ -3460,10 +3463,10 @@
         <v>29</v>
       </c>
       <c r="N45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3474,37 +3477,37 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B46" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F46" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G46" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H46" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I46" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J46" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L46" t="s">
         <v>28</v>
@@ -3513,10 +3516,10 @@
         <v>29</v>
       </c>
       <c r="N46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3527,37 +3530,37 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E47" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F47" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -3566,10 +3569,10 @@
         <v>29</v>
       </c>
       <c r="N47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3580,37 +3583,37 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I48" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K48" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3619,10 +3622,10 @@
         <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O48" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3633,37 +3636,37 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D49" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
@@ -3672,10 +3675,10 @@
         <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O49" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3686,37 +3689,37 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B50" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D50" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E50" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3725,10 +3728,10 @@
         <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O50" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3739,37 +3742,37 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C51" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D51" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="E51" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G51" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H51" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I51" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J51" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K51" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3778,10 +3781,10 @@
         <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O51" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3798,22 +3801,22 @@
         <v>141</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D52" t="s">
+        <v>242</v>
+      </c>
+      <c r="E52" t="s">
+        <v>243</v>
+      </c>
+      <c r="F52" t="s">
+        <v>244</v>
+      </c>
+      <c r="G52" t="s">
         <v>241</v>
       </c>
-      <c r="E52" t="s">
-        <v>242</v>
-      </c>
-      <c r="F52" t="s">
-        <v>243</v>
-      </c>
-      <c r="G52" t="s">
-        <v>240</v>
-      </c>
       <c r="H52" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I52" t="s">
         <v>25</v>
@@ -3831,16 +3834,16 @@
         <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
@@ -3851,28 +3854,28 @@
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D53" t="s">
+        <v>247</v>
+      </c>
+      <c r="E53" t="s">
+        <v>248</v>
+      </c>
+      <c r="F53" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" t="s">
         <v>246</v>
       </c>
-      <c r="E53" t="s">
+      <c r="H53" t="s">
         <v>247</v>
-      </c>
-      <c r="F53" t="s">
-        <v>248</v>
-      </c>
-      <c r="G53" t="s">
-        <v>245</v>
-      </c>
-      <c r="H53" t="s">
-        <v>246</v>
       </c>
       <c r="I53" t="s">
         <v>25</v>
       </c>
       <c r="J53" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K53" t="s">
         <v>27</v>
@@ -3893,7 +3896,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -419,7 +419,7 @@
     <t xml:space="preserve">median-listing-price</t>
   </si>
   <si>
-    <t xml:space="preserve">Median price of for-sale residential listings on the market in a given month</t>
+    <t xml:space="preserve">Real median price of for-sale residential listings on the market in a given month</t>
   </si>
   <si>
     <t xml:space="preserve">Observed rental index</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">rent-index</t>
   </si>
   <si>
-    <t xml:space="preserve">Zillow observed rental index (ZORI), all homes</t>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
   </si>
   <si>
     <t xml:space="preserve">Zillow</t>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -179,442 +179,451 @@
     <t xml:space="preserve">$123k</t>
   </si>
   <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024M11</t>
   </si>
   <si>
     <t xml:space="preserve">2025M11</t>
   </si>
   <si>
+    <t xml:space="preserve">DMV-2026-02-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2025-02-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active residential for-sale listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active-listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential listing price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-listing-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real median price of for-sale residential listings on the market in a given month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">municipal-services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household Wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household-wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medicaid-enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State agency reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNAP participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snap-participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q1</t>
+  </si>
+  <si>
     <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-02-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active residential for-sale listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real median price of for-sale residential listings on the market in a given month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNAP participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snap-participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q1</t>
   </si>
   <si>
     <t xml:space="preserve">Near-prime consumers</t>
@@ -1396,16 +1405,16 @@
         <v>44</v>
       </c>
       <c r="N6" t="s">
+        <v>30</v>
+      </c>
+      <c r="O6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="s">
         <v>55</v>
-      </c>
-      <c r="O6" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1428,10 +1437,10 @@
         <v>51</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
@@ -1449,16 +1458,16 @@
         <v>44</v>
       </c>
       <c r="N7" t="s">
+        <v>30</v>
+      </c>
+      <c r="O7" t="s">
+        <v>31</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="s">
         <v>55</v>
-      </c>
-      <c r="O7" t="s">
-        <v>56</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1481,10 +1490,10 @@
         <v>51</v>
       </c>
       <c r="G8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
@@ -1502,42 +1511,42 @@
         <v>44</v>
       </c>
       <c r="N8" t="s">
+        <v>30</v>
+      </c>
+      <c r="O8" t="s">
+        <v>31</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="s">
         <v>55</v>
-      </c>
-      <c r="O8" t="s">
-        <v>56</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" t="s">
         <v>62</v>
       </c>
-      <c r="B9" t="s">
+      <c r="D9" t="s">
         <v>63</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" t="s">
-        <v>66</v>
       </c>
       <c r="F9" t="s">
         <v>51</v>
       </c>
       <c r="G9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
         <v>25</v>
@@ -1555,42 +1564,42 @@
         <v>44</v>
       </c>
       <c r="N9" t="s">
+        <v>30</v>
+      </c>
+      <c r="O9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="s">
         <v>55</v>
-      </c>
-      <c r="O9" t="s">
-        <v>56</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
         <v>68</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>69</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>70</v>
       </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>71</v>
-      </c>
-      <c r="G10" t="s">
-        <v>72</v>
-      </c>
-      <c r="H10" t="s">
-        <v>73</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
@@ -1617,33 +1626,33 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" t="s">
         <v>75</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>76</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>77</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>78</v>
-      </c>
-      <c r="G11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" t="s">
-        <v>80</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -1661,10 +1670,10 @@
         <v>44</v>
       </c>
       <c r="N11" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O11" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1675,22 +1684,22 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>76</v>
-      </c>
-      <c r="E12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F12" t="s">
-        <v>78</v>
       </c>
       <c r="G12" t="s">
         <v>82</v>
@@ -1714,10 +1723,10 @@
         <v>44</v>
       </c>
       <c r="N12" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O12" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1767,10 +1776,10 @@
         <v>94</v>
       </c>
       <c r="N13" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O13" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1820,10 +1829,10 @@
         <v>94</v>
       </c>
       <c r="N14" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O14" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1873,10 +1882,10 @@
         <v>94</v>
       </c>
       <c r="N15" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O15" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1926,10 +1935,10 @@
         <v>94</v>
       </c>
       <c r="N16" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O16" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1979,10 +1988,10 @@
         <v>94</v>
       </c>
       <c r="N17" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O17" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -2032,10 +2041,10 @@
         <v>94</v>
       </c>
       <c r="N18" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O18" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -2094,7 +2103,7 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20">
@@ -2147,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
@@ -2200,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22">
@@ -2253,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="Q22" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
@@ -2403,16 +2412,16 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="O25" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
@@ -2423,22 +2432,22 @@
         <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F26" t="s">
         <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="I26" t="s">
         <v>25</v>
@@ -2456,16 +2465,16 @@
         <v>29</v>
       </c>
       <c r="N26" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="O26" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
@@ -2476,22 +2485,22 @@
         <v>119</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E27" t="s">
+        <v>140</v>
+      </c>
+      <c r="F27" t="s">
+        <v>141</v>
+      </c>
+      <c r="G27" t="s">
         <v>138</v>
       </c>
-      <c r="F27" t="s">
+      <c r="H27" t="s">
         <v>139</v>
-      </c>
-      <c r="G27" t="s">
-        <v>136</v>
-      </c>
-      <c r="H27" t="s">
-        <v>137</v>
       </c>
       <c r="I27" t="s">
         <v>25</v>
@@ -2509,48 +2518,48 @@
         <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>30</v>
+        <v>133</v>
       </c>
       <c r="O27" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F28" t="s">
         <v>123</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="K28" t="s">
         <v>27</v>
@@ -2571,33 +2580,33 @@
         <v>0</v>
       </c>
       <c r="Q28" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E29" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" t="s">
         <v>149</v>
       </c>
-      <c r="G29" t="s">
-        <v>147</v>
-      </c>
       <c r="H29" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
@@ -2615,42 +2624,42 @@
         <v>94</v>
       </c>
       <c r="N29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F30" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
@@ -2668,57 +2677,57 @@
         <v>94</v>
       </c>
       <c r="N30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C31" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K31" t="s">
         <v>27</v>
       </c>
       <c r="L31" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N31" t="s">
         <v>30</v>
@@ -2730,33 +2739,33 @@
         <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D32" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="H32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
@@ -2774,42 +2783,42 @@
         <v>29</v>
       </c>
       <c r="N32" t="s">
+        <v>30</v>
+      </c>
+      <c r="O32" t="s">
+        <v>31</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="s">
         <v>55</v>
-      </c>
-      <c r="O32" t="s">
-        <v>56</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B33" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H33" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
@@ -2827,42 +2836,42 @@
         <v>29</v>
       </c>
       <c r="N33" t="s">
+        <v>30</v>
+      </c>
+      <c r="O33" t="s">
+        <v>31</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="s">
         <v>55</v>
-      </c>
-      <c r="O33" t="s">
-        <v>56</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C34" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D34" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E34" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="G34" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H34" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
@@ -2880,16 +2889,16 @@
         <v>29</v>
       </c>
       <c r="N34" t="s">
+        <v>30</v>
+      </c>
+      <c r="O34" t="s">
+        <v>31</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="s">
         <v>55</v>
-      </c>
-      <c r="O34" t="s">
-        <v>56</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="35">
@@ -2900,22 +2909,22 @@
         <v>85</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E35" t="s">
+        <v>182</v>
+      </c>
+      <c r="F35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s">
         <v>180</v>
       </c>
-      <c r="F35" t="s">
+      <c r="H35" t="s">
         <v>181</v>
-      </c>
-      <c r="G35" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" t="s">
-        <v>179</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
@@ -2933,42 +2942,42 @@
         <v>44</v>
       </c>
       <c r="N35" t="s">
+        <v>30</v>
+      </c>
+      <c r="O35" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="s">
         <v>55</v>
-      </c>
-      <c r="O35" t="s">
-        <v>56</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D36" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" t="s">
+        <v>189</v>
+      </c>
+      <c r="G36" t="s">
         <v>186</v>
       </c>
-      <c r="F36" t="s">
+      <c r="H36" t="s">
         <v>187</v>
-      </c>
-      <c r="G36" t="s">
-        <v>184</v>
-      </c>
-      <c r="H36" t="s">
-        <v>185</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
@@ -2986,10 +2995,10 @@
         <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O36" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
@@ -3000,28 +3009,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C37" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E37" t="s">
+        <v>194</v>
+      </c>
+      <c r="F37" t="s">
+        <v>189</v>
+      </c>
+      <c r="G37" t="s">
         <v>192</v>
       </c>
-      <c r="F37" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" t="s">
-        <v>190</v>
-      </c>
       <c r="H37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -3039,10 +3048,10 @@
         <v>29</v>
       </c>
       <c r="N37" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O37" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3053,28 +3062,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D38" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E38" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F38" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G38" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I38" t="s">
         <v>41</v>
@@ -3092,42 +3101,42 @@
         <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O38" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C39" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F39" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G39" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="H39" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I39" t="s">
         <v>41</v>
@@ -3145,42 +3154,42 @@
         <v>29</v>
       </c>
       <c r="N39" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D40" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E40" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F40" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="G40" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I40" t="s">
         <v>41</v>
@@ -3198,42 +3207,42 @@
         <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O40" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E41" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F41" t="s">
         <v>40</v>
       </c>
       <c r="G41" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H41" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="I41" t="s">
         <v>41</v>
@@ -3271,22 +3280,22 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D42" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E42" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F42" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G42" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="H42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="I42" t="s">
         <v>25</v>
@@ -3304,51 +3313,51 @@
         <v>94</v>
       </c>
       <c r="N42" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O42" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F43" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="H43" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I43" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J43" t="s">
         <v>26</v>
       </c>
       <c r="K43" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L43" t="s">
         <v>28</v>
@@ -3357,51 +3366,51 @@
         <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O43" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B44" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C44" t="s">
+        <v>225</v>
+      </c>
+      <c r="D44" t="s">
+        <v>226</v>
+      </c>
+      <c r="E44" t="s">
+        <v>227</v>
+      </c>
+      <c r="F44" t="s">
+        <v>221</v>
+      </c>
+      <c r="G44" t="s">
+        <v>228</v>
+      </c>
+      <c r="H44" t="s">
+        <v>229</v>
+      </c>
+      <c r="I44" t="s">
         <v>222</v>
-      </c>
-      <c r="D44" t="s">
-        <v>223</v>
-      </c>
-      <c r="E44" t="s">
-        <v>224</v>
-      </c>
-      <c r="F44" t="s">
-        <v>218</v>
-      </c>
-      <c r="G44" t="s">
-        <v>225</v>
-      </c>
-      <c r="H44" t="s">
-        <v>226</v>
-      </c>
-      <c r="I44" t="s">
-        <v>219</v>
       </c>
       <c r="J44" t="s">
         <v>126</v>
       </c>
       <c r="K44" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L44" t="s">
         <v>28</v>
@@ -3410,51 +3419,51 @@
         <v>29</v>
       </c>
       <c r="N44" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O44" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C45" t="s">
+        <v>225</v>
+      </c>
+      <c r="D45" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" t="s">
+        <v>227</v>
+      </c>
+      <c r="F45" t="s">
+        <v>221</v>
+      </c>
+      <c r="G45" t="s">
+        <v>230</v>
+      </c>
+      <c r="H45" t="s">
+        <v>231</v>
+      </c>
+      <c r="I45" t="s">
         <v>222</v>
-      </c>
-      <c r="D45" t="s">
-        <v>223</v>
-      </c>
-      <c r="E45" t="s">
-        <v>224</v>
-      </c>
-      <c r="F45" t="s">
-        <v>218</v>
-      </c>
-      <c r="G45" t="s">
-        <v>227</v>
-      </c>
-      <c r="H45" t="s">
-        <v>228</v>
-      </c>
-      <c r="I45" t="s">
-        <v>219</v>
       </c>
       <c r="J45" t="s">
         <v>126</v>
       </c>
       <c r="K45" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L45" t="s">
         <v>28</v>
@@ -3463,51 +3472,51 @@
         <v>29</v>
       </c>
       <c r="N45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O45" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" t="s">
+        <v>227</v>
+      </c>
+      <c r="F46" t="s">
+        <v>221</v>
+      </c>
+      <c r="G46" t="s">
+        <v>232</v>
+      </c>
+      <c r="H46" t="s">
+        <v>233</v>
+      </c>
+      <c r="I46" t="s">
         <v>222</v>
-      </c>
-      <c r="D46" t="s">
-        <v>223</v>
-      </c>
-      <c r="E46" t="s">
-        <v>224</v>
-      </c>
-      <c r="F46" t="s">
-        <v>218</v>
-      </c>
-      <c r="G46" t="s">
-        <v>229</v>
-      </c>
-      <c r="H46" t="s">
-        <v>230</v>
-      </c>
-      <c r="I46" t="s">
-        <v>219</v>
       </c>
       <c r="J46" t="s">
         <v>126</v>
       </c>
       <c r="K46" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L46" t="s">
         <v>28</v>
@@ -3516,51 +3525,51 @@
         <v>29</v>
       </c>
       <c r="N46" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O46" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C47" t="s">
+        <v>225</v>
+      </c>
+      <c r="D47" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" t="s">
+        <v>221</v>
+      </c>
+      <c r="G47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H47" t="s">
+        <v>235</v>
+      </c>
+      <c r="I47" t="s">
         <v>222</v>
-      </c>
-      <c r="D47" t="s">
-        <v>223</v>
-      </c>
-      <c r="E47" t="s">
-        <v>224</v>
-      </c>
-      <c r="F47" t="s">
-        <v>218</v>
-      </c>
-      <c r="G47" t="s">
-        <v>231</v>
-      </c>
-      <c r="H47" t="s">
-        <v>232</v>
-      </c>
-      <c r="I47" t="s">
-        <v>219</v>
       </c>
       <c r="J47" t="s">
         <v>126</v>
       </c>
       <c r="K47" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -3569,51 +3578,51 @@
         <v>29</v>
       </c>
       <c r="N47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B48" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C48" t="s">
+        <v>225</v>
+      </c>
+      <c r="D48" t="s">
+        <v>226</v>
+      </c>
+      <c r="E48" t="s">
+        <v>227</v>
+      </c>
+      <c r="F48" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48" t="s">
+        <v>236</v>
+      </c>
+      <c r="H48" t="s">
+        <v>237</v>
+      </c>
+      <c r="I48" t="s">
         <v>222</v>
-      </c>
-      <c r="D48" t="s">
-        <v>223</v>
-      </c>
-      <c r="E48" t="s">
-        <v>224</v>
-      </c>
-      <c r="F48" t="s">
-        <v>218</v>
-      </c>
-      <c r="G48" t="s">
-        <v>233</v>
-      </c>
-      <c r="H48" t="s">
-        <v>234</v>
-      </c>
-      <c r="I48" t="s">
-        <v>219</v>
       </c>
       <c r="J48" t="s">
         <v>126</v>
       </c>
       <c r="K48" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3622,51 +3631,51 @@
         <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O48" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C49" t="s">
+        <v>225</v>
+      </c>
+      <c r="D49" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" t="s">
+        <v>221</v>
+      </c>
+      <c r="G49" t="s">
+        <v>238</v>
+      </c>
+      <c r="H49" t="s">
+        <v>239</v>
+      </c>
+      <c r="I49" t="s">
         <v>222</v>
-      </c>
-      <c r="D49" t="s">
-        <v>223</v>
-      </c>
-      <c r="E49" t="s">
-        <v>224</v>
-      </c>
-      <c r="F49" t="s">
-        <v>218</v>
-      </c>
-      <c r="G49" t="s">
-        <v>235</v>
-      </c>
-      <c r="H49" t="s">
-        <v>236</v>
-      </c>
-      <c r="I49" t="s">
-        <v>219</v>
       </c>
       <c r="J49" t="s">
         <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
@@ -3675,51 +3684,51 @@
         <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O49" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C50" t="s">
+        <v>225</v>
+      </c>
+      <c r="D50" t="s">
+        <v>226</v>
+      </c>
+      <c r="E50" t="s">
+        <v>227</v>
+      </c>
+      <c r="F50" t="s">
+        <v>221</v>
+      </c>
+      <c r="G50" t="s">
+        <v>240</v>
+      </c>
+      <c r="H50" t="s">
+        <v>241</v>
+      </c>
+      <c r="I50" t="s">
         <v>222</v>
-      </c>
-      <c r="D50" t="s">
-        <v>223</v>
-      </c>
-      <c r="E50" t="s">
-        <v>224</v>
-      </c>
-      <c r="F50" t="s">
-        <v>218</v>
-      </c>
-      <c r="G50" t="s">
-        <v>237</v>
-      </c>
-      <c r="H50" t="s">
-        <v>238</v>
-      </c>
-      <c r="I50" t="s">
-        <v>219</v>
       </c>
       <c r="J50" t="s">
         <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3728,51 +3737,51 @@
         <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O50" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C51" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D51" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="E51" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F51" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="G51" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="H51" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="I51" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="J51" t="s">
         <v>126</v>
       </c>
       <c r="K51" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3781,42 +3790,42 @@
         <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O51" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C52" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D52" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E52" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F52" t="s">
+        <v>247</v>
+      </c>
+      <c r="G52" t="s">
         <v>244</v>
       </c>
-      <c r="G52" t="s">
-        <v>241</v>
-      </c>
       <c r="H52" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="I52" t="s">
         <v>25</v>
@@ -3834,10 +3843,10 @@
         <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O52" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
@@ -3854,28 +3863,28 @@
         <v>18</v>
       </c>
       <c r="C53" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D53" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="E53" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
+        <v>252</v>
+      </c>
+      <c r="G53" t="s">
         <v>249</v>
       </c>
-      <c r="G53" t="s">
-        <v>246</v>
-      </c>
       <c r="H53" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="I53" t="s">
         <v>25</v>
       </c>
       <c r="J53" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K53" t="s">
         <v>27</v>
@@ -3887,16 +3896,16 @@
         <v>29</v>
       </c>
       <c r="N53" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="O53" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
       <c r="Q53" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -1,784 +1,818 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHaskins\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53CD11E-EF5A-4A83-B920-062AEEE8582B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
-  <si>
-    <t xml:space="preserve">topic.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">topic.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metric.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metric.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metrics.definition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">metrics.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.interval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.change</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.notes.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.format.notes.key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.date_range.start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.date_range.end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level.map</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vintage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Economy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overall-economy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total nonfarm payroll jobs, measured at location of employment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-03-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal government jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-federal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 12-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-12-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-03-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="262">
+  <si>
+    <t>topic.name</t>
+  </si>
+  <si>
+    <t>topic.key</t>
+  </si>
+  <si>
+    <t>metric.name</t>
+  </si>
+  <si>
+    <t>metric.key</t>
+  </si>
+  <si>
+    <t>metrics.definition</t>
+  </si>
+  <si>
+    <t>metrics.source</t>
+  </si>
+  <si>
+    <t>level.name</t>
+  </si>
+  <si>
+    <t>level.key</t>
+  </si>
+  <si>
+    <t>level.interval</t>
+  </si>
+  <si>
+    <t>level.format.base</t>
+  </si>
+  <si>
+    <t>level.format.change</t>
+  </si>
+  <si>
+    <t>level.format.notes.name</t>
+  </si>
+  <si>
+    <t>level.format.notes.key</t>
+  </si>
+  <si>
+    <t>level.date_range.start</t>
+  </si>
+  <si>
+    <t>level.date_range.end</t>
+  </si>
+  <si>
+    <t>level.map</t>
+  </si>
+  <si>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>Overall Economy</t>
+  </si>
+  <si>
+    <t>overall-economy</t>
+  </si>
+  <si>
+    <t>Jobs</t>
+  </si>
+  <si>
+    <t>jobs</t>
+  </si>
+  <si>
+    <t>Total nonfarm payroll jobs, measured at location of employment</t>
+  </si>
+  <si>
+    <t>Lightcast and U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t>Total jobs</t>
+  </si>
+  <si>
+    <t>jobs-total</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>123k</t>
+  </si>
+  <si>
+    <t>pct</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>2024M12</t>
+  </si>
+  <si>
+    <t>2025M12</t>
+  </si>
+  <si>
+    <t>DMV-2026-03-03</t>
+  </si>
+  <si>
+    <t>Private sector jobs</t>
+  </si>
+  <si>
+    <t>jobs-private</t>
+  </si>
+  <si>
+    <t>Federal government jobs</t>
+  </si>
+  <si>
+    <t>jobs-federal</t>
+  </si>
+  <si>
+    <t>Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t>business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t>Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t>Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>0.[0]</t>
+  </si>
+  <si>
+    <t>Rolling 12-month total</t>
+  </si>
+  <si>
+    <t>rolling-12-sum</t>
+  </si>
+  <si>
+    <t>2024Q4</t>
+  </si>
+  <si>
+    <t>2025Q4</t>
+  </si>
+  <si>
+    <t>DMV-2026-03-04</t>
+  </si>
+  <si>
+    <t>Federal obligations</t>
+  </si>
+  <si>
+    <t>federal-obligations</t>
+  </si>
+  <si>
+    <t>Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t>USASpending</t>
+  </si>
+  <si>
+    <t>Federal obligations, total</t>
+  </si>
+  <si>
+    <t>federal-obligations-total</t>
+  </si>
+  <si>
+    <t>$123k</t>
+  </si>
+  <si>
+    <t>DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t>Federal obligations, grants</t>
+  </si>
+  <si>
+    <t>federal-obligations-grants</t>
+  </si>
+  <si>
+    <t>Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t>federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t>Innovation</t>
+  </si>
+  <si>
+    <t>innovation</t>
+  </si>
+  <si>
+    <t>Academic research funding</t>
+  </si>
+  <si>
+    <t>research-hd</t>
+  </si>
+  <si>
+    <t>Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t>Academic research funding obligated</t>
+  </si>
+  <si>
+    <t>Utility patents</t>
+  </si>
+  <si>
+    <t>patents</t>
+  </si>
+  <si>
+    <t>Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t>United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t>Utility patent applications filed</t>
+  </si>
+  <si>
+    <t>patents-filed</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-18</t>
+  </si>
+  <si>
+    <t>Venture capital</t>
+  </si>
+  <si>
+    <t>venture-capital</t>
+  </si>
+  <si>
+    <t>Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t>Crunchbase</t>
+  </si>
+  <si>
+    <t>Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t>venture-capital-volume</t>
+  </si>
+  <si>
+    <t>2024M11</t>
+  </si>
+  <si>
+    <t>2025M11</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-09</t>
+  </si>
+  <si>
+    <t>Venture capital deals</t>
+  </si>
+  <si>
+    <t>venture-capital-deals</t>
+  </si>
+  <si>
+    <t>Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t>labor-market</t>
+  </si>
+  <si>
+    <t>Unemployment rate</t>
+  </si>
+  <si>
+    <t>unempr-sa</t>
   </si>
   <si>
     <t xml:space="preserve">Percentage of labor force not currently employed  </t>
   </si>
   <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-02-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active residential for-sale listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of for-sale residential listings on the market in a given month, excluding those pending sale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real median price of for-sale residential listings on the market in a given month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
+    <t>Unemployment rate, total</t>
+  </si>
+  <si>
+    <t>unempr-sa-total</t>
+  </si>
+  <si>
+    <t>0.[00]%</t>
+  </si>
+  <si>
+    <t>pct_diff</t>
+  </si>
+  <si>
+    <t>Rolling 3-month average</t>
+  </si>
+  <si>
+    <t>rolling-3-mean</t>
+  </si>
+  <si>
+    <t>Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t>unempr-sa-white</t>
+  </si>
+  <si>
+    <t>Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t>unempr-sa-black</t>
+  </si>
+  <si>
+    <t>Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t>unempr-sa-poc</t>
+  </si>
+  <si>
+    <t>Unemployment rate, men</t>
+  </si>
+  <si>
+    <t>unempr-sa-male</t>
+  </si>
+  <si>
+    <t>Unemployment rate, female</t>
+  </si>
+  <si>
+    <t>unempr-sa-female</t>
+  </si>
+  <si>
+    <t>Job postings</t>
+  </si>
+  <si>
+    <t>unique-postings-fte</t>
+  </si>
+  <si>
+    <t>Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t>Lightcast</t>
+  </si>
+  <si>
+    <t>Total job postings, full-time</t>
+  </si>
+  <si>
+    <t>unique-postings-total</t>
+  </si>
+  <si>
+    <t>Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t>unique-postings-private</t>
+  </si>
+  <si>
+    <t>Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t>unique-postings-public</t>
+  </si>
+  <si>
+    <t>Internship postings</t>
+  </si>
+  <si>
+    <t>unique-postings-internships</t>
+  </si>
+  <si>
+    <t>Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t>real-estate</t>
+  </si>
+  <si>
+    <t>Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t>commercial-occupancy</t>
+  </si>
+  <si>
+    <t>Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t>CoStar</t>
+  </si>
+  <si>
+    <t>Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t>commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t>0.[0]%</t>
+  </si>
+  <si>
+    <t>Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t>commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t>Active residential for-sale listings</t>
+  </si>
+  <si>
+    <t>active-listings</t>
+  </si>
+  <si>
+    <t>2025M2</t>
+  </si>
+  <si>
+    <t>2026M2</t>
+  </si>
+  <si>
+    <t>Median residential listing price</t>
+  </si>
+  <si>
+    <t>median-listing-price</t>
+  </si>
+  <si>
+    <t>Observed rental index</t>
+  </si>
+  <si>
+    <t>rent-index</t>
+  </si>
+  <si>
+    <t>Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t>Zillow</t>
+  </si>
+  <si>
+    <t>Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t>destination-travel</t>
+  </si>
+  <si>
+    <t>Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t>hotel-revpar</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
   </si>
   <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNAP participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snap-participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-prime consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-nearprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severely credit-constrained consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-subprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">personal-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About the DMV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">about</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total-population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attainment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eduatt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less than high school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less-than-hs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school or equivalent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high-school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some college or associate's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some-college-aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bachelors-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduate or professional degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">graduate-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hs-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign-born</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+    <t>$0.[00]</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-27</t>
+  </si>
+  <si>
+    <t>Overnight visitors</t>
+  </si>
+  <si>
+    <t>overnight-visitors</t>
+  </si>
+  <si>
+    <t>DataFy</t>
+  </si>
+  <si>
+    <t>2024M9</t>
+  </si>
+  <si>
+    <t>2025M9</t>
+  </si>
+  <si>
+    <t>Visitor spending</t>
+  </si>
+  <si>
+    <t>visitor-spending</t>
+  </si>
+  <si>
+    <t>Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t>Visitor spending, total</t>
+  </si>
+  <si>
+    <t>visitor-spending-total</t>
+  </si>
+  <si>
+    <t>Municipal Services</t>
+  </si>
+  <si>
+    <t>municipal-services</t>
+  </si>
+  <si>
+    <t>Transit ridership</t>
+  </si>
+  <si>
+    <t>transit-ridership</t>
+  </si>
+  <si>
+    <t>Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t>U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t>Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t>transit-vrm</t>
+  </si>
+  <si>
+    <t>0.[00]</t>
+  </si>
+  <si>
+    <t>Rolling 3-month total</t>
+  </si>
+  <si>
+    <t>rolling-3-sum</t>
+  </si>
+  <si>
+    <t>Crime rate</t>
+  </si>
+  <si>
+    <t>crime-rate</t>
+  </si>
+  <si>
+    <t>Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t>Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t>Total, all major crimes</t>
+  </si>
+  <si>
+    <t>crime-rate-total</t>
+  </si>
+  <si>
+    <t>Violent crimes</t>
+  </si>
+  <si>
+    <t>crime-rate-violent</t>
+  </si>
+  <si>
+    <t>Property crimes</t>
+  </si>
+  <si>
+    <t>crime-rate-property</t>
+  </si>
+  <si>
+    <t>Mass layoff notifications</t>
+  </si>
+  <si>
+    <t>warn-notices</t>
+  </si>
+  <si>
+    <t>Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t>WarnTracker.com</t>
+  </si>
+  <si>
+    <t>Household Wellbeing</t>
+  </si>
+  <si>
+    <t>household-wellbeing</t>
+  </si>
+  <si>
+    <t>Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t>medicaid-enrollment</t>
+  </si>
+  <si>
+    <t>Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t>State agency reporting</t>
+  </si>
+  <si>
+    <t>2024M10</t>
+  </si>
+  <si>
+    <t>2025M10</t>
+  </si>
+  <si>
+    <t>SNAP participation</t>
+  </si>
+  <si>
+    <t>snap-participation</t>
+  </si>
+  <si>
+    <t>Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
+  </si>
+  <si>
+    <t>Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t>credit-constrained</t>
+  </si>
+  <si>
+    <t>Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t>Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t>Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t>credit-constrained-total</t>
+  </si>
+  <si>
+    <t>2024Q1</t>
+  </si>
+  <si>
+    <t>2025Q1</t>
+  </si>
+  <si>
+    <t>DMV-2025-12-11</t>
+  </si>
+  <si>
+    <t>Near-prime consumers</t>
+  </si>
+  <si>
+    <t>credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t>Severely credit-constrained consumers</t>
+  </si>
+  <si>
+    <t>credit-constrained-subprime</t>
+  </si>
+  <si>
+    <t>Personal bankruptcy rate</t>
+  </si>
+  <si>
+    <t>personal-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t>Non-business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t>Resident spending</t>
+  </si>
+  <si>
+    <t>resident-spending</t>
+  </si>
+  <si>
+    <t>Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t>Resident spending, total</t>
+  </si>
+  <si>
+    <t>resident-spending-total</t>
+  </si>
+  <si>
+    <t>About the DMV</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>Population</t>
+  </si>
+  <si>
+    <t>total-population</t>
+  </si>
+  <si>
+    <t>Total population</t>
+  </si>
+  <si>
+    <t>U.S. Census Bureau and Lightcast</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>2024A1</t>
+  </si>
+  <si>
+    <t>Educational attainment</t>
+  </si>
+  <si>
+    <t>eduatt</t>
+  </si>
+  <si>
+    <t>Educational attaintment for population aged 25 and older</t>
+  </si>
+  <si>
+    <t>Less than high school</t>
+  </si>
+  <si>
+    <t>less-than-hs</t>
+  </si>
+  <si>
+    <t>High school or equivalent</t>
+  </si>
+  <si>
+    <t>high-school</t>
+  </si>
+  <si>
+    <t>Some college or associate's degree</t>
+  </si>
+  <si>
+    <t>some-college-aa</t>
+  </si>
+  <si>
+    <t>Bachelor's degree</t>
+  </si>
+  <si>
+    <t>bachelors-degree</t>
+  </si>
+  <si>
+    <t>Graduate or professional degree</t>
+  </si>
+  <si>
+    <t>graduate-degree</t>
+  </si>
+  <si>
+    <t>High school degree or higher, total</t>
+  </si>
+  <si>
+    <t>hs-plus</t>
+  </si>
+  <si>
+    <t>Bachelor's degree or higher, total</t>
+  </si>
+  <si>
+    <t>ba-plus</t>
+  </si>
+  <si>
+    <t>Share of foreign-born population (%)</t>
+  </si>
+  <si>
+    <t>foreign-born</t>
+  </si>
+  <si>
+    <t>Total air passengers served</t>
+  </si>
+  <si>
+    <t>air-travel</t>
+  </si>
+  <si>
+    <t>Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t>U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t>air-passengers</t>
+  </si>
+  <si>
+    <t>Consumer prices</t>
+  </si>
+  <si>
+    <t>cpi-total</t>
+  </si>
+  <si>
+    <t>Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t>U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t>Median residential sale price</t>
+  </si>
+  <si>
+    <t>median-sale-price</t>
+  </si>
+  <si>
+    <t>Home sales</t>
+  </si>
+  <si>
+    <t>home-sales</t>
+  </si>
+  <si>
+    <t>Residential home sales</t>
+  </si>
+  <si>
+    <t>Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t>median-dom</t>
+  </si>
+  <si>
+    <t>list-to-sale-ratio</t>
+  </si>
+  <si>
+    <t>homes-sold-above-list</t>
+  </si>
+  <si>
+    <t>Median days on market</t>
+  </si>
+  <si>
+    <t>List-to-sale price ratio</t>
+  </si>
+  <si>
+    <t>Homes sold above list price (%)</t>
+  </si>
+  <si>
+    <t>DMV-2026-02-07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -814,6 +848,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1095,11 +1138,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q57"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1152,7 +1195,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1198,14 +1241,14 @@
       <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2">
         <v>1</v>
       </c>
       <c r="Q2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1251,14 +1294,14 @@
       <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3">
         <v>1</v>
       </c>
       <c r="Q3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1304,14 +1347,14 @@
       <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4">
         <v>1</v>
       </c>
       <c r="Q4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1357,14 +1400,14 @@
       <c r="O5" t="s">
         <v>46</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>1</v>
       </c>
       <c r="Q5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1410,14 +1453,14 @@
       <c r="O6" t="s">
         <v>31</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1463,14 +1506,14 @@
       <c r="O7" t="s">
         <v>31</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>1</v>
       </c>
       <c r="Q7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1516,14 +1559,14 @@
       <c r="O8" t="s">
         <v>31</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>1</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1569,14 +1612,14 @@
       <c r="O9" t="s">
         <v>31</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>1</v>
       </c>
       <c r="Q9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1622,14 +1665,14 @@
       <c r="O10" t="s">
         <v>31</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>1</v>
       </c>
       <c r="Q10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1675,14 +1718,14 @@
       <c r="O11" t="s">
         <v>80</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>1</v>
       </c>
       <c r="Q11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1728,14 +1771,14 @@
       <c r="O12" t="s">
         <v>80</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1781,14 +1824,14 @@
       <c r="O13" t="s">
         <v>80</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -1808,10 +1851,10 @@
         <v>22</v>
       </c>
       <c r="G14" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" t="s">
         <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>97</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
@@ -1834,14 +1877,14 @@
       <c r="O14" t="s">
         <v>80</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -1861,10 +1904,10 @@
         <v>22</v>
       </c>
       <c r="G15" t="s">
+        <v>97</v>
+      </c>
+      <c r="H15" t="s">
         <v>98</v>
-      </c>
-      <c r="H15" t="s">
-        <v>99</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
@@ -1887,14 +1930,14 @@
       <c r="O15" t="s">
         <v>80</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -1914,10 +1957,10 @@
         <v>22</v>
       </c>
       <c r="G16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" t="s">
         <v>100</v>
-      </c>
-      <c r="H16" t="s">
-        <v>101</v>
       </c>
       <c r="I16" t="s">
         <v>25</v>
@@ -1940,14 +1983,14 @@
       <c r="O16" t="s">
         <v>80</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -1967,10 +2010,10 @@
         <v>22</v>
       </c>
       <c r="G17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" t="s">
         <v>102</v>
-      </c>
-      <c r="H17" t="s">
-        <v>103</v>
       </c>
       <c r="I17" t="s">
         <v>25</v>
@@ -1993,14 +2036,14 @@
       <c r="O17" t="s">
         <v>80</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -2020,10 +2063,10 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" t="s">
         <v>104</v>
-      </c>
-      <c r="H18" t="s">
-        <v>105</v>
       </c>
       <c r="I18" t="s">
         <v>25</v>
@@ -2046,14 +2089,14 @@
       <c r="O18" t="s">
         <v>80</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2061,22 +2104,22 @@
         <v>85</v>
       </c>
       <c r="C19" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" t="s">
         <v>106</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>107</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>108</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>109</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>110</v>
-      </c>
-      <c r="H19" t="s">
-        <v>111</v>
       </c>
       <c r="I19" t="s">
         <v>25</v>
@@ -2099,14 +2142,14 @@
       <c r="O19" t="s">
         <v>31</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>1</v>
       </c>
       <c r="Q19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -2114,22 +2157,22 @@
         <v>85</v>
       </c>
       <c r="C20" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" t="s">
         <v>106</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>107</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>108</v>
       </c>
-      <c r="F20" t="s">
-        <v>109</v>
-      </c>
       <c r="G20" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" t="s">
         <v>112</v>
-      </c>
-      <c r="H20" t="s">
-        <v>113</v>
       </c>
       <c r="I20" t="s">
         <v>25</v>
@@ -2152,14 +2195,14 @@
       <c r="O20" t="s">
         <v>31</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20">
         <v>1</v>
       </c>
       <c r="Q20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -2167,22 +2210,22 @@
         <v>85</v>
       </c>
       <c r="C21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D21" t="s">
         <v>106</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>107</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>108</v>
       </c>
-      <c r="F21" t="s">
-        <v>109</v>
-      </c>
       <c r="G21" t="s">
+        <v>113</v>
+      </c>
+      <c r="H21" t="s">
         <v>114</v>
-      </c>
-      <c r="H21" t="s">
-        <v>115</v>
       </c>
       <c r="I21" t="s">
         <v>25</v>
@@ -2205,14 +2248,14 @@
       <c r="O21" t="s">
         <v>31</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21">
         <v>1</v>
       </c>
       <c r="Q21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -2220,22 +2263,22 @@
         <v>85</v>
       </c>
       <c r="C22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" t="s">
         <v>106</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>107</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>108</v>
       </c>
-      <c r="F22" t="s">
-        <v>109</v>
-      </c>
       <c r="G22" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" t="s">
         <v>116</v>
-      </c>
-      <c r="H22" t="s">
-        <v>117</v>
       </c>
       <c r="I22" t="s">
         <v>25</v>
@@ -2258,43 +2301,43 @@
       <c r="O22" t="s">
         <v>31</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>1</v>
       </c>
       <c r="Q22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" t="s">
         <v>118</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>119</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>120</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>121</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>122</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>123</v>
       </c>
-      <c r="G23" t="s">
+      <c r="H23" t="s">
         <v>124</v>
-      </c>
-      <c r="H23" t="s">
-        <v>125</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K23" t="s">
         <v>92</v>
@@ -2311,43 +2354,43 @@
       <c r="O23" t="s">
         <v>46</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" t="s">
         <v>118</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>119</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>120</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>121</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>122</v>
       </c>
-      <c r="F24" t="s">
-        <v>123</v>
-      </c>
       <c r="G24" t="s">
+        <v>126</v>
+      </c>
+      <c r="H24" t="s">
         <v>127</v>
-      </c>
-      <c r="H24" t="s">
-        <v>128</v>
       </c>
       <c r="I24" t="s">
         <v>41</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K24" t="s">
         <v>92</v>
@@ -2364,37 +2407,37 @@
       <c r="O24" t="s">
         <v>46</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>117</v>
+      </c>
+      <c r="B25" t="s">
         <v>118</v>
       </c>
-      <c r="B25" t="s">
-        <v>119</v>
-      </c>
       <c r="C25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D25" t="s">
+        <v>252</v>
+      </c>
+      <c r="E25" t="s">
+        <v>253</v>
+      </c>
+      <c r="F25" t="s">
+        <v>254</v>
+      </c>
+      <c r="G25" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" t="s">
         <v>129</v>
-      </c>
-      <c r="D25" t="s">
-        <v>130</v>
-      </c>
-      <c r="E25" t="s">
-        <v>131</v>
-      </c>
-      <c r="F25" t="s">
-        <v>132</v>
-      </c>
-      <c r="G25" t="s">
-        <v>129</v>
-      </c>
-      <c r="H25" t="s">
-        <v>130</v>
       </c>
       <c r="I25" t="s">
         <v>25</v>
@@ -2412,42 +2455,42 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O25" t="s">
-        <v>134</v>
-      </c>
-      <c r="P25" t="n">
+        <v>131</v>
+      </c>
+      <c r="P25">
         <v>1</v>
       </c>
       <c r="Q25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>117</v>
+      </c>
+      <c r="B26" t="s">
         <v>118</v>
       </c>
-      <c r="B26" t="s">
-        <v>119</v>
-      </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>251</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>252</v>
       </c>
       <c r="E26" t="s">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="F26" t="s">
+        <v>254</v>
+      </c>
+      <c r="G26" t="s">
         <v>132</v>
       </c>
-      <c r="G26" t="s">
-        <v>135</v>
-      </c>
       <c r="H26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I26" t="s">
         <v>25</v>
@@ -2465,42 +2508,42 @@
         <v>29</v>
       </c>
       <c r="N26" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O26" t="s">
-        <v>134</v>
-      </c>
-      <c r="P26" t="n">
+        <v>131</v>
+      </c>
+      <c r="P26">
         <v>1</v>
       </c>
       <c r="Q26" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
         <v>118</v>
       </c>
-      <c r="B27" t="s">
-        <v>119</v>
-      </c>
       <c r="C27" t="s">
-        <v>138</v>
+        <v>251</v>
       </c>
       <c r="D27" t="s">
-        <v>139</v>
+        <v>252</v>
       </c>
       <c r="E27" t="s">
-        <v>140</v>
+        <v>253</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>254</v>
       </c>
       <c r="G27" t="s">
-        <v>138</v>
+        <v>249</v>
       </c>
       <c r="H27" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
       <c r="I27" t="s">
         <v>25</v>
@@ -2518,48 +2561,48 @@
         <v>29</v>
       </c>
       <c r="N27" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="O27" t="s">
-        <v>134</v>
-      </c>
-      <c r="P27" t="n">
+        <v>131</v>
+      </c>
+      <c r="P27">
         <v>1</v>
       </c>
       <c r="Q27" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B28" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>251</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="E28" t="s">
-        <v>146</v>
+        <v>253</v>
       </c>
       <c r="F28" t="s">
-        <v>123</v>
+        <v>254</v>
       </c>
       <c r="G28" t="s">
-        <v>144</v>
+        <v>258</v>
       </c>
       <c r="H28" t="s">
-        <v>145</v>
+        <v>255</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="K28" t="s">
         <v>27</v>
@@ -2571,207 +2614,207 @@
         <v>29</v>
       </c>
       <c r="N28" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="O28" t="s">
-        <v>31</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
+        <v>131</v>
+      </c>
+      <c r="P28">
+        <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="E29" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="F29" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="G29" t="s">
-        <v>149</v>
+        <v>259</v>
       </c>
       <c r="H29" t="s">
-        <v>150</v>
+        <v>256</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L29" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="M29" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="O29" t="s">
-        <v>153</v>
-      </c>
-      <c r="P29" t="n">
+        <v>131</v>
+      </c>
+      <c r="P29">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B30" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>154</v>
+        <v>251</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="E30" t="s">
-        <v>156</v>
+        <v>253</v>
       </c>
       <c r="F30" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="G30" t="s">
-        <v>157</v>
+        <v>260</v>
       </c>
       <c r="H30" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L30" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="M30" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="O30" t="s">
-        <v>153</v>
-      </c>
-      <c r="P30" t="n">
+        <v>131</v>
+      </c>
+      <c r="P30">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="B31" t="s">
-        <v>160</v>
+        <v>118</v>
       </c>
       <c r="C31" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="D31" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="E31" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="F31" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="H31" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="K31" t="s">
         <v>27</v>
       </c>
       <c r="L31" t="s">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="M31" t="s">
-        <v>169</v>
+        <v>29</v>
       </c>
       <c r="N31" t="s">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="O31" t="s">
-        <v>31</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
+        <v>131</v>
+      </c>
+      <c r="P31">
+        <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="E32" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="F32" t="s">
-        <v>173</v>
+        <v>122</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="H32" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="K32" t="s">
         <v>27</v>
@@ -2788,158 +2831,158 @@
       <c r="O32" t="s">
         <v>31</v>
       </c>
-      <c r="P32" t="n">
-        <v>1</v>
+      <c r="P32">
+        <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="E33" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="F33" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="G33" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="H33" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K33" t="s">
         <v>27</v>
       </c>
       <c r="L33" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="M33" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="N33" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="O33" t="s">
-        <v>31</v>
-      </c>
-      <c r="P33" t="n">
+        <v>149</v>
+      </c>
+      <c r="P33">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="G34" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="H34" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
         <v>27</v>
       </c>
       <c r="L34" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="M34" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="N34" t="s">
-        <v>30</v>
+        <v>148</v>
       </c>
       <c r="O34" t="s">
-        <v>31</v>
-      </c>
-      <c r="P34" t="n">
+        <v>149</v>
+      </c>
+      <c r="P34">
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="D35" t="s">
-        <v>181</v>
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="F35" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="G35" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="H35" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="K35" t="s">
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
       <c r="M35" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -2947,43 +2990,43 @@
       <c r="O35" t="s">
         <v>31</v>
       </c>
-      <c r="P35" t="n">
-        <v>1</v>
+      <c r="P35">
+        <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="E36" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="F36" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G36" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="H36" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K36" t="s">
         <v>27</v>
@@ -2995,48 +3038,48 @@
         <v>29</v>
       </c>
       <c r="N36" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="O36" t="s">
-        <v>191</v>
-      </c>
-      <c r="P36" t="n">
+        <v>31</v>
+      </c>
+      <c r="P36">
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C37" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D37" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="F37" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="G37" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="H37" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
       </c>
       <c r="J37" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K37" t="s">
         <v>27</v>
@@ -3048,51 +3091,51 @@
         <v>29</v>
       </c>
       <c r="N37" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="O37" t="s">
-        <v>191</v>
-      </c>
-      <c r="P37" t="n">
+        <v>31</v>
+      </c>
+      <c r="P37">
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="B38" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="F38" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="G38" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="H38" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="I38" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="K38" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="L38" t="s">
         <v>28</v>
@@ -3101,104 +3144,104 @@
         <v>29</v>
       </c>
       <c r="N38" t="s">
-        <v>201</v>
+        <v>30</v>
       </c>
       <c r="O38" t="s">
-        <v>202</v>
-      </c>
-      <c r="P38" t="n">
+        <v>31</v>
+      </c>
+      <c r="P38">
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>176</v>
+      </c>
+      <c r="D39" t="s">
+        <v>177</v>
+      </c>
+      <c r="E39" t="s">
+        <v>178</v>
+      </c>
+      <c r="F39" t="s">
+        <v>179</v>
+      </c>
+      <c r="G39" t="s">
+        <v>176</v>
+      </c>
+      <c r="H39" t="s">
+        <v>177</v>
+      </c>
+      <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
+        <v>42</v>
+      </c>
+      <c r="K39" t="s">
+        <v>27</v>
+      </c>
+      <c r="L39" t="s">
+        <v>43</v>
+      </c>
+      <c r="M39" t="s">
+        <v>44</v>
+      </c>
+      <c r="N39" t="s">
+        <v>30</v>
+      </c>
+      <c r="O39" t="s">
+        <v>31</v>
+      </c>
+      <c r="P39">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>180</v>
+      </c>
+      <c r="B40" t="s">
+        <v>181</v>
+      </c>
+      <c r="C40" t="s">
+        <v>182</v>
+      </c>
+      <c r="D40" t="s">
+        <v>183</v>
+      </c>
+      <c r="E40" t="s">
         <v>184</v>
       </c>
-      <c r="B39" t="s">
+      <c r="F40" t="s">
         <v>185</v>
       </c>
-      <c r="C39" t="s">
-        <v>195</v>
-      </c>
-      <c r="D39" t="s">
-        <v>196</v>
-      </c>
-      <c r="E39" t="s">
-        <v>197</v>
-      </c>
-      <c r="F39" t="s">
-        <v>198</v>
-      </c>
-      <c r="G39" t="s">
-        <v>204</v>
-      </c>
-      <c r="H39" t="s">
-        <v>205</v>
-      </c>
-      <c r="I39" t="s">
-        <v>41</v>
-      </c>
-      <c r="J39" t="s">
-        <v>91</v>
-      </c>
-      <c r="K39" t="s">
-        <v>92</v>
-      </c>
-      <c r="L39" t="s">
-        <v>28</v>
-      </c>
-      <c r="M39" t="s">
-        <v>29</v>
-      </c>
-      <c r="N39" t="s">
-        <v>201</v>
-      </c>
-      <c r="O39" t="s">
-        <v>202</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B40" t="s">
-        <v>185</v>
-      </c>
-      <c r="C40" t="s">
-        <v>195</v>
-      </c>
-      <c r="D40" t="s">
-        <v>196</v>
-      </c>
-      <c r="E40" t="s">
-        <v>197</v>
-      </c>
-      <c r="F40" t="s">
-        <v>198</v>
-      </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="H40" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="I40" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="K40" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="L40" t="s">
         <v>28</v>
@@ -3207,157 +3250,157 @@
         <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="O40" t="s">
-        <v>202</v>
-      </c>
-      <c r="P40" t="n">
+        <v>187</v>
+      </c>
+      <c r="P40">
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s">
+        <v>181</v>
+      </c>
+      <c r="C41" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" t="s">
+        <v>189</v>
+      </c>
+      <c r="E41" t="s">
+        <v>190</v>
+      </c>
+      <c r="F41" t="s">
         <v>185</v>
       </c>
-      <c r="C41" t="s">
-        <v>208</v>
-      </c>
-      <c r="D41" t="s">
-        <v>209</v>
-      </c>
-      <c r="E41" t="s">
-        <v>210</v>
-      </c>
-      <c r="F41" t="s">
-        <v>40</v>
-      </c>
       <c r="G41" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="I41" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K41" t="s">
         <v>27</v>
       </c>
       <c r="L41" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M41" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="N41" t="s">
-        <v>45</v>
+        <v>186</v>
       </c>
       <c r="O41" t="s">
-        <v>46</v>
-      </c>
-      <c r="P41" t="n">
+        <v>187</v>
+      </c>
+      <c r="P41">
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>180</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>181</v>
       </c>
       <c r="C42" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="D42" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E42" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="F42" t="s">
-        <v>151</v>
+        <v>194</v>
       </c>
       <c r="G42" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="H42" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J42" t="s">
-        <v>54</v>
+        <v>91</v>
       </c>
       <c r="K42" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L42" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="M42" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="N42" t="s">
-        <v>152</v>
+        <v>197</v>
       </c>
       <c r="O42" t="s">
-        <v>153</v>
-      </c>
-      <c r="P42" t="n">
+        <v>198</v>
+      </c>
+      <c r="P42">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="43">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>216</v>
+        <v>180</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>181</v>
       </c>
       <c r="C43" t="s">
-        <v>218</v>
+        <v>191</v>
       </c>
       <c r="D43" t="s">
-        <v>219</v>
+        <v>192</v>
       </c>
       <c r="E43" t="s">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="F43" t="s">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="G43" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="H43" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="I43" t="s">
-        <v>222</v>
+        <v>41</v>
       </c>
       <c r="J43" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="L43" t="s">
         <v>28</v>
@@ -3366,51 +3409,51 @@
         <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="O43" t="s">
-        <v>224</v>
-      </c>
-      <c r="P43" t="n">
+        <v>198</v>
+      </c>
+      <c r="P43">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" t="s">
+        <v>192</v>
+      </c>
+      <c r="E44" t="s">
+        <v>193</v>
+      </c>
+      <c r="F44" t="s">
+        <v>194</v>
+      </c>
+      <c r="G44" t="s">
+        <v>202</v>
+      </c>
+      <c r="H44" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>216</v>
-      </c>
-      <c r="B44" t="s">
-        <v>217</v>
-      </c>
-      <c r="C44" t="s">
-        <v>225</v>
-      </c>
-      <c r="D44" t="s">
-        <v>226</v>
-      </c>
-      <c r="E44" t="s">
-        <v>227</v>
-      </c>
-      <c r="F44" t="s">
-        <v>221</v>
-      </c>
-      <c r="G44" t="s">
-        <v>228</v>
-      </c>
-      <c r="H44" t="s">
-        <v>229</v>
-      </c>
       <c r="I44" t="s">
-        <v>222</v>
+        <v>41</v>
       </c>
       <c r="J44" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="L44" t="s">
         <v>28</v>
@@ -3419,157 +3462,157 @@
         <v>29</v>
       </c>
       <c r="N44" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="O44" t="s">
-        <v>224</v>
-      </c>
-      <c r="P44" t="n">
+        <v>198</v>
+      </c>
+      <c r="P44">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>180</v>
+      </c>
+      <c r="B45" t="s">
+        <v>181</v>
+      </c>
+      <c r="C45" t="s">
+        <v>204</v>
+      </c>
+      <c r="D45" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" t="s">
+        <v>40</v>
+      </c>
+      <c r="G45" t="s">
+        <v>204</v>
+      </c>
+      <c r="H45" t="s">
+        <v>205</v>
+      </c>
+      <c r="I45" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" t="s">
+        <v>42</v>
+      </c>
+      <c r="K45" t="s">
+        <v>27</v>
+      </c>
+      <c r="L45" t="s">
+        <v>43</v>
+      </c>
+      <c r="M45" t="s">
+        <v>44</v>
+      </c>
+      <c r="N45" t="s">
+        <v>45</v>
+      </c>
+      <c r="O45" t="s">
+        <v>46</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>207</v>
+      </c>
+      <c r="D46" t="s">
+        <v>208</v>
+      </c>
+      <c r="E46" t="s">
+        <v>209</v>
+      </c>
+      <c r="F46" t="s">
+        <v>147</v>
+      </c>
+      <c r="G46" t="s">
+        <v>210</v>
+      </c>
+      <c r="H46" t="s">
+        <v>211</v>
+      </c>
+      <c r="I46" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" t="s">
+        <v>54</v>
+      </c>
+      <c r="K46" t="s">
+        <v>27</v>
+      </c>
+      <c r="L46" t="s">
+        <v>93</v>
+      </c>
+      <c r="M46" t="s">
+        <v>94</v>
+      </c>
+      <c r="N46" t="s">
+        <v>148</v>
+      </c>
+      <c r="O46" t="s">
+        <v>149</v>
+      </c>
+      <c r="P46">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" t="s">
+        <v>213</v>
+      </c>
+      <c r="C47" t="s">
+        <v>214</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
         <v>216</v>
       </c>
-      <c r="B45" t="s">
+      <c r="F47" t="s">
         <v>217</v>
       </c>
-      <c r="C45" t="s">
-        <v>225</v>
-      </c>
-      <c r="D45" t="s">
-        <v>226</v>
-      </c>
-      <c r="E45" t="s">
-        <v>227</v>
-      </c>
-      <c r="F45" t="s">
-        <v>221</v>
-      </c>
-      <c r="G45" t="s">
-        <v>230</v>
-      </c>
-      <c r="H45" t="s">
-        <v>231</v>
-      </c>
-      <c r="I45" t="s">
-        <v>222</v>
-      </c>
-      <c r="J45" t="s">
-        <v>126</v>
-      </c>
-      <c r="K45" t="s">
-        <v>223</v>
-      </c>
-      <c r="L45" t="s">
-        <v>28</v>
-      </c>
-      <c r="M45" t="s">
-        <v>29</v>
-      </c>
-      <c r="N45" t="s">
-        <v>224</v>
-      </c>
-      <c r="O45" t="s">
-        <v>224</v>
-      </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
+      <c r="G47" t="s">
         <v>216</v>
       </c>
-      <c r="B46" t="s">
-        <v>217</v>
-      </c>
-      <c r="C46" t="s">
-        <v>225</v>
-      </c>
-      <c r="D46" t="s">
-        <v>226</v>
-      </c>
-      <c r="E46" t="s">
-        <v>227</v>
-      </c>
-      <c r="F46" t="s">
-        <v>221</v>
-      </c>
-      <c r="G46" t="s">
-        <v>232</v>
-      </c>
-      <c r="H46" t="s">
-        <v>233</v>
-      </c>
-      <c r="I46" t="s">
-        <v>222</v>
-      </c>
-      <c r="J46" t="s">
-        <v>126</v>
-      </c>
-      <c r="K46" t="s">
-        <v>223</v>
-      </c>
-      <c r="L46" t="s">
-        <v>28</v>
-      </c>
-      <c r="M46" t="s">
-        <v>29</v>
-      </c>
-      <c r="N46" t="s">
-        <v>224</v>
-      </c>
-      <c r="O46" t="s">
-        <v>224</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>216</v>
-      </c>
-      <c r="B47" t="s">
-        <v>217</v>
-      </c>
-      <c r="C47" t="s">
-        <v>225</v>
-      </c>
-      <c r="D47" t="s">
-        <v>226</v>
-      </c>
-      <c r="E47" t="s">
-        <v>227</v>
-      </c>
-      <c r="F47" t="s">
-        <v>221</v>
-      </c>
-      <c r="G47" t="s">
-        <v>234</v>
-      </c>
       <c r="H47" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="I47" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J47" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="K47" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -3578,51 +3621,51 @@
         <v>29</v>
       </c>
       <c r="N47" t="s">
+        <v>220</v>
+      </c>
+      <c r="O47" t="s">
+        <v>220</v>
+      </c>
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>212</v>
+      </c>
+      <c r="B48" t="s">
+        <v>213</v>
+      </c>
+      <c r="C48" t="s">
+        <v>221</v>
+      </c>
+      <c r="D48" t="s">
+        <v>222</v>
+      </c>
+      <c r="E48" t="s">
+        <v>223</v>
+      </c>
+      <c r="F48" t="s">
+        <v>217</v>
+      </c>
+      <c r="G48" t="s">
         <v>224</v>
       </c>
-      <c r="O47" t="s">
-        <v>224</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>216</v>
-      </c>
-      <c r="B48" t="s">
-        <v>217</v>
-      </c>
-      <c r="C48" t="s">
+      <c r="H48" t="s">
         <v>225</v>
       </c>
-      <c r="D48" t="s">
-        <v>226</v>
-      </c>
-      <c r="E48" t="s">
-        <v>227</v>
-      </c>
-      <c r="F48" t="s">
-        <v>221</v>
-      </c>
-      <c r="G48" t="s">
-        <v>236</v>
-      </c>
-      <c r="H48" t="s">
-        <v>237</v>
-      </c>
       <c r="I48" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J48" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K48" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3631,51 +3674,51 @@
         <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O48" t="s">
-        <v>224</v>
-      </c>
-      <c r="P48" t="n">
+        <v>220</v>
+      </c>
+      <c r="P48">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B49" t="s">
+        <v>213</v>
+      </c>
+      <c r="C49" t="s">
+        <v>221</v>
+      </c>
+      <c r="D49" t="s">
+        <v>222</v>
+      </c>
+      <c r="E49" t="s">
+        <v>223</v>
+      </c>
+      <c r="F49" t="s">
         <v>217</v>
       </c>
-      <c r="C49" t="s">
-        <v>225</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="G49" t="s">
         <v>226</v>
       </c>
-      <c r="E49" t="s">
+      <c r="H49" t="s">
         <v>227</v>
       </c>
-      <c r="F49" t="s">
-        <v>221</v>
-      </c>
-      <c r="G49" t="s">
-        <v>238</v>
-      </c>
-      <c r="H49" t="s">
-        <v>239</v>
-      </c>
       <c r="I49" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K49" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
@@ -3684,51 +3727,51 @@
         <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O49" t="s">
-        <v>224</v>
-      </c>
-      <c r="P49" t="n">
+        <v>220</v>
+      </c>
+      <c r="P49">
         <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s">
+        <v>213</v>
+      </c>
+      <c r="C50" t="s">
+        <v>221</v>
+      </c>
+      <c r="D50" t="s">
+        <v>222</v>
+      </c>
+      <c r="E50" t="s">
+        <v>223</v>
+      </c>
+      <c r="F50" t="s">
         <v>217</v>
       </c>
-      <c r="C50" t="s">
-        <v>225</v>
-      </c>
-      <c r="D50" t="s">
-        <v>226</v>
-      </c>
-      <c r="E50" t="s">
-        <v>227</v>
-      </c>
-      <c r="F50" t="s">
-        <v>221</v>
-      </c>
       <c r="G50" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H50" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="I50" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J50" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K50" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3737,51 +3780,51 @@
         <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O50" t="s">
-        <v>224</v>
-      </c>
-      <c r="P50" t="n">
+        <v>220</v>
+      </c>
+      <c r="P50">
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B51" t="s">
+        <v>213</v>
+      </c>
+      <c r="C51" t="s">
+        <v>221</v>
+      </c>
+      <c r="D51" t="s">
+        <v>222</v>
+      </c>
+      <c r="E51" t="s">
+        <v>223</v>
+      </c>
+      <c r="F51" t="s">
         <v>217</v>
       </c>
-      <c r="C51" t="s">
+      <c r="G51" t="s">
+        <v>230</v>
+      </c>
+      <c r="H51" t="s">
+        <v>231</v>
+      </c>
+      <c r="I51" t="s">
         <v>218</v>
       </c>
-      <c r="D51" t="s">
+      <c r="J51" t="s">
+        <v>125</v>
+      </c>
+      <c r="K51" t="s">
         <v>219</v>
-      </c>
-      <c r="E51" t="s">
-        <v>220</v>
-      </c>
-      <c r="F51" t="s">
-        <v>221</v>
-      </c>
-      <c r="G51" t="s">
-        <v>242</v>
-      </c>
-      <c r="H51" t="s">
-        <v>243</v>
-      </c>
-      <c r="I51" t="s">
-        <v>222</v>
-      </c>
-      <c r="J51" t="s">
-        <v>126</v>
-      </c>
-      <c r="K51" t="s">
-        <v>223</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3790,51 +3833,51 @@
         <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="O51" t="s">
-        <v>224</v>
-      </c>
-      <c r="P51" t="n">
+        <v>220</v>
+      </c>
+      <c r="P51">
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>142</v>
+        <v>212</v>
       </c>
       <c r="B52" t="s">
-        <v>143</v>
+        <v>213</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="D52" t="s">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="E52" t="s">
-        <v>246</v>
+        <v>223</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>217</v>
       </c>
       <c r="G52" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="H52" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>218</v>
       </c>
       <c r="J52" t="s">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="K52" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="L52" t="s">
         <v>28</v>
@@ -3843,51 +3886,51 @@
         <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>190</v>
+        <v>220</v>
       </c>
       <c r="O52" t="s">
-        <v>191</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="P52">
+        <v>1</v>
       </c>
       <c r="Q52" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>17</v>
+        <v>212</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>213</v>
       </c>
       <c r="C53" t="s">
-        <v>249</v>
+        <v>221</v>
       </c>
       <c r="D53" t="s">
-        <v>250</v>
+        <v>222</v>
       </c>
       <c r="E53" t="s">
-        <v>251</v>
+        <v>223</v>
       </c>
       <c r="F53" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="G53" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H53" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="I53" t="s">
-        <v>25</v>
+        <v>218</v>
       </c>
       <c r="J53" t="s">
-        <v>167</v>
+        <v>125</v>
       </c>
       <c r="K53" t="s">
-        <v>27</v>
+        <v>219</v>
       </c>
       <c r="L53" t="s">
         <v>28</v>
@@ -3896,20 +3939,238 @@
         <v>29</v>
       </c>
       <c r="N53" t="s">
+        <v>220</v>
+      </c>
+      <c r="O53" t="s">
+        <v>220</v>
+      </c>
+      <c r="P53">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" t="s">
+        <v>213</v>
+      </c>
+      <c r="C54" t="s">
+        <v>221</v>
+      </c>
+      <c r="D54" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" t="s">
+        <v>223</v>
+      </c>
+      <c r="F54" t="s">
+        <v>217</v>
+      </c>
+      <c r="G54" t="s">
+        <v>236</v>
+      </c>
+      <c r="H54" t="s">
+        <v>237</v>
+      </c>
+      <c r="I54" t="s">
+        <v>218</v>
+      </c>
+      <c r="J54" t="s">
+        <v>125</v>
+      </c>
+      <c r="K54" t="s">
+        <v>219</v>
+      </c>
+      <c r="L54" t="s">
+        <v>28</v>
+      </c>
+      <c r="M54" t="s">
+        <v>29</v>
+      </c>
+      <c r="N54" t="s">
+        <v>220</v>
+      </c>
+      <c r="O54" t="s">
+        <v>220</v>
+      </c>
+      <c r="P54">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>212</v>
+      </c>
+      <c r="B55" t="s">
+        <v>213</v>
+      </c>
+      <c r="C55" t="s">
+        <v>214</v>
+      </c>
+      <c r="D55" t="s">
+        <v>215</v>
+      </c>
+      <c r="E55" t="s">
+        <v>216</v>
+      </c>
+      <c r="F55" t="s">
+        <v>217</v>
+      </c>
+      <c r="G55" t="s">
+        <v>238</v>
+      </c>
+      <c r="H55" t="s">
+        <v>239</v>
+      </c>
+      <c r="I55" t="s">
+        <v>218</v>
+      </c>
+      <c r="J55" t="s">
+        <v>125</v>
+      </c>
+      <c r="K55" t="s">
+        <v>219</v>
+      </c>
+      <c r="L55" t="s">
+        <v>28</v>
+      </c>
+      <c r="M55" t="s">
+        <v>29</v>
+      </c>
+      <c r="N55" t="s">
+        <v>220</v>
+      </c>
+      <c r="O55" t="s">
+        <v>220</v>
+      </c>
+      <c r="P55">
+        <v>1</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" t="s">
+        <v>240</v>
+      </c>
+      <c r="D56" t="s">
+        <v>241</v>
+      </c>
+      <c r="E56" t="s">
+        <v>242</v>
+      </c>
+      <c r="F56" t="s">
+        <v>243</v>
+      </c>
+      <c r="G56" t="s">
+        <v>240</v>
+      </c>
+      <c r="H56" t="s">
+        <v>244</v>
+      </c>
+      <c r="I56" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" t="s">
+        <v>26</v>
+      </c>
+      <c r="K56" t="s">
+        <v>27</v>
+      </c>
+      <c r="L56" t="s">
+        <v>28</v>
+      </c>
+      <c r="M56" t="s">
+        <v>29</v>
+      </c>
+      <c r="N56" t="s">
+        <v>186</v>
+      </c>
+      <c r="O56" t="s">
+        <v>187</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57" t="s">
+        <v>246</v>
+      </c>
+      <c r="E57" t="s">
+        <v>247</v>
+      </c>
+      <c r="F57" t="s">
+        <v>248</v>
+      </c>
+      <c r="G57" t="s">
+        <v>245</v>
+      </c>
+      <c r="H57" t="s">
+        <v>246</v>
+      </c>
+      <c r="I57" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" t="s">
+        <v>163</v>
+      </c>
+      <c r="K57" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" t="s">
+        <v>29</v>
+      </c>
+      <c r="N57" t="s">
         <v>79</v>
       </c>
-      <c r="O53" t="s">
+      <c r="O57" t="s">
         <v>80</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P57">
         <v>0</v>
       </c>
-      <c r="Q53" t="s">
-        <v>148</v>
+      <c r="Q57" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a6274e99-f707-4183-90a3-28f81526dfab}" enabled="1" method="Standard" siteId="{0a02388e-6178-4513-9b82-88b9dc6bf457}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -1,818 +1,808 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GHaskins\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53CD11E-EF5A-4A83-B920-062AEEE8582B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="913" uniqueCount="262">
-  <si>
-    <t>topic.name</t>
-  </si>
-  <si>
-    <t>topic.key</t>
-  </si>
-  <si>
-    <t>metric.name</t>
-  </si>
-  <si>
-    <t>metric.key</t>
-  </si>
-  <si>
-    <t>metrics.definition</t>
-  </si>
-  <si>
-    <t>metrics.source</t>
-  </si>
-  <si>
-    <t>level.name</t>
-  </si>
-  <si>
-    <t>level.key</t>
-  </si>
-  <si>
-    <t>level.interval</t>
-  </si>
-  <si>
-    <t>level.format.base</t>
-  </si>
-  <si>
-    <t>level.format.change</t>
-  </si>
-  <si>
-    <t>level.format.notes.name</t>
-  </si>
-  <si>
-    <t>level.format.notes.key</t>
-  </si>
-  <si>
-    <t>level.date_range.start</t>
-  </si>
-  <si>
-    <t>level.date_range.end</t>
-  </si>
-  <si>
-    <t>level.map</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>Overall Economy</t>
-  </si>
-  <si>
-    <t>overall-economy</t>
-  </si>
-  <si>
-    <t>Jobs</t>
-  </si>
-  <si>
-    <t>jobs</t>
-  </si>
-  <si>
-    <t>Total nonfarm payroll jobs, measured at location of employment</t>
-  </si>
-  <si>
-    <t>Lightcast and U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t>Total jobs</t>
-  </si>
-  <si>
-    <t>jobs-total</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>123k</t>
-  </si>
-  <si>
-    <t>pct</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>2024M12</t>
-  </si>
-  <si>
-    <t>2025M12</t>
-  </si>
-  <si>
-    <t>DMV-2026-03-03</t>
-  </si>
-  <si>
-    <t>Private sector jobs</t>
-  </si>
-  <si>
-    <t>jobs-private</t>
-  </si>
-  <si>
-    <t>Federal government jobs</t>
-  </si>
-  <si>
-    <t>jobs-federal</t>
-  </si>
-  <si>
-    <t>Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t>business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t>Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t>Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t>Q</t>
-  </si>
-  <si>
-    <t>0.[0]</t>
-  </si>
-  <si>
-    <t>Rolling 12-month total</t>
-  </si>
-  <si>
-    <t>rolling-12-sum</t>
-  </si>
-  <si>
-    <t>2024Q4</t>
-  </si>
-  <si>
-    <t>2025Q4</t>
-  </si>
-  <si>
-    <t>DMV-2026-03-04</t>
-  </si>
-  <si>
-    <t>Federal obligations</t>
-  </si>
-  <si>
-    <t>federal-obligations</t>
-  </si>
-  <si>
-    <t>Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t>USASpending</t>
-  </si>
-  <si>
-    <t>Federal obligations, total</t>
-  </si>
-  <si>
-    <t>federal-obligations-total</t>
-  </si>
-  <si>
-    <t>$123k</t>
-  </si>
-  <si>
-    <t>DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t>Federal obligations, grants</t>
-  </si>
-  <si>
-    <t>federal-obligations-grants</t>
-  </si>
-  <si>
-    <t>Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t>federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t>Innovation</t>
-  </si>
-  <si>
-    <t>innovation</t>
-  </si>
-  <si>
-    <t>Academic research funding</t>
-  </si>
-  <si>
-    <t>research-hd</t>
-  </si>
-  <si>
-    <t>Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t>Academic research funding obligated</t>
-  </si>
-  <si>
-    <t>Utility patents</t>
-  </si>
-  <si>
-    <t>patents</t>
-  </si>
-  <si>
-    <t>Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t>United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t>Utility patent applications filed</t>
-  </si>
-  <si>
-    <t>patents-filed</t>
-  </si>
-  <si>
-    <t>DMV-2026-02-18</t>
-  </si>
-  <si>
-    <t>Venture capital</t>
-  </si>
-  <si>
-    <t>venture-capital</t>
-  </si>
-  <si>
-    <t>Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t>Crunchbase</t>
-  </si>
-  <si>
-    <t>Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t>venture-capital-volume</t>
-  </si>
-  <si>
-    <t>2024M11</t>
-  </si>
-  <si>
-    <t>2025M11</t>
-  </si>
-  <si>
-    <t>DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t>Venture capital deals</t>
-  </si>
-  <si>
-    <t>venture-capital-deals</t>
-  </si>
-  <si>
-    <t>Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t>labor-market</t>
-  </si>
-  <si>
-    <t>Unemployment rate</t>
-  </si>
-  <si>
-    <t>unempr-sa</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+  <si>
+    <t xml:space="preserve">topic.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">topic.key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metric.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metric.key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metrics.definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">metrics.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.interval</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.format.base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.format.change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.format.notes.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.format.notes.key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.date_range.start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.date_range.end</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vintage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Economy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overall-economy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total nonfarm payroll jobs, measured at location of employment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 12-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-12-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-03-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USASpending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
   </si>
   <si>
     <t xml:space="preserve">Percentage of labor force not currently employed  </t>
   </si>
   <si>
-    <t>Unemployment rate, total</t>
-  </si>
-  <si>
-    <t>unempr-sa-total</t>
-  </si>
-  <si>
-    <t>0.[00]%</t>
-  </si>
-  <si>
-    <t>pct_diff</t>
-  </si>
-  <si>
-    <t>Rolling 3-month average</t>
-  </si>
-  <si>
-    <t>rolling-3-mean</t>
-  </si>
-  <si>
-    <t>Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t>unempr-sa-white</t>
-  </si>
-  <si>
-    <t>Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t>unempr-sa-black</t>
-  </si>
-  <si>
-    <t>Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t>unempr-sa-poc</t>
-  </si>
-  <si>
-    <t>Unemployment rate, men</t>
-  </si>
-  <si>
-    <t>unempr-sa-male</t>
-  </si>
-  <si>
-    <t>Unemployment rate, female</t>
-  </si>
-  <si>
-    <t>unempr-sa-female</t>
-  </si>
-  <si>
-    <t>Job postings</t>
-  </si>
-  <si>
-    <t>unique-postings-fte</t>
-  </si>
-  <si>
-    <t>Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t>Lightcast</t>
-  </si>
-  <si>
-    <t>Total job postings, full-time</t>
-  </si>
-  <si>
-    <t>unique-postings-total</t>
-  </si>
-  <si>
-    <t>Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t>unique-postings-private</t>
-  </si>
-  <si>
-    <t>Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t>unique-postings-public</t>
-  </si>
-  <si>
-    <t>Internship postings</t>
-  </si>
-  <si>
-    <t>unique-postings-internships</t>
-  </si>
-  <si>
-    <t>Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t>real-estate</t>
-  </si>
-  <si>
-    <t>Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t>commercial-occupancy</t>
-  </si>
-  <si>
-    <t>Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t>CoStar</t>
-  </si>
-  <si>
-    <t>Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t>commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t>0.[0]%</t>
-  </si>
-  <si>
-    <t>Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t>commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t>Active residential for-sale listings</t>
-  </si>
-  <si>
-    <t>active-listings</t>
-  </si>
-  <si>
-    <t>2025M2</t>
-  </si>
-  <si>
-    <t>2026M2</t>
-  </si>
-  <si>
-    <t>Median residential listing price</t>
-  </si>
-  <si>
-    <t>median-listing-price</t>
-  </si>
-  <si>
-    <t>Observed rental index</t>
-  </si>
-  <si>
-    <t>rent-index</t>
-  </si>
-  <si>
-    <t>Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t>Zillow</t>
-  </si>
-  <si>
-    <t>Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t>destination-travel</t>
-  </si>
-  <si>
-    <t>Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t>hotel-revpar</t>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active residential for-sale listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active-listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential sale price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-sale-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median days on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-dom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List-to-sale price ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list-to-sale-ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homes sold above list price (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homes-sold-above-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
   </si>
   <si>
     <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
   </si>
   <si>
-    <t>$0.[00]</t>
-  </si>
-  <si>
-    <t>DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t>Overnight visitors</t>
-  </si>
-  <si>
-    <t>overnight-visitors</t>
-  </si>
-  <si>
-    <t>DataFy</t>
-  </si>
-  <si>
-    <t>2024M9</t>
-  </si>
-  <si>
-    <t>2025M9</t>
-  </si>
-  <si>
-    <t>Visitor spending</t>
-  </si>
-  <si>
-    <t>visitor-spending</t>
-  </si>
-  <si>
-    <t>Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t>Visitor spending, total</t>
-  </si>
-  <si>
-    <t>visitor-spending-total</t>
-  </si>
-  <si>
-    <t>Municipal Services</t>
-  </si>
-  <si>
-    <t>municipal-services</t>
-  </si>
-  <si>
-    <t>Transit ridership</t>
-  </si>
-  <si>
-    <t>transit-ridership</t>
-  </si>
-  <si>
-    <t>Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t>U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t>Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t>transit-vrm</t>
-  </si>
-  <si>
-    <t>0.[00]</t>
-  </si>
-  <si>
-    <t>Rolling 3-month total</t>
-  </si>
-  <si>
-    <t>rolling-3-sum</t>
-  </si>
-  <si>
-    <t>Crime rate</t>
-  </si>
-  <si>
-    <t>crime-rate</t>
-  </si>
-  <si>
-    <t>Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t>Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t>Total, all major crimes</t>
-  </si>
-  <si>
-    <t>crime-rate-total</t>
-  </si>
-  <si>
-    <t>Violent crimes</t>
-  </si>
-  <si>
-    <t>crime-rate-violent</t>
-  </si>
-  <si>
-    <t>Property crimes</t>
-  </si>
-  <si>
-    <t>crime-rate-property</t>
-  </si>
-  <si>
-    <t>Mass layoff notifications</t>
-  </si>
-  <si>
-    <t>warn-notices</t>
-  </si>
-  <si>
-    <t>Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t>WarnTracker.com</t>
-  </si>
-  <si>
-    <t>Household Wellbeing</t>
-  </si>
-  <si>
-    <t>household-wellbeing</t>
-  </si>
-  <si>
-    <t>Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t>medicaid-enrollment</t>
-  </si>
-  <si>
-    <t>Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t>State agency reporting</t>
-  </si>
-  <si>
-    <t>2024M10</t>
-  </si>
-  <si>
-    <t>2025M10</t>
-  </si>
-  <si>
-    <t>SNAP participation</t>
-  </si>
-  <si>
-    <t>snap-participation</t>
-  </si>
-  <si>
-    <t>Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
-  </si>
-  <si>
-    <t>Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t>credit-constrained</t>
-  </si>
-  <si>
-    <t>Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t>Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t>Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t>credit-constrained-total</t>
-  </si>
-  <si>
-    <t>2024Q1</t>
-  </si>
-  <si>
-    <t>2025Q1</t>
-  </si>
-  <si>
-    <t>DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t>Near-prime consumers</t>
-  </si>
-  <si>
-    <t>credit-constrained-nearprime</t>
-  </si>
-  <si>
-    <t>Severely credit-constrained consumers</t>
-  </si>
-  <si>
-    <t>credit-constrained-subprime</t>
-  </si>
-  <si>
-    <t>Personal bankruptcy rate</t>
-  </si>
-  <si>
-    <t>personal-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t>Non-business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t>Resident spending</t>
-  </si>
-  <si>
-    <t>resident-spending</t>
-  </si>
-  <si>
-    <t>Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t>Resident spending, total</t>
-  </si>
-  <si>
-    <t>resident-spending-total</t>
-  </si>
-  <si>
-    <t>About the DMV</t>
-  </si>
-  <si>
-    <t>about</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
-    <t>total-population</t>
-  </si>
-  <si>
-    <t>Total population</t>
-  </si>
-  <si>
-    <t>U.S. Census Bureau and Lightcast</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>2024A1</t>
-  </si>
-  <si>
-    <t>Educational attainment</t>
-  </si>
-  <si>
-    <t>eduatt</t>
-  </si>
-  <si>
-    <t>Educational attaintment for population aged 25 and older</t>
-  </si>
-  <si>
-    <t>Less than high school</t>
-  </si>
-  <si>
-    <t>less-than-hs</t>
-  </si>
-  <si>
-    <t>High school or equivalent</t>
-  </si>
-  <si>
-    <t>high-school</t>
-  </si>
-  <si>
-    <t>Some college or associate's degree</t>
-  </si>
-  <si>
-    <t>some-college-aa</t>
-  </si>
-  <si>
-    <t>Bachelor's degree</t>
-  </si>
-  <si>
-    <t>bachelors-degree</t>
-  </si>
-  <si>
-    <t>Graduate or professional degree</t>
-  </si>
-  <si>
-    <t>graduate-degree</t>
-  </si>
-  <si>
-    <t>High school degree or higher, total</t>
-  </si>
-  <si>
-    <t>hs-plus</t>
-  </si>
-  <si>
-    <t>Bachelor's degree or higher, total</t>
-  </si>
-  <si>
-    <t>ba-plus</t>
-  </si>
-  <si>
-    <t>Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t>foreign-born</t>
-  </si>
-  <si>
-    <t>Total air passengers served</t>
-  </si>
-  <si>
-    <t>air-travel</t>
-  </si>
-  <si>
-    <t>Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t>U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t>air-passengers</t>
-  </si>
-  <si>
-    <t>Consumer prices</t>
-  </si>
-  <si>
-    <t>cpi-total</t>
-  </si>
-  <si>
-    <t>Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t>U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t>Median residential sale price</t>
-  </si>
-  <si>
-    <t>median-sale-price</t>
-  </si>
-  <si>
-    <t>Home sales</t>
-  </si>
-  <si>
-    <t>home-sales</t>
-  </si>
-  <si>
-    <t>Residential home sales</t>
-  </si>
-  <si>
-    <t>Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t>median-dom</t>
-  </si>
-  <si>
-    <t>list-to-sale-ratio</t>
-  </si>
-  <si>
-    <t>homes-sold-above-list</t>
-  </si>
-  <si>
-    <t>Median days on market</t>
-  </si>
-  <si>
-    <t>List-to-sale price ratio</t>
-  </si>
-  <si>
-    <t>Homes sold above list price (%)</t>
-  </si>
-  <si>
-    <t>DMV-2026-02-07</t>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">municipal-services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household Wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household-wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medicaid-enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State agency reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNAP participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snap-participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2025-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-prime consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severely credit-constrained consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-subprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personal-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About the DMV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total-population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educational attainment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eduatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less than high school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">less-than-hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school or equivalent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high-school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some college or associate's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">some-college-aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bachelors-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduate or professional degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">graduate-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hs-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ba-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of foreign-born population (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign-born</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total air passengers served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-passengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -848,15 +838,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1138,11 +1119,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q57"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1195,7 +1176,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -1241,14 +1222,14 @@
       <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>1</v>
       </c>
       <c r="Q2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1294,14 +1275,14 @@
       <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1347,14 +1328,14 @@
       <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1400,14 +1381,14 @@
       <c r="O5" t="s">
         <v>46</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1453,14 +1434,14 @@
       <c r="O6" t="s">
         <v>31</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -1506,14 +1487,14 @@
       <c r="O7" t="s">
         <v>31</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -1559,14 +1540,14 @@
       <c r="O8" t="s">
         <v>31</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>60</v>
       </c>
@@ -1612,14 +1593,14 @@
       <c r="O9" t="s">
         <v>31</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>60</v>
       </c>
@@ -1665,14 +1646,14 @@
       <c r="O10" t="s">
         <v>31</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>60</v>
       </c>
@@ -1718,14 +1699,14 @@
       <c r="O11" t="s">
         <v>80</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1771,14 +1752,14 @@
       <c r="O12" t="s">
         <v>80</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>1</v>
       </c>
       <c r="Q12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>84</v>
       </c>
@@ -1824,14 +1805,14 @@
       <c r="O13" t="s">
         <v>80</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>84</v>
       </c>
@@ -1851,10 +1832,10 @@
         <v>22</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I14" t="s">
         <v>25</v>
@@ -1877,14 +1858,14 @@
       <c r="O14" t="s">
         <v>80</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
         <v>84</v>
       </c>
@@ -1904,10 +1885,10 @@
         <v>22</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s">
         <v>25</v>
@@ -1930,14 +1911,14 @@
       <c r="O15" t="s">
         <v>80</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -1957,10 +1938,10 @@
         <v>22</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" t="s">
         <v>25</v>
@@ -1983,14 +1964,14 @@
       <c r="O16" t="s">
         <v>80</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>84</v>
       </c>
@@ -2010,10 +1991,10 @@
         <v>22</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" t="s">
         <v>25</v>
@@ -2036,14 +2017,14 @@
       <c r="O17" t="s">
         <v>80</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -2063,10 +2044,10 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I18" t="s">
         <v>25</v>
@@ -2089,14 +2070,14 @@
       <c r="O18" t="s">
         <v>80</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>84</v>
       </c>
@@ -2104,22 +2085,22 @@
         <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I19" t="s">
         <v>25</v>
@@ -2142,14 +2123,14 @@
       <c r="O19" t="s">
         <v>31</v>
       </c>
-      <c r="P19">
+      <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -2157,22 +2138,22 @@
         <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I20" t="s">
         <v>25</v>
@@ -2195,14 +2176,14 @@
       <c r="O20" t="s">
         <v>31</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -2210,22 +2191,22 @@
         <v>85</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
         <v>25</v>
@@ -2248,14 +2229,14 @@
       <c r="O21" t="s">
         <v>31</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>1</v>
       </c>
       <c r="Q21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -2263,22 +2244,22 @@
         <v>85</v>
       </c>
       <c r="C22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I22" t="s">
         <v>25</v>
@@ -2301,43 +2282,43 @@
       <c r="O22" t="s">
         <v>31</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>1</v>
       </c>
       <c r="Q22" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I23" t="s">
         <v>41</v>
       </c>
       <c r="J23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K23" t="s">
         <v>92</v>
@@ -2354,43 +2335,43 @@
       <c r="O23" t="s">
         <v>46</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H24" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I24" t="s">
         <v>41</v>
       </c>
       <c r="J24" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K24" t="s">
         <v>92</v>
@@ -2407,37 +2388,37 @@
       <c r="O24" t="s">
         <v>46</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C25" t="s">
-        <v>251</v>
+        <v>129</v>
       </c>
       <c r="D25" t="s">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="E25" t="s">
-        <v>253</v>
+        <v>131</v>
       </c>
       <c r="F25" t="s">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="G25" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="H25" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="I25" t="s">
         <v>25</v>
@@ -2455,42 +2436,42 @@
         <v>29</v>
       </c>
       <c r="N25" t="s">
+        <v>135</v>
+      </c>
+      <c r="O25" t="s">
+        <v>136</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s">
         <v>130</v>
       </c>
-      <c r="O25" t="s">
+      <c r="E26" t="s">
         <v>131</v>
       </c>
-      <c r="P25">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>117</v>
-      </c>
-      <c r="B26" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" t="s">
-        <v>251</v>
-      </c>
-      <c r="D26" t="s">
-        <v>252</v>
-      </c>
-      <c r="E26" t="s">
-        <v>253</v>
-      </c>
       <c r="F26" t="s">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="G26" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H26" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="I26" t="s">
         <v>25</v>
@@ -2508,42 +2489,42 @@
         <v>29</v>
       </c>
       <c r="N26" t="s">
+        <v>135</v>
+      </c>
+      <c r="O26" t="s">
+        <v>136</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" t="s">
+        <v>129</v>
+      </c>
+      <c r="D27" t="s">
         <v>130</v>
       </c>
-      <c r="O26" t="s">
+      <c r="E27" t="s">
         <v>131</v>
       </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" t="s">
-        <v>251</v>
-      </c>
-      <c r="D27" t="s">
-        <v>252</v>
-      </c>
-      <c r="E27" t="s">
-        <v>253</v>
-      </c>
       <c r="F27" t="s">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="G27" t="s">
-        <v>249</v>
+        <v>140</v>
       </c>
       <c r="H27" t="s">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s">
         <v>25</v>
@@ -2561,51 +2542,51 @@
         <v>29</v>
       </c>
       <c r="N27" t="s">
+        <v>135</v>
+      </c>
+      <c r="O27" t="s">
+        <v>136</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" t="s">
+        <v>129</v>
+      </c>
+      <c r="D28" t="s">
         <v>130</v>
       </c>
-      <c r="O27" t="s">
+      <c r="E28" t="s">
         <v>131</v>
       </c>
-      <c r="P27">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" t="s">
-        <v>251</v>
-      </c>
-      <c r="D28" t="s">
-        <v>252</v>
-      </c>
-      <c r="E28" t="s">
-        <v>253</v>
-      </c>
       <c r="F28" t="s">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="G28" t="s">
-        <v>258</v>
+        <v>142</v>
       </c>
       <c r="H28" t="s">
-        <v>255</v>
+        <v>143</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2614,48 +2595,48 @@
         <v>29</v>
       </c>
       <c r="N28" t="s">
+        <v>135</v>
+      </c>
+      <c r="O28" t="s">
+        <v>136</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" t="s">
+        <v>129</v>
+      </c>
+      <c r="D29" t="s">
         <v>130</v>
       </c>
-      <c r="O28" t="s">
+      <c r="E29" t="s">
         <v>131</v>
       </c>
-      <c r="P28">
-        <v>1</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>117</v>
-      </c>
-      <c r="B29" t="s">
-        <v>118</v>
-      </c>
-      <c r="C29" t="s">
-        <v>251</v>
-      </c>
-      <c r="D29" t="s">
-        <v>252</v>
-      </c>
-      <c r="E29" t="s">
-        <v>253</v>
-      </c>
       <c r="F29" t="s">
-        <v>254</v>
+        <v>132</v>
       </c>
       <c r="G29" t="s">
-        <v>259</v>
+        <v>144</v>
       </c>
       <c r="H29" t="s">
-        <v>256</v>
+        <v>145</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="K29" t="s">
         <v>92</v>
@@ -2667,51 +2648,51 @@
         <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="O29" t="s">
-        <v>131</v>
-      </c>
-      <c r="P29">
+        <v>136</v>
+      </c>
+      <c r="P29" t="n">
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>251</v>
+        <v>146</v>
       </c>
       <c r="D30" t="s">
-        <v>252</v>
+        <v>147</v>
       </c>
       <c r="E30" t="s">
-        <v>253</v>
+        <v>148</v>
       </c>
       <c r="F30" t="s">
-        <v>254</v>
+        <v>149</v>
       </c>
       <c r="G30" t="s">
-        <v>260</v>
+        <v>146</v>
       </c>
       <c r="H30" t="s">
-        <v>257</v>
+        <v>147</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2720,48 +2701,48 @@
         <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="O30" t="s">
-        <v>131</v>
-      </c>
-      <c r="P30">
+        <v>136</v>
+      </c>
+      <c r="P30" t="n">
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="C31" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="D31" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="F31" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="G31" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="H31" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="K31" t="s">
         <v>27</v>
@@ -2773,101 +2754,101 @@
         <v>29</v>
       </c>
       <c r="N31" t="s">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="O31" t="s">
-        <v>131</v>
-      </c>
-      <c r="P31">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
       </c>
       <c r="Q31" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C32" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="D32" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="G32" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="H32" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>143</v>
+        <v>26</v>
       </c>
       <c r="K32" t="s">
         <v>27</v>
       </c>
       <c r="L32" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="M32" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="N32" t="s">
-        <v>30</v>
+        <v>160</v>
       </c>
       <c r="O32" t="s">
-        <v>31</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
+        <v>161</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C33" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="E33" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F33" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H33" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="K33" t="s">
         <v>27</v>
@@ -2879,110 +2860,110 @@
         <v>94</v>
       </c>
       <c r="N33" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="O33" t="s">
-        <v>149</v>
-      </c>
-      <c r="P33">
+        <v>161</v>
+      </c>
+      <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="E34" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="F34" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="G34" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="H34" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>54</v>
+        <v>175</v>
       </c>
       <c r="K34" t="s">
         <v>27</v>
       </c>
       <c r="L34" t="s">
-        <v>93</v>
+        <v>176</v>
       </c>
       <c r="M34" t="s">
-        <v>94</v>
+        <v>177</v>
       </c>
       <c r="N34" t="s">
-        <v>148</v>
+        <v>30</v>
       </c>
       <c r="O34" t="s">
-        <v>149</v>
-      </c>
-      <c r="P34">
-        <v>1</v>
+        <v>31</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
       </c>
       <c r="Q34" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D35" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="E35" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="F35" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="G35" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="H35" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>163</v>
+        <v>42</v>
       </c>
       <c r="K35" t="s">
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>164</v>
+        <v>28</v>
       </c>
       <c r="M35" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -2990,37 +2971,37 @@
       <c r="O35" t="s">
         <v>31</v>
       </c>
-      <c r="P35">
-        <v>0</v>
+      <c r="P35" t="n">
+        <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D36" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E36" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F36" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="G36" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
@@ -3043,37 +3024,37 @@
       <c r="O36" t="s">
         <v>31</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>1</v>
       </c>
       <c r="Q36" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="C37" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="E37" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="F37" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="G37" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="H37" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -3096,37 +3077,37 @@
       <c r="O37" t="s">
         <v>31</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="B38" t="s">
-        <v>156</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="F38" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="G38" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="H38" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
@@ -3138,10 +3119,10 @@
         <v>27</v>
       </c>
       <c r="L38" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M38" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N38" t="s">
         <v>30</v>
@@ -3149,90 +3130,90 @@
       <c r="O38" t="s">
         <v>31</v>
       </c>
-      <c r="P38">
+      <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>193</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="D39" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E39" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="F39" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="G39" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="H39" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="I39" t="s">
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="K39" t="s">
         <v>27</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M39" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="N39" t="s">
-        <v>30</v>
+        <v>198</v>
       </c>
       <c r="O39" t="s">
-        <v>31</v>
-      </c>
-      <c r="P39">
+        <v>199</v>
+      </c>
+      <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="D40" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E40" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="F40" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="G40" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="H40" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="I40" t="s">
         <v>25</v>
@@ -3250,51 +3231,51 @@
         <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="O40" t="s">
-        <v>187</v>
-      </c>
-      <c r="P40">
+        <v>199</v>
+      </c>
+      <c r="P40" t="n">
         <v>1</v>
       </c>
       <c r="Q40" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B41" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C41" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D41" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E41" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="G41" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="H41" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J41" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L41" t="s">
         <v>28</v>
@@ -3303,42 +3284,42 @@
         <v>29</v>
       </c>
       <c r="N41" t="s">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="O41" t="s">
-        <v>187</v>
-      </c>
-      <c r="P41">
+        <v>210</v>
+      </c>
+      <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B42" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C42" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D42" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E42" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F42" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G42" t="s">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="H42" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="I42" t="s">
         <v>41</v>
@@ -3356,42 +3337,42 @@
         <v>29</v>
       </c>
       <c r="N42" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="O42" t="s">
-        <v>198</v>
-      </c>
-      <c r="P42">
+        <v>210</v>
+      </c>
+      <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B43" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C43" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="D43" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="E43" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="F43" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="G43" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="H43" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="I43" t="s">
         <v>41</v>
@@ -3409,210 +3390,210 @@
         <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="O43" t="s">
-        <v>198</v>
-      </c>
-      <c r="P43">
+        <v>210</v>
+      </c>
+      <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C44" t="s">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="D44" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="E44" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="F44" t="s">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="G44" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="H44" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="I44" t="s">
         <v>41</v>
       </c>
       <c r="J44" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="K44" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="L44" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M44" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N44" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="O44" t="s">
-        <v>198</v>
-      </c>
-      <c r="P44">
+        <v>46</v>
+      </c>
+      <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>18</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="D45" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="E45" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="G45" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="H45" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="I45" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K45" t="s">
         <v>27</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="M45" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="N45" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="O45" t="s">
-        <v>46</v>
-      </c>
-      <c r="P45">
+        <v>161</v>
+      </c>
+      <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>225</v>
       </c>
       <c r="C46" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="F46" t="s">
-        <v>147</v>
+        <v>229</v>
       </c>
       <c r="G46" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="H46" t="s">
+        <v>227</v>
+      </c>
+      <c r="I46" t="s">
+        <v>230</v>
+      </c>
+      <c r="J46" t="s">
+        <v>26</v>
+      </c>
+      <c r="K46" t="s">
+        <v>231</v>
+      </c>
+      <c r="L46" t="s">
+        <v>28</v>
+      </c>
+      <c r="M46" t="s">
+        <v>29</v>
+      </c>
+      <c r="N46" t="s">
+        <v>232</v>
+      </c>
+      <c r="O46" t="s">
+        <v>232</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="s">
         <v>211</v>
       </c>
-      <c r="I46" t="s">
-        <v>25</v>
-      </c>
-      <c r="J46" t="s">
-        <v>54</v>
-      </c>
-      <c r="K46" t="s">
-        <v>27</v>
-      </c>
-      <c r="L46" t="s">
-        <v>93</v>
-      </c>
-      <c r="M46" t="s">
-        <v>94</v>
-      </c>
-      <c r="N46" t="s">
-        <v>148</v>
-      </c>
-      <c r="O46" t="s">
-        <v>149</v>
-      </c>
-      <c r="P46">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C47" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="D47" t="s">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="E47" t="s">
-        <v>216</v>
+        <v>235</v>
       </c>
       <c r="F47" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G47" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="H47" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="I47" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J47" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="K47" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -3621,51 +3602,51 @@
         <v>29</v>
       </c>
       <c r="N47" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O47" t="s">
-        <v>220</v>
-      </c>
-      <c r="P47">
+        <v>232</v>
+      </c>
+      <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E48" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F48" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G48" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="H48" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="I48" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J48" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K48" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3674,51 +3655,51 @@
         <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O48" t="s">
-        <v>220</v>
-      </c>
-      <c r="P48">
+        <v>232</v>
+      </c>
+      <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D49" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E49" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G49" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="H49" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="I49" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J49" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
@@ -3727,51 +3708,51 @@
         <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O49" t="s">
-        <v>220</v>
-      </c>
-      <c r="P49">
+        <v>232</v>
+      </c>
+      <c r="P49" t="n">
         <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C50" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E50" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G50" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="H50" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="I50" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J50" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3780,51 +3761,51 @@
         <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O50" t="s">
-        <v>220</v>
-      </c>
-      <c r="P50">
+        <v>232</v>
+      </c>
+      <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C51" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D51" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E51" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F51" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G51" t="s">
+        <v>244</v>
+      </c>
+      <c r="H51" t="s">
+        <v>245</v>
+      </c>
+      <c r="I51" t="s">
         <v>230</v>
       </c>
-      <c r="H51" t="s">
+      <c r="J51" t="s">
+        <v>126</v>
+      </c>
+      <c r="K51" t="s">
         <v>231</v>
-      </c>
-      <c r="I51" t="s">
-        <v>218</v>
-      </c>
-      <c r="J51" t="s">
-        <v>125</v>
-      </c>
-      <c r="K51" t="s">
-        <v>219</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3833,51 +3814,51 @@
         <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O51" t="s">
-        <v>220</v>
-      </c>
-      <c r="P51">
+        <v>232</v>
+      </c>
+      <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C52" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D52" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E52" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F52" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G52" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="H52" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="I52" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K52" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L52" t="s">
         <v>28</v>
@@ -3886,51 +3867,51 @@
         <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O52" t="s">
-        <v>220</v>
-      </c>
-      <c r="P52">
+        <v>232</v>
+      </c>
+      <c r="P52" t="n">
         <v>1</v>
       </c>
       <c r="Q52" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C53" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D53" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="E53" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F53" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G53" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="H53" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="I53" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J53" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K53" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L53" t="s">
         <v>28</v>
@@ -3939,51 +3920,51 @@
         <v>29</v>
       </c>
       <c r="N53" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O53" t="s">
-        <v>220</v>
-      </c>
-      <c r="P53">
+        <v>232</v>
+      </c>
+      <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C54" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D54" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E54" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F54" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="G54" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="H54" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="I54" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="J54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K54" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L54" t="s">
         <v>28</v>
@@ -3992,51 +3973,51 @@
         <v>29</v>
       </c>
       <c r="N54" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="O54" t="s">
-        <v>220</v>
-      </c>
-      <c r="P54">
+        <v>232</v>
+      </c>
+      <c r="P54" t="n">
         <v>1</v>
       </c>
       <c r="Q54" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" t="s">
-        <v>212</v>
+        <v>150</v>
       </c>
       <c r="B55" t="s">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="D55" t="s">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="E55" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="F55" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="G55" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="H55" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="I55" t="s">
-        <v>218</v>
+        <v>25</v>
       </c>
       <c r="J55" t="s">
-        <v>125</v>
+        <v>26</v>
       </c>
       <c r="K55" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
       <c r="L55" t="s">
         <v>28</v>
@@ -4045,48 +4026,48 @@
         <v>29</v>
       </c>
       <c r="N55" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="O55" t="s">
-        <v>220</v>
-      </c>
-      <c r="P55">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
       </c>
       <c r="Q55" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>139</v>
+        <v>18</v>
       </c>
       <c r="C56" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="D56" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
       <c r="E56" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="F56" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="G56" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="H56" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="I56" t="s">
         <v>25</v>
       </c>
       <c r="J56" t="s">
-        <v>26</v>
+        <v>175</v>
       </c>
       <c r="K56" t="s">
         <v>27</v>
@@ -4098,79 +4079,20 @@
         <v>29</v>
       </c>
       <c r="N56" t="s">
-        <v>186</v>
+        <v>79</v>
       </c>
       <c r="O56" t="s">
-        <v>187</v>
-      </c>
-      <c r="P56">
+        <v>80</v>
+      </c>
+      <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>17</v>
-      </c>
-      <c r="B57" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" t="s">
-        <v>245</v>
-      </c>
-      <c r="D57" t="s">
-        <v>246</v>
-      </c>
-      <c r="E57" t="s">
-        <v>247</v>
-      </c>
-      <c r="F57" t="s">
-        <v>248</v>
-      </c>
-      <c r="G57" t="s">
-        <v>245</v>
-      </c>
-      <c r="H57" t="s">
-        <v>246</v>
-      </c>
-      <c r="I57" t="s">
-        <v>25</v>
-      </c>
-      <c r="J57" t="s">
-        <v>163</v>
-      </c>
-      <c r="K57" t="s">
-        <v>27</v>
-      </c>
-      <c r="L57" t="s">
-        <v>28</v>
-      </c>
-      <c r="M57" t="s">
-        <v>29</v>
-      </c>
-      <c r="N57" t="s">
-        <v>79</v>
-      </c>
-      <c r="O57" t="s">
-        <v>80</v>
-      </c>
-      <c r="P57">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{a6274e99-f707-4183-90a3-28f81526dfab}" enabled="1" method="Standard" siteId="{0a02388e-6178-4513-9b82-88b9dc6bf457}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-listing-price</t>
   </si>
   <si>
     <t xml:space="preserve">Median residential sale price</t>
@@ -2449,57 +2452,29 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>118</v>
-      </c>
-      <c r="B26" t="s">
-        <v>119</v>
-      </c>
-      <c r="C26" t="s">
-        <v>129</v>
-      </c>
-      <c r="D26" t="s">
-        <v>130</v>
-      </c>
-      <c r="E26" t="s">
-        <v>131</v>
-      </c>
-      <c r="F26" t="s">
-        <v>132</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26" t="s">
         <v>138</v>
       </c>
-      <c r="H26" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" t="s">
-        <v>28</v>
-      </c>
-      <c r="M26" t="s">
-        <v>29</v>
-      </c>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
       <c r="N26" t="s">
         <v>135</v>
       </c>
       <c r="O26" t="s">
         <v>136</v>
       </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>137</v>
-      </c>
+      <c r="P26"/>
+      <c r="Q26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
@@ -2521,10 +2496,10 @@
         <v>132</v>
       </c>
       <c r="G27" t="s">
+        <v>139</v>
+      </c>
+      <c r="H27" t="s">
         <v>140</v>
-      </c>
-      <c r="H27" t="s">
-        <v>141</v>
       </c>
       <c r="I27" t="s">
         <v>25</v>
@@ -2574,19 +2549,19 @@
         <v>132</v>
       </c>
       <c r="G28" t="s">
+        <v>141</v>
+      </c>
+      <c r="H28" t="s">
         <v>142</v>
-      </c>
-      <c r="H28" t="s">
-        <v>143</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="L28" t="s">
         <v>28</v>
@@ -2627,16 +2602,16 @@
         <v>132</v>
       </c>
       <c r="G29" t="s">
+        <v>143</v>
+      </c>
+      <c r="H29" t="s">
         <v>144</v>
-      </c>
-      <c r="H29" t="s">
-        <v>145</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="K29" t="s">
         <v>92</v>
@@ -2668,31 +2643,31 @@
         <v>119</v>
       </c>
       <c r="C30" t="s">
+        <v>129</v>
+      </c>
+      <c r="D30" t="s">
+        <v>130</v>
+      </c>
+      <c r="E30" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" t="s">
+        <v>132</v>
+      </c>
+      <c r="G30" t="s">
+        <v>145</v>
+      </c>
+      <c r="H30" t="s">
         <v>146</v>
-      </c>
-      <c r="D30" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" t="s">
-        <v>148</v>
-      </c>
-      <c r="F30" t="s">
-        <v>149</v>
-      </c>
-      <c r="G30" t="s">
-        <v>146</v>
-      </c>
-      <c r="H30" t="s">
-        <v>147</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>126</v>
       </c>
       <c r="K30" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L30" t="s">
         <v>28</v>
@@ -2715,34 +2690,34 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" t="s">
         <v>150</v>
       </c>
-      <c r="B31" t="s">
-        <v>151</v>
-      </c>
-      <c r="C31" t="s">
-        <v>152</v>
-      </c>
-      <c r="D31" t="s">
-        <v>153</v>
-      </c>
-      <c r="E31" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" t="s">
-        <v>123</v>
-      </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="H31" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="K31" t="s">
         <v>27</v>
@@ -2754,101 +2729,101 @@
         <v>29</v>
       </c>
       <c r="N31" t="s">
-        <v>30</v>
+        <v>135</v>
       </c>
       <c r="O31" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D32" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F32" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="G32" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H32" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>26</v>
+        <v>156</v>
       </c>
       <c r="K32" t="s">
         <v>27</v>
       </c>
       <c r="L32" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="M32" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>160</v>
+        <v>30</v>
       </c>
       <c r="O32" t="s">
-        <v>161</v>
+        <v>31</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
+        <v>160</v>
+      </c>
+      <c r="G33" t="s">
+        <v>158</v>
+      </c>
+      <c r="H33" t="s">
         <v>159</v>
-      </c>
-      <c r="G33" t="s">
-        <v>165</v>
-      </c>
-      <c r="H33" t="s">
-        <v>166</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="K33" t="s">
         <v>27</v>
@@ -2860,110 +2835,110 @@
         <v>94</v>
       </c>
       <c r="N33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D34" t="s">
+        <v>164</v>
+      </c>
+      <c r="E34" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" t="s">
+        <v>160</v>
+      </c>
+      <c r="G34" t="s">
+        <v>166</v>
+      </c>
+      <c r="H34" t="s">
         <v>167</v>
-      </c>
-      <c r="B34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C34" t="s">
-        <v>169</v>
-      </c>
-      <c r="D34" t="s">
-        <v>170</v>
-      </c>
-      <c r="E34" t="s">
-        <v>171</v>
-      </c>
-      <c r="F34" t="s">
-        <v>172</v>
-      </c>
-      <c r="G34" t="s">
-        <v>173</v>
-      </c>
-      <c r="H34" t="s">
-        <v>174</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>175</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
         <v>27</v>
       </c>
       <c r="L34" t="s">
-        <v>176</v>
+        <v>93</v>
       </c>
       <c r="M34" t="s">
-        <v>177</v>
+        <v>94</v>
       </c>
       <c r="N34" t="s">
-        <v>30</v>
+        <v>161</v>
       </c>
       <c r="O34" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>72</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="D35" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F35" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="G35" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H35" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>42</v>
+        <v>176</v>
       </c>
       <c r="K35" t="s">
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>28</v>
+        <v>177</v>
       </c>
       <c r="M35" t="s">
-        <v>29</v>
+        <v>178</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -2972,36 +2947,36 @@
         <v>31</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G36" t="s">
+        <v>183</v>
+      </c>
+      <c r="H36" t="s">
         <v>184</v>
-      </c>
-      <c r="H36" t="s">
-        <v>185</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
@@ -3033,28 +3008,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G37" t="s">
+        <v>185</v>
+      </c>
+      <c r="H37" t="s">
         <v>186</v>
-      </c>
-      <c r="H37" t="s">
-        <v>187</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -3086,28 +3061,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="C38" t="s">
+        <v>179</v>
+      </c>
+      <c r="D38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E38" t="s">
+        <v>181</v>
+      </c>
+      <c r="F38" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" t="s">
+        <v>187</v>
+      </c>
+      <c r="H38" t="s">
         <v>188</v>
-      </c>
-      <c r="D38" t="s">
-        <v>189</v>
-      </c>
-      <c r="E38" t="s">
-        <v>190</v>
-      </c>
-      <c r="F38" t="s">
-        <v>191</v>
-      </c>
-      <c r="G38" t="s">
-        <v>188</v>
-      </c>
-      <c r="H38" t="s">
-        <v>189</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
@@ -3119,10 +3094,10 @@
         <v>27</v>
       </c>
       <c r="L38" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M38" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="N38" t="s">
         <v>30</v>
@@ -3139,81 +3114,81 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>84</v>
+      </c>
+      <c r="B39" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" t="s">
         <v>192</v>
       </c>
-      <c r="B39" t="s">
-        <v>193</v>
-      </c>
-      <c r="C39" t="s">
-        <v>194</v>
-      </c>
-      <c r="D39" t="s">
-        <v>195</v>
-      </c>
-      <c r="E39" t="s">
-        <v>196</v>
-      </c>
-      <c r="F39" t="s">
-        <v>197</v>
-      </c>
       <c r="G39" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="H39" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="I39" t="s">
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="K39" t="s">
         <v>27</v>
       </c>
       <c r="L39" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M39" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="N39" t="s">
-        <v>198</v>
+        <v>30</v>
       </c>
       <c r="O39" t="s">
-        <v>199</v>
+        <v>31</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C40" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D40" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E40" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="F40" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G40" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="H40" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I40" t="s">
         <v>25</v>
@@ -3231,10 +3206,10 @@
         <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3245,37 +3220,37 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C41" t="s">
+        <v>201</v>
+      </c>
+      <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
         <v>203</v>
       </c>
-      <c r="D41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E41" t="s">
-        <v>205</v>
-      </c>
       <c r="F41" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G41" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="H41" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="I41" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
       <c r="K41" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="L41" t="s">
         <v>28</v>
@@ -3284,42 +3259,42 @@
         <v>29</v>
       </c>
       <c r="N41" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="O41" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>211</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G42" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H42" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="I42" t="s">
         <v>41</v>
@@ -3337,42 +3312,42 @@
         <v>29</v>
       </c>
       <c r="N42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C43" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G43" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43" t="s">
         <v>214</v>
-      </c>
-      <c r="H43" t="s">
-        <v>215</v>
       </c>
       <c r="I43" t="s">
         <v>41</v>
@@ -3390,210 +3365,210 @@
         <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C44" t="s">
+        <v>204</v>
+      </c>
+      <c r="D44" t="s">
+        <v>205</v>
+      </c>
+      <c r="E44" t="s">
+        <v>206</v>
+      </c>
+      <c r="F44" t="s">
+        <v>207</v>
+      </c>
+      <c r="G44" t="s">
+        <v>215</v>
+      </c>
+      <c r="H44" t="s">
         <v>216</v>
-      </c>
-      <c r="D44" t="s">
-        <v>217</v>
-      </c>
-      <c r="E44" t="s">
-        <v>218</v>
-      </c>
-      <c r="F44" t="s">
-        <v>40</v>
-      </c>
-      <c r="G44" t="s">
-        <v>216</v>
-      </c>
-      <c r="H44" t="s">
-        <v>217</v>
       </c>
       <c r="I44" t="s">
         <v>41</v>
       </c>
       <c r="J44" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="L44" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="M44" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="N44" t="s">
-        <v>45</v>
+        <v>210</v>
       </c>
       <c r="O44" t="s">
-        <v>46</v>
+        <v>211</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>47</v>
+        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>193</v>
       </c>
       <c r="B45" t="s">
-        <v>18</v>
+        <v>194</v>
       </c>
       <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>218</v>
+      </c>
+      <c r="E45" t="s">
         <v>219</v>
       </c>
-      <c r="D45" t="s">
-        <v>220</v>
-      </c>
-      <c r="E45" t="s">
-        <v>221</v>
-      </c>
       <c r="F45" t="s">
-        <v>159</v>
+        <v>40</v>
       </c>
       <c r="G45" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H45" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J45" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="K45" t="s">
         <v>27</v>
       </c>
       <c r="L45" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="M45" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="N45" t="s">
-        <v>160</v>
+        <v>45</v>
       </c>
       <c r="O45" t="s">
-        <v>161</v>
+        <v>46</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="s">
-        <v>156</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" t="s">
+        <v>220</v>
+      </c>
+      <c r="D46" t="s">
+        <v>221</v>
+      </c>
+      <c r="E46" t="s">
+        <v>222</v>
+      </c>
+      <c r="F46" t="s">
+        <v>160</v>
+      </c>
+      <c r="G46" t="s">
+        <v>223</v>
+      </c>
+      <c r="H46" t="s">
         <v>224</v>
       </c>
-      <c r="B46" t="s">
-        <v>225</v>
-      </c>
-      <c r="C46" t="s">
-        <v>226</v>
-      </c>
-      <c r="D46" t="s">
-        <v>227</v>
-      </c>
-      <c r="E46" t="s">
-        <v>228</v>
-      </c>
-      <c r="F46" t="s">
-        <v>229</v>
-      </c>
-      <c r="G46" t="s">
-        <v>228</v>
-      </c>
-      <c r="H46" t="s">
-        <v>227</v>
-      </c>
       <c r="I46" t="s">
-        <v>230</v>
+        <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="K46" t="s">
-        <v>231</v>
+        <v>27</v>
       </c>
       <c r="L46" t="s">
-        <v>28</v>
+        <v>93</v>
       </c>
       <c r="M46" t="s">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="N46" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="O46" t="s">
-        <v>232</v>
+        <v>162</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>211</v>
+        <v>157</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C47" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="F47" t="s">
+        <v>230</v>
+      </c>
+      <c r="G47" t="s">
         <v>229</v>
       </c>
-      <c r="G47" t="s">
-        <v>236</v>
-      </c>
       <c r="H47" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="I47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J47" t="s">
-        <v>126</v>
+        <v>26</v>
       </c>
       <c r="K47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -3602,51 +3577,51 @@
         <v>29</v>
       </c>
       <c r="N47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B48" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F48" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G48" t="s">
+        <v>237</v>
+      </c>
+      <c r="H48" t="s">
         <v>238</v>
       </c>
-      <c r="H48" t="s">
-        <v>239</v>
-      </c>
       <c r="I48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J48" t="s">
         <v>126</v>
       </c>
       <c r="K48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3655,51 +3630,51 @@
         <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B49" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G49" t="s">
+        <v>239</v>
+      </c>
+      <c r="H49" t="s">
         <v>240</v>
       </c>
-      <c r="H49" t="s">
-        <v>241</v>
-      </c>
       <c r="I49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J49" t="s">
         <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
@@ -3708,51 +3683,51 @@
         <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F50" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G50" t="s">
+        <v>241</v>
+      </c>
+      <c r="H50" t="s">
         <v>242</v>
       </c>
-      <c r="H50" t="s">
-        <v>243</v>
-      </c>
       <c r="I50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J50" t="s">
         <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3761,51 +3736,51 @@
         <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B51" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F51" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G51" t="s">
+        <v>243</v>
+      </c>
+      <c r="H51" t="s">
         <v>244</v>
       </c>
-      <c r="H51" t="s">
-        <v>245</v>
-      </c>
       <c r="I51" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J51" t="s">
         <v>126</v>
       </c>
       <c r="K51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3814,51 +3789,51 @@
         <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F52" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G52" t="s">
+        <v>245</v>
+      </c>
+      <c r="H52" t="s">
         <v>246</v>
       </c>
-      <c r="H52" t="s">
-        <v>247</v>
-      </c>
       <c r="I52" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J52" t="s">
         <v>126</v>
       </c>
       <c r="K52" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L52" t="s">
         <v>28</v>
@@ -3867,51 +3842,51 @@
         <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
       <c r="Q52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F53" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G53" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" t="s">
         <v>248</v>
       </c>
-      <c r="H53" t="s">
-        <v>249</v>
-      </c>
       <c r="I53" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J53" t="s">
         <v>126</v>
       </c>
       <c r="K53" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L53" t="s">
         <v>28</v>
@@ -3920,51 +3895,51 @@
         <v>29</v>
       </c>
       <c r="N53" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O53" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C54" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="D54" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G54" t="s">
+        <v>249</v>
+      </c>
+      <c r="H54" t="s">
         <v>250</v>
       </c>
-      <c r="H54" t="s">
-        <v>251</v>
-      </c>
       <c r="I54" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="J54" t="s">
         <v>126</v>
       </c>
       <c r="K54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L54" t="s">
         <v>28</v>
@@ -3973,51 +3948,51 @@
         <v>29</v>
       </c>
       <c r="N54" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O54" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
       <c r="Q54" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>150</v>
+        <v>225</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="C55" t="s">
+        <v>227</v>
+      </c>
+      <c r="D55" t="s">
+        <v>228</v>
+      </c>
+      <c r="E55" t="s">
+        <v>229</v>
+      </c>
+      <c r="F55" t="s">
+        <v>230</v>
+      </c>
+      <c r="G55" t="s">
+        <v>251</v>
+      </c>
+      <c r="H55" t="s">
         <v>252</v>
       </c>
-      <c r="D55" t="s">
-        <v>253</v>
-      </c>
-      <c r="E55" t="s">
-        <v>254</v>
-      </c>
-      <c r="F55" t="s">
-        <v>255</v>
-      </c>
-      <c r="G55" t="s">
-        <v>252</v>
-      </c>
-      <c r="H55" t="s">
-        <v>256</v>
-      </c>
       <c r="I55" t="s">
-        <v>25</v>
+        <v>231</v>
       </c>
       <c r="J55" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="K55" t="s">
-        <v>27</v>
+        <v>232</v>
       </c>
       <c r="L55" t="s">
         <v>28</v>
@@ -4026,48 +4001,48 @@
         <v>29</v>
       </c>
       <c r="N55" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="O55" t="s">
-        <v>199</v>
+        <v>233</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" t="s">
-        <v>81</v>
+        <v>212</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="B56" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="C56" t="s">
+        <v>253</v>
+      </c>
+      <c r="D56" t="s">
+        <v>254</v>
+      </c>
+      <c r="E56" t="s">
+        <v>255</v>
+      </c>
+      <c r="F56" t="s">
+        <v>256</v>
+      </c>
+      <c r="G56" t="s">
+        <v>253</v>
+      </c>
+      <c r="H56" t="s">
         <v>257</v>
-      </c>
-      <c r="D56" t="s">
-        <v>258</v>
-      </c>
-      <c r="E56" t="s">
-        <v>259</v>
-      </c>
-      <c r="F56" t="s">
-        <v>260</v>
-      </c>
-      <c r="G56" t="s">
-        <v>257</v>
-      </c>
-      <c r="H56" t="s">
-        <v>258</v>
       </c>
       <c r="I56" t="s">
         <v>25</v>
       </c>
       <c r="J56" t="s">
-        <v>175</v>
+        <v>26</v>
       </c>
       <c r="K56" t="s">
         <v>27</v>
@@ -4079,16 +4054,69 @@
         <v>29</v>
       </c>
       <c r="N56" t="s">
-        <v>79</v>
+        <v>199</v>
       </c>
       <c r="O56" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="s">
-        <v>156</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>258</v>
+      </c>
+      <c r="D57" t="s">
+        <v>259</v>
+      </c>
+      <c r="E57" t="s">
+        <v>260</v>
+      </c>
+      <c r="F57" t="s">
+        <v>261</v>
+      </c>
+      <c r="G57" t="s">
+        <v>258</v>
+      </c>
+      <c r="H57" t="s">
+        <v>259</v>
+      </c>
+      <c r="I57" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" t="s">
+        <v>176</v>
+      </c>
+      <c r="K57" t="s">
+        <v>27</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" t="s">
+        <v>29</v>
+      </c>
+      <c r="N57" t="s">
+        <v>79</v>
+      </c>
+      <c r="O57" t="s">
+        <v>80</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential listing price</t>
   </si>
   <si>
     <t xml:space="preserve">median-listing-price</t>
@@ -2452,29 +2455,57 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
+      <c r="A26" t="s">
+        <v>118</v>
+      </c>
+      <c r="B26" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" t="s">
+        <v>129</v>
+      </c>
+      <c r="D26" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" t="s">
+        <v>138</v>
+      </c>
       <c r="H26" t="s">
-        <v>138</v>
-      </c>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
+        <v>139</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
       <c r="N26" t="s">
         <v>135</v>
       </c>
       <c r="O26" t="s">
         <v>136</v>
       </c>
-      <c r="P26"/>
-      <c r="Q26"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
@@ -2496,10 +2527,10 @@
         <v>132</v>
       </c>
       <c r="G27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I27" t="s">
         <v>25</v>
@@ -2549,10 +2580,10 @@
         <v>132</v>
       </c>
       <c r="G28" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I28" t="s">
         <v>25</v>
@@ -2602,10 +2633,10 @@
         <v>132</v>
       </c>
       <c r="G29" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I29" t="s">
         <v>25</v>
@@ -2655,10 +2686,10 @@
         <v>132</v>
       </c>
       <c r="G30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I30" t="s">
         <v>25</v>
@@ -2696,22 +2727,22 @@
         <v>119</v>
       </c>
       <c r="C31" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D31" t="s">
+        <v>149</v>
+      </c>
+      <c r="E31" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" t="s">
+        <v>151</v>
+      </c>
+      <c r="G31" t="s">
         <v>148</v>
       </c>
-      <c r="E31" t="s">
+      <c r="H31" t="s">
         <v>149</v>
-      </c>
-      <c r="F31" t="s">
-        <v>150</v>
-      </c>
-      <c r="G31" t="s">
-        <v>147</v>
-      </c>
-      <c r="H31" t="s">
-        <v>148</v>
       </c>
       <c r="I31" t="s">
         <v>25</v>
@@ -2743,34 +2774,34 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E32" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F32" t="s">
         <v>123</v>
       </c>
       <c r="G32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I32" t="s">
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K32" t="s">
         <v>27</v>
@@ -2791,33 +2822,33 @@
         <v>0</v>
       </c>
       <c r="Q32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" t="s">
         <v>159</v>
       </c>
-      <c r="E33" t="s">
-        <v>158</v>
-      </c>
       <c r="F33" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" t="s">
+        <v>159</v>
+      </c>
+      <c r="H33" t="s">
         <v>160</v>
-      </c>
-      <c r="G33" t="s">
-        <v>158</v>
-      </c>
-      <c r="H33" t="s">
-        <v>159</v>
       </c>
       <c r="I33" t="s">
         <v>25</v>
@@ -2835,42 +2866,42 @@
         <v>94</v>
       </c>
       <c r="N33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H34" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
@@ -2888,57 +2919,57 @@
         <v>94</v>
       </c>
       <c r="N34" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O34" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I35" t="s">
         <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K35" t="s">
         <v>27</v>
       </c>
       <c r="L35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N35" t="s">
         <v>30</v>
@@ -2955,28 +2986,28 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C36" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I36" t="s">
         <v>25</v>
@@ -3008,28 +3039,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G37" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="I37" t="s">
         <v>25</v>
@@ -3061,28 +3092,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G38" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I38" t="s">
         <v>25</v>
@@ -3120,22 +3151,22 @@
         <v>85</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
+        <v>191</v>
+      </c>
+      <c r="E39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F39" t="s">
+        <v>193</v>
+      </c>
+      <c r="G39" t="s">
         <v>190</v>
       </c>
-      <c r="E39" t="s">
+      <c r="H39" t="s">
         <v>191</v>
-      </c>
-      <c r="F39" t="s">
-        <v>192</v>
-      </c>
-      <c r="G39" t="s">
-        <v>189</v>
-      </c>
-      <c r="H39" t="s">
-        <v>190</v>
       </c>
       <c r="I39" t="s">
         <v>25</v>
@@ -3167,28 +3198,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D40" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" t="s">
+        <v>198</v>
+      </c>
+      <c r="F40" t="s">
+        <v>199</v>
+      </c>
+      <c r="G40" t="s">
         <v>196</v>
       </c>
-      <c r="E40" t="s">
+      <c r="H40" t="s">
         <v>197</v>
-      </c>
-      <c r="F40" t="s">
-        <v>198</v>
-      </c>
-      <c r="G40" t="s">
-        <v>195</v>
-      </c>
-      <c r="H40" t="s">
-        <v>196</v>
       </c>
       <c r="I40" t="s">
         <v>25</v>
@@ -3206,10 +3237,10 @@
         <v>29</v>
       </c>
       <c r="N40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3220,28 +3251,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D41" t="s">
+        <v>203</v>
+      </c>
+      <c r="E41" t="s">
+        <v>204</v>
+      </c>
+      <c r="F41" t="s">
+        <v>199</v>
+      </c>
+      <c r="G41" t="s">
         <v>202</v>
       </c>
-      <c r="E41" t="s">
+      <c r="H41" t="s">
         <v>203</v>
-      </c>
-      <c r="F41" t="s">
-        <v>198</v>
-      </c>
-      <c r="G41" t="s">
-        <v>201</v>
-      </c>
-      <c r="H41" t="s">
-        <v>202</v>
       </c>
       <c r="I41" t="s">
         <v>25</v>
@@ -3259,10 +3290,10 @@
         <v>29</v>
       </c>
       <c r="N41" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O41" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3273,28 +3304,28 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I42" t="s">
         <v>41</v>
@@ -3312,42 +3343,42 @@
         <v>29</v>
       </c>
       <c r="N42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I43" t="s">
         <v>41</v>
@@ -3365,42 +3396,42 @@
         <v>29</v>
       </c>
       <c r="N43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="I44" t="s">
         <v>41</v>
@@ -3418,42 +3449,42 @@
         <v>29</v>
       </c>
       <c r="N44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s">
         <v>40</v>
       </c>
       <c r="G45" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I45" t="s">
         <v>41</v>
@@ -3491,22 +3522,22 @@
         <v>18</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I46" t="s">
         <v>25</v>
@@ -3524,51 +3555,51 @@
         <v>94</v>
       </c>
       <c r="N46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E47" t="s">
+        <v>230</v>
+      </c>
+      <c r="F47" t="s">
+        <v>231</v>
+      </c>
+      <c r="G47" t="s">
+        <v>230</v>
+      </c>
+      <c r="H47" t="s">
         <v>229</v>
       </c>
-      <c r="F47" t="s">
-        <v>230</v>
-      </c>
-      <c r="G47" t="s">
-        <v>229</v>
-      </c>
-      <c r="H47" t="s">
-        <v>228</v>
-      </c>
       <c r="I47" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J47" t="s">
         <v>26</v>
       </c>
       <c r="K47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L47" t="s">
         <v>28</v>
@@ -3577,51 +3608,51 @@
         <v>29</v>
       </c>
       <c r="N47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B48" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D48" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E48" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F48" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G48" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H48" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J48" t="s">
         <v>126</v>
       </c>
       <c r="K48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s">
         <v>28</v>
@@ -3630,51 +3661,51 @@
         <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F49" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G49" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I49" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J49" t="s">
         <v>126</v>
       </c>
       <c r="K49" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L49" t="s">
         <v>28</v>
@@ -3683,51 +3714,51 @@
         <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O49" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F50" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H50" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I50" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J50" t="s">
         <v>126</v>
       </c>
       <c r="K50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L50" t="s">
         <v>28</v>
@@ -3736,51 +3767,51 @@
         <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D51" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I51" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J51" t="s">
         <v>126</v>
       </c>
       <c r="K51" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L51" t="s">
         <v>28</v>
@@ -3789,51 +3820,51 @@
         <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O51" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D52" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E52" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I52" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J52" t="s">
         <v>126</v>
       </c>
       <c r="K52" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L52" t="s">
         <v>28</v>
@@ -3842,51 +3873,51 @@
         <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O52" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
       <c r="Q52" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D53" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F53" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G53" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H53" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I53" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J53" t="s">
         <v>126</v>
       </c>
       <c r="K53" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L53" t="s">
         <v>28</v>
@@ -3895,51 +3926,51 @@
         <v>29</v>
       </c>
       <c r="N53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O53" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
       <c r="Q53" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B54" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D54" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F54" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G54" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H54" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I54" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J54" t="s">
         <v>126</v>
       </c>
       <c r="K54" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L54" t="s">
         <v>28</v>
@@ -3948,51 +3979,51 @@
         <v>29</v>
       </c>
       <c r="N54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O54" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
       <c r="Q54" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C55" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D55" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E55" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G55" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I55" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J55" t="s">
         <v>126</v>
       </c>
       <c r="K55" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="L55" t="s">
         <v>28</v>
@@ -4001,42 +4032,42 @@
         <v>29</v>
       </c>
       <c r="N55" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O55" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
       <c r="Q55" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D56" t="s">
+        <v>255</v>
+      </c>
+      <c r="E56" t="s">
+        <v>256</v>
+      </c>
+      <c r="F56" t="s">
+        <v>257</v>
+      </c>
+      <c r="G56" t="s">
         <v>254</v>
       </c>
-      <c r="E56" t="s">
-        <v>255</v>
-      </c>
-      <c r="F56" t="s">
-        <v>256</v>
-      </c>
-      <c r="G56" t="s">
-        <v>253</v>
-      </c>
       <c r="H56" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="I56" t="s">
         <v>25</v>
@@ -4054,10 +4085,10 @@
         <v>29</v>
       </c>
       <c r="N56" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -4074,28 +4105,28 @@
         <v>18</v>
       </c>
       <c r="C57" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
+        <v>260</v>
+      </c>
+      <c r="E57" t="s">
+        <v>261</v>
+      </c>
+      <c r="F57" t="s">
+        <v>262</v>
+      </c>
+      <c r="G57" t="s">
         <v>259</v>
       </c>
-      <c r="E57" t="s">
+      <c r="H57" t="s">
         <v>260</v>
-      </c>
-      <c r="F57" t="s">
-        <v>261</v>
-      </c>
-      <c r="G57" t="s">
-        <v>258</v>
-      </c>
-      <c r="H57" t="s">
-        <v>259</v>
       </c>
       <c r="I57" t="s">
         <v>25</v>
       </c>
       <c r="J57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K57" t="s">
         <v>27</v>
@@ -4116,7 +4147,7 @@
         <v>0</v>
       </c>
       <c r="Q57" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="264">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t xml:space="preserve">level.map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level.rev</t>
   </si>
   <si>
     <t xml:space="preserve">vintage</t>
@@ -1181,2973 +1184,3144 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="s">
-        <v>32</v>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
         <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="s">
-        <v>32</v>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
       <c r="I5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
-      <c r="Q5" t="s">
-        <v>47</v>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
-      <c r="Q6" t="s">
-        <v>55</v>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>58</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" t="s">
+        <v>45</v>
+      </c>
+      <c r="N7" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
         <v>56</v>
-      </c>
-      <c r="H7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N7" t="s">
-        <v>30</v>
-      </c>
-      <c r="O7" t="s">
-        <v>31</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="s">
-        <v>55</v>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
+        <v>65</v>
+      </c>
+      <c r="F9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" t="s">
         <v>64</v>
       </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" t="s">
-        <v>63</v>
-      </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="s">
-        <v>55</v>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="s">
-        <v>72</v>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" t="s">
-        <v>81</v>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" t="s">
+        <v>84</v>
+      </c>
+      <c r="I12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s">
+        <v>44</v>
+      </c>
+      <c r="M12" t="s">
+        <v>45</v>
+      </c>
+      <c r="N12" t="s">
+        <v>80</v>
+      </c>
+      <c r="O12" t="s">
+        <v>81</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
         <v>82</v>
-      </c>
-      <c r="H12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" t="s">
-        <v>25</v>
-      </c>
-      <c r="J12" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" t="s">
-        <v>43</v>
-      </c>
-      <c r="M12" t="s">
-        <v>44</v>
-      </c>
-      <c r="N12" t="s">
-        <v>79</v>
-      </c>
-      <c r="O12" t="s">
-        <v>80</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="s">
-        <v>95</v>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" t="s">
+        <v>26</v>
+      </c>
+      <c r="J14" t="s">
+        <v>92</v>
+      </c>
+      <c r="K14" t="s">
+        <v>93</v>
+      </c>
+      <c r="L14" t="s">
+        <v>94</v>
+      </c>
+      <c r="M14" t="s">
+        <v>95</v>
+      </c>
+      <c r="N14" t="s">
+        <v>80</v>
+      </c>
+      <c r="O14" t="s">
+        <v>81</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="s">
         <v>96</v>
-      </c>
-      <c r="H14" t="s">
-        <v>97</v>
-      </c>
-      <c r="I14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" t="s">
-        <v>91</v>
-      </c>
-      <c r="K14" t="s">
-        <v>92</v>
-      </c>
-      <c r="L14" t="s">
-        <v>93</v>
-      </c>
-      <c r="M14" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" t="s">
-        <v>79</v>
-      </c>
-      <c r="O14" t="s">
-        <v>80</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
-      <c r="Q15" t="s">
-        <v>95</v>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="s">
-        <v>95</v>
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" t="s">
-        <v>95</v>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
-      <c r="Q18" t="s">
-        <v>95</v>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
-      <c r="Q19" t="s">
-        <v>72</v>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
-      <c r="Q20" t="s">
-        <v>72</v>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E21" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F21" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O21" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
       </c>
-      <c r="Q21" t="s">
-        <v>72</v>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O22" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="s">
-        <v>72</v>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E23" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G23" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J23" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N23" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="s">
-        <v>47</v>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F24" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G24" t="s">
+        <v>128</v>
+      </c>
+      <c r="H24" t="s">
+        <v>129</v>
+      </c>
+      <c r="I24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" t="s">
         <v>127</v>
       </c>
-      <c r="H24" t="s">
-        <v>128</v>
-      </c>
-      <c r="I24" t="s">
-        <v>41</v>
-      </c>
-      <c r="J24" t="s">
-        <v>126</v>
-      </c>
       <c r="K24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
       </c>
-      <c r="Q24" t="s">
-        <v>47</v>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D25" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="s">
-        <v>137</v>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G26" t="s">
+        <v>139</v>
+      </c>
+      <c r="H26" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K26" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s">
+        <v>30</v>
+      </c>
+      <c r="N26" t="s">
+        <v>136</v>
+      </c>
+      <c r="O26" t="s">
+        <v>137</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
         <v>138</v>
-      </c>
-      <c r="H26" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" t="s">
-        <v>54</v>
-      </c>
-      <c r="K26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" t="s">
-        <v>28</v>
-      </c>
-      <c r="M26" t="s">
-        <v>29</v>
-      </c>
-      <c r="N26" t="s">
-        <v>135</v>
-      </c>
-      <c r="O26" t="s">
-        <v>136</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B27" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F27" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="s">
-        <v>137</v>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G28" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
-      <c r="Q28" t="s">
-        <v>137</v>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F29" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G29" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
       </c>
-      <c r="Q29" t="s">
-        <v>137</v>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D30" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
       </c>
-      <c r="Q30" t="s">
-        <v>137</v>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
+        <v>150</v>
+      </c>
+      <c r="E31" t="s">
+        <v>151</v>
+      </c>
+      <c r="F31" t="s">
+        <v>152</v>
+      </c>
+      <c r="G31" t="s">
         <v>149</v>
       </c>
-      <c r="E31" t="s">
+      <c r="H31" t="s">
         <v>150</v>
       </c>
-      <c r="F31" t="s">
-        <v>151</v>
-      </c>
-      <c r="G31" t="s">
-        <v>148</v>
-      </c>
-      <c r="H31" t="s">
-        <v>149</v>
-      </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" t="s">
-        <v>137</v>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B32" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C32" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D32" t="s">
+        <v>156</v>
+      </c>
+      <c r="E32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" t="s">
+        <v>124</v>
+      </c>
+      <c r="G32" t="s">
         <v>155</v>
       </c>
-      <c r="E32" t="s">
+      <c r="H32" t="s">
         <v>156</v>
       </c>
-      <c r="F32" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" t="s">
-        <v>154</v>
-      </c>
-      <c r="H32" t="s">
-        <v>155</v>
-      </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="s">
-        <v>158</v>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C33" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" t="s">
+        <v>161</v>
+      </c>
+      <c r="E33" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" t="s">
+        <v>162</v>
+      </c>
+      <c r="G33" t="s">
+        <v>160</v>
+      </c>
+      <c r="H33" t="s">
+        <v>161</v>
+      </c>
+      <c r="I33" t="s">
+        <v>26</v>
+      </c>
+      <c r="J33" t="s">
+        <v>27</v>
+      </c>
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>94</v>
+      </c>
+      <c r="M33" t="s">
+        <v>95</v>
+      </c>
+      <c r="N33" t="s">
+        <v>163</v>
+      </c>
+      <c r="O33" t="s">
+        <v>164</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="s">
         <v>159</v>
-      </c>
-      <c r="D33" t="s">
-        <v>160</v>
-      </c>
-      <c r="E33" t="s">
-        <v>159</v>
-      </c>
-      <c r="F33" t="s">
-        <v>161</v>
-      </c>
-      <c r="G33" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" t="s">
-        <v>160</v>
-      </c>
-      <c r="I33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" t="s">
-        <v>93</v>
-      </c>
-      <c r="M33" t="s">
-        <v>94</v>
-      </c>
-      <c r="N33" t="s">
-        <v>162</v>
-      </c>
-      <c r="O33" t="s">
-        <v>163</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F34" t="s">
+        <v>162</v>
+      </c>
+      <c r="G34" t="s">
+        <v>168</v>
+      </c>
+      <c r="H34" t="s">
+        <v>169</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" t="s">
+        <v>55</v>
+      </c>
+      <c r="K34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" t="s">
+        <v>94</v>
+      </c>
+      <c r="M34" t="s">
+        <v>95</v>
+      </c>
+      <c r="N34" t="s">
+        <v>163</v>
+      </c>
+      <c r="O34" t="s">
         <v>164</v>
       </c>
-      <c r="D34" t="s">
-        <v>165</v>
-      </c>
-      <c r="E34" t="s">
-        <v>166</v>
-      </c>
-      <c r="F34" t="s">
-        <v>161</v>
-      </c>
-      <c r="G34" t="s">
-        <v>167</v>
-      </c>
-      <c r="H34" t="s">
-        <v>168</v>
-      </c>
-      <c r="I34" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" t="s">
-        <v>54</v>
-      </c>
-      <c r="K34" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" t="s">
-        <v>93</v>
-      </c>
-      <c r="M34" t="s">
-        <v>94</v>
-      </c>
-      <c r="N34" t="s">
-        <v>162</v>
-      </c>
-      <c r="O34" t="s">
-        <v>163</v>
-      </c>
       <c r="P34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="s">
-        <v>158</v>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="s">
-        <v>72</v>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C36" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" t="s">
-        <v>55</v>
+      <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B37" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G37" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" t="s">
-        <v>55</v>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C38" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F38" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O38" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
-      <c r="Q38" t="s">
-        <v>55</v>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D39" t="s">
+        <v>192</v>
+      </c>
+      <c r="E39" t="s">
+        <v>193</v>
+      </c>
+      <c r="F39" t="s">
+        <v>194</v>
+      </c>
+      <c r="G39" t="s">
         <v>191</v>
       </c>
-      <c r="E39" t="s">
+      <c r="H39" t="s">
         <v>192</v>
       </c>
-      <c r="F39" t="s">
-        <v>193</v>
-      </c>
-      <c r="G39" t="s">
-        <v>190</v>
-      </c>
-      <c r="H39" t="s">
-        <v>191</v>
-      </c>
       <c r="I39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
-      <c r="Q39" t="s">
-        <v>55</v>
+      <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D40" t="s">
+        <v>198</v>
+      </c>
+      <c r="E40" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" t="s">
+        <v>200</v>
+      </c>
+      <c r="G40" t="s">
         <v>197</v>
       </c>
-      <c r="E40" t="s">
+      <c r="H40" t="s">
         <v>198</v>
       </c>
-      <c r="F40" t="s">
-        <v>199</v>
-      </c>
-      <c r="G40" t="s">
-        <v>196</v>
-      </c>
-      <c r="H40" t="s">
-        <v>197</v>
-      </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L40" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M40" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="s">
-        <v>81</v>
+      <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" t="s">
+        <v>203</v>
+      </c>
+      <c r="D41" t="s">
+        <v>204</v>
+      </c>
+      <c r="E41" t="s">
+        <v>205</v>
+      </c>
+      <c r="F41" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" t="s">
+        <v>203</v>
+      </c>
+      <c r="H41" t="s">
+        <v>204</v>
+      </c>
+      <c r="I41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" t="s">
+        <v>27</v>
+      </c>
+      <c r="K41" t="s">
+        <v>28</v>
+      </c>
+      <c r="L41" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" t="s">
+        <v>30</v>
+      </c>
+      <c r="N41" t="s">
+        <v>201</v>
+      </c>
+      <c r="O41" t="s">
         <v>202</v>
       </c>
-      <c r="D41" t="s">
-        <v>203</v>
-      </c>
-      <c r="E41" t="s">
-        <v>204</v>
-      </c>
-      <c r="F41" t="s">
-        <v>199</v>
-      </c>
-      <c r="G41" t="s">
-        <v>202</v>
-      </c>
-      <c r="H41" t="s">
-        <v>203</v>
-      </c>
-      <c r="I41" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" t="s">
-        <v>26</v>
-      </c>
-      <c r="K41" t="s">
-        <v>27</v>
-      </c>
-      <c r="L41" t="s">
-        <v>28</v>
-      </c>
-      <c r="M41" t="s">
-        <v>29</v>
-      </c>
-      <c r="N41" t="s">
-        <v>200</v>
-      </c>
-      <c r="O41" t="s">
-        <v>201</v>
-      </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
-      <c r="Q41" t="s">
-        <v>81</v>
+      <c r="Q41" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I42" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O42" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
-      <c r="Q42" t="s">
-        <v>213</v>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G43" t="s">
+        <v>215</v>
+      </c>
+      <c r="H43" t="s">
+        <v>216</v>
+      </c>
+      <c r="I43" t="s">
+        <v>42</v>
+      </c>
+      <c r="J43" t="s">
+        <v>92</v>
+      </c>
+      <c r="K43" t="s">
+        <v>93</v>
+      </c>
+      <c r="L43" t="s">
+        <v>29</v>
+      </c>
+      <c r="M43" t="s">
+        <v>30</v>
+      </c>
+      <c r="N43" t="s">
+        <v>212</v>
+      </c>
+      <c r="O43" t="s">
+        <v>213</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1</v>
+      </c>
+      <c r="R43" t="s">
         <v>214</v>
-      </c>
-      <c r="H43" t="s">
-        <v>215</v>
-      </c>
-      <c r="I43" t="s">
-        <v>41</v>
-      </c>
-      <c r="J43" t="s">
-        <v>91</v>
-      </c>
-      <c r="K43" t="s">
-        <v>92</v>
-      </c>
-      <c r="L43" t="s">
-        <v>28</v>
-      </c>
-      <c r="M43" t="s">
-        <v>29</v>
-      </c>
-      <c r="N43" t="s">
-        <v>211</v>
-      </c>
-      <c r="O43" t="s">
-        <v>212</v>
-      </c>
-      <c r="P43" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B44" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D44" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F44" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I44" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O44" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" t="s">
-        <v>213</v>
+      <c r="Q44" t="n">
+        <v>1</v>
+      </c>
+      <c r="R44" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C45" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D45" t="s">
+        <v>220</v>
+      </c>
+      <c r="E45" t="s">
+        <v>221</v>
+      </c>
+      <c r="F45" t="s">
+        <v>41</v>
+      </c>
+      <c r="G45" t="s">
         <v>219</v>
       </c>
-      <c r="E45" t="s">
+      <c r="H45" t="s">
         <v>220</v>
       </c>
-      <c r="F45" t="s">
-        <v>40</v>
-      </c>
-      <c r="G45" t="s">
-        <v>218</v>
-      </c>
-      <c r="H45" t="s">
-        <v>219</v>
-      </c>
       <c r="I45" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J45" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L45" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" t="s">
-        <v>47</v>
+      <c r="Q45" t="n">
+        <v>1</v>
+      </c>
+      <c r="R45" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L46" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M46" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="s">
-        <v>158</v>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E47" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" t="s">
+        <v>232</v>
+      </c>
+      <c r="G47" t="s">
+        <v>231</v>
+      </c>
+      <c r="H47" t="s">
         <v>230</v>
       </c>
-      <c r="F47" t="s">
-        <v>231</v>
-      </c>
-      <c r="G47" t="s">
-        <v>230</v>
-      </c>
-      <c r="H47" t="s">
-        <v>229</v>
-      </c>
       <c r="I47" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K47" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L47" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M47" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O47" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" t="s">
-        <v>213</v>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
+        <v>236</v>
+      </c>
+      <c r="D48" t="s">
+        <v>237</v>
+      </c>
+      <c r="E48" t="s">
+        <v>238</v>
+      </c>
+      <c r="F48" t="s">
+        <v>232</v>
+      </c>
+      <c r="G48" t="s">
+        <v>239</v>
+      </c>
+      <c r="H48" t="s">
+        <v>240</v>
+      </c>
+      <c r="I48" t="s">
+        <v>233</v>
+      </c>
+      <c r="J48" t="s">
+        <v>127</v>
+      </c>
+      <c r="K48" t="s">
+        <v>234</v>
+      </c>
+      <c r="L48" t="s">
+        <v>29</v>
+      </c>
+      <c r="M48" t="s">
+        <v>30</v>
+      </c>
+      <c r="N48" t="s">
         <v>235</v>
       </c>
-      <c r="D48" t="s">
-        <v>236</v>
-      </c>
-      <c r="E48" t="s">
-        <v>237</v>
-      </c>
-      <c r="F48" t="s">
-        <v>231</v>
-      </c>
-      <c r="G48" t="s">
-        <v>238</v>
-      </c>
-      <c r="H48" t="s">
-        <v>239</v>
-      </c>
-      <c r="I48" t="s">
-        <v>232</v>
-      </c>
-      <c r="J48" t="s">
-        <v>126</v>
-      </c>
-      <c r="K48" t="s">
-        <v>233</v>
-      </c>
-      <c r="L48" t="s">
-        <v>28</v>
-      </c>
-      <c r="M48" t="s">
-        <v>29</v>
-      </c>
-      <c r="N48" t="s">
-        <v>234</v>
-      </c>
       <c r="O48" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
-      <c r="Q48" t="s">
-        <v>213</v>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
+        <v>236</v>
+      </c>
+      <c r="D49" t="s">
+        <v>237</v>
+      </c>
+      <c r="E49" t="s">
+        <v>238</v>
+      </c>
+      <c r="F49" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" t="s">
+        <v>241</v>
+      </c>
+      <c r="H49" t="s">
+        <v>242</v>
+      </c>
+      <c r="I49" t="s">
+        <v>233</v>
+      </c>
+      <c r="J49" t="s">
+        <v>127</v>
+      </c>
+      <c r="K49" t="s">
+        <v>234</v>
+      </c>
+      <c r="L49" t="s">
+        <v>29</v>
+      </c>
+      <c r="M49" t="s">
+        <v>30</v>
+      </c>
+      <c r="N49" t="s">
         <v>235</v>
       </c>
-      <c r="D49" t="s">
-        <v>236</v>
-      </c>
-      <c r="E49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F49" t="s">
-        <v>231</v>
-      </c>
-      <c r="G49" t="s">
-        <v>240</v>
-      </c>
-      <c r="H49" t="s">
-        <v>241</v>
-      </c>
-      <c r="I49" t="s">
-        <v>232</v>
-      </c>
-      <c r="J49" t="s">
-        <v>126</v>
-      </c>
-      <c r="K49" t="s">
-        <v>233</v>
-      </c>
-      <c r="L49" t="s">
-        <v>28</v>
-      </c>
-      <c r="M49" t="s">
-        <v>29</v>
-      </c>
-      <c r="N49" t="s">
-        <v>234</v>
-      </c>
       <c r="O49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="Q49" t="s">
-        <v>213</v>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" t="s">
+        <v>238</v>
+      </c>
+      <c r="F50" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" t="s">
+        <v>243</v>
+      </c>
+      <c r="H50" t="s">
+        <v>244</v>
+      </c>
+      <c r="I50" t="s">
+        <v>233</v>
+      </c>
+      <c r="J50" t="s">
+        <v>127</v>
+      </c>
+      <c r="K50" t="s">
+        <v>234</v>
+      </c>
+      <c r="L50" t="s">
+        <v>29</v>
+      </c>
+      <c r="M50" t="s">
+        <v>30</v>
+      </c>
+      <c r="N50" t="s">
         <v>235</v>
       </c>
-      <c r="D50" t="s">
-        <v>236</v>
-      </c>
-      <c r="E50" t="s">
-        <v>237</v>
-      </c>
-      <c r="F50" t="s">
-        <v>231</v>
-      </c>
-      <c r="G50" t="s">
-        <v>242</v>
-      </c>
-      <c r="H50" t="s">
-        <v>243</v>
-      </c>
-      <c r="I50" t="s">
-        <v>232</v>
-      </c>
-      <c r="J50" t="s">
-        <v>126</v>
-      </c>
-      <c r="K50" t="s">
-        <v>233</v>
-      </c>
-      <c r="L50" t="s">
-        <v>28</v>
-      </c>
-      <c r="M50" t="s">
-        <v>29</v>
-      </c>
-      <c r="N50" t="s">
-        <v>234</v>
-      </c>
       <c r="O50" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
-      <c r="Q50" t="s">
-        <v>213</v>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
+        <v>236</v>
+      </c>
+      <c r="D51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E51" t="s">
+        <v>238</v>
+      </c>
+      <c r="F51" t="s">
+        <v>232</v>
+      </c>
+      <c r="G51" t="s">
+        <v>245</v>
+      </c>
+      <c r="H51" t="s">
+        <v>246</v>
+      </c>
+      <c r="I51" t="s">
+        <v>233</v>
+      </c>
+      <c r="J51" t="s">
+        <v>127</v>
+      </c>
+      <c r="K51" t="s">
+        <v>234</v>
+      </c>
+      <c r="L51" t="s">
+        <v>29</v>
+      </c>
+      <c r="M51" t="s">
+        <v>30</v>
+      </c>
+      <c r="N51" t="s">
         <v>235</v>
       </c>
-      <c r="D51" t="s">
-        <v>236</v>
-      </c>
-      <c r="E51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F51" t="s">
-        <v>231</v>
-      </c>
-      <c r="G51" t="s">
-        <v>244</v>
-      </c>
-      <c r="H51" t="s">
-        <v>245</v>
-      </c>
-      <c r="I51" t="s">
-        <v>232</v>
-      </c>
-      <c r="J51" t="s">
-        <v>126</v>
-      </c>
-      <c r="K51" t="s">
-        <v>233</v>
-      </c>
-      <c r="L51" t="s">
-        <v>28</v>
-      </c>
-      <c r="M51" t="s">
-        <v>29</v>
-      </c>
-      <c r="N51" t="s">
-        <v>234</v>
-      </c>
       <c r="O51" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="s">
-        <v>213</v>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
+        <v>236</v>
+      </c>
+      <c r="D52" t="s">
+        <v>237</v>
+      </c>
+      <c r="E52" t="s">
+        <v>238</v>
+      </c>
+      <c r="F52" t="s">
+        <v>232</v>
+      </c>
+      <c r="G52" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" t="s">
+        <v>248</v>
+      </c>
+      <c r="I52" t="s">
+        <v>233</v>
+      </c>
+      <c r="J52" t="s">
+        <v>127</v>
+      </c>
+      <c r="K52" t="s">
+        <v>234</v>
+      </c>
+      <c r="L52" t="s">
+        <v>29</v>
+      </c>
+      <c r="M52" t="s">
+        <v>30</v>
+      </c>
+      <c r="N52" t="s">
         <v>235</v>
       </c>
-      <c r="D52" t="s">
-        <v>236</v>
-      </c>
-      <c r="E52" t="s">
-        <v>237</v>
-      </c>
-      <c r="F52" t="s">
-        <v>231</v>
-      </c>
-      <c r="G52" t="s">
-        <v>246</v>
-      </c>
-      <c r="H52" t="s">
-        <v>247</v>
-      </c>
-      <c r="I52" t="s">
-        <v>232</v>
-      </c>
-      <c r="J52" t="s">
-        <v>126</v>
-      </c>
-      <c r="K52" t="s">
-        <v>233</v>
-      </c>
-      <c r="L52" t="s">
-        <v>28</v>
-      </c>
-      <c r="M52" t="s">
-        <v>29</v>
-      </c>
-      <c r="N52" t="s">
-        <v>234</v>
-      </c>
       <c r="O52" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="s">
-        <v>213</v>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C53" t="s">
+        <v>236</v>
+      </c>
+      <c r="D53" t="s">
+        <v>237</v>
+      </c>
+      <c r="E53" t="s">
+        <v>238</v>
+      </c>
+      <c r="F53" t="s">
+        <v>232</v>
+      </c>
+      <c r="G53" t="s">
+        <v>249</v>
+      </c>
+      <c r="H53" t="s">
+        <v>250</v>
+      </c>
+      <c r="I53" t="s">
+        <v>233</v>
+      </c>
+      <c r="J53" t="s">
+        <v>127</v>
+      </c>
+      <c r="K53" t="s">
+        <v>234</v>
+      </c>
+      <c r="L53" t="s">
+        <v>29</v>
+      </c>
+      <c r="M53" t="s">
+        <v>30</v>
+      </c>
+      <c r="N53" t="s">
         <v>235</v>
       </c>
-      <c r="D53" t="s">
-        <v>236</v>
-      </c>
-      <c r="E53" t="s">
-        <v>237</v>
-      </c>
-      <c r="F53" t="s">
-        <v>231</v>
-      </c>
-      <c r="G53" t="s">
-        <v>248</v>
-      </c>
-      <c r="H53" t="s">
-        <v>249</v>
-      </c>
-      <c r="I53" t="s">
-        <v>232</v>
-      </c>
-      <c r="J53" t="s">
-        <v>126</v>
-      </c>
-      <c r="K53" t="s">
-        <v>233</v>
-      </c>
-      <c r="L53" t="s">
-        <v>28</v>
-      </c>
-      <c r="M53" t="s">
-        <v>29</v>
-      </c>
-      <c r="N53" t="s">
-        <v>234</v>
-      </c>
       <c r="O53" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="s">
-        <v>213</v>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B54" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C54" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" t="s">
+        <v>237</v>
+      </c>
+      <c r="E54" t="s">
+        <v>238</v>
+      </c>
+      <c r="F54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G54" t="s">
+        <v>251</v>
+      </c>
+      <c r="H54" t="s">
+        <v>252</v>
+      </c>
+      <c r="I54" t="s">
+        <v>233</v>
+      </c>
+      <c r="J54" t="s">
+        <v>127</v>
+      </c>
+      <c r="K54" t="s">
+        <v>234</v>
+      </c>
+      <c r="L54" t="s">
+        <v>29</v>
+      </c>
+      <c r="M54" t="s">
+        <v>30</v>
+      </c>
+      <c r="N54" t="s">
         <v>235</v>
       </c>
-      <c r="D54" t="s">
-        <v>236</v>
-      </c>
-      <c r="E54" t="s">
-        <v>237</v>
-      </c>
-      <c r="F54" t="s">
-        <v>231</v>
-      </c>
-      <c r="G54" t="s">
-        <v>250</v>
-      </c>
-      <c r="H54" t="s">
-        <v>251</v>
-      </c>
-      <c r="I54" t="s">
-        <v>232</v>
-      </c>
-      <c r="J54" t="s">
-        <v>126</v>
-      </c>
-      <c r="K54" t="s">
-        <v>233</v>
-      </c>
-      <c r="L54" t="s">
-        <v>28</v>
-      </c>
-      <c r="M54" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" t="s">
-        <v>234</v>
-      </c>
       <c r="O54" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" t="s">
-        <v>213</v>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B55" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C55" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D55" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F55" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="G55" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I55" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="J55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K55" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O55" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="s">
-        <v>213</v>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C56" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
+        <v>256</v>
+      </c>
+      <c r="E56" t="s">
+        <v>257</v>
+      </c>
+      <c r="F56" t="s">
+        <v>258</v>
+      </c>
+      <c r="G56" t="s">
         <v>255</v>
       </c>
-      <c r="E56" t="s">
-        <v>256</v>
-      </c>
-      <c r="F56" t="s">
-        <v>257</v>
-      </c>
-      <c r="G56" t="s">
-        <v>254</v>
-      </c>
       <c r="H56" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J56" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N56" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="O56" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="s">
-        <v>81</v>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D57" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" t="s">
+        <v>262</v>
+      </c>
+      <c r="F57" t="s">
+        <v>263</v>
+      </c>
+      <c r="G57" t="s">
         <v>260</v>
       </c>
-      <c r="E57" t="s">
+      <c r="H57" t="s">
         <v>261</v>
       </c>
-      <c r="F57" t="s">
-        <v>262</v>
-      </c>
-      <c r="G57" t="s">
-        <v>259</v>
-      </c>
-      <c r="H57" t="s">
-        <v>260</v>
-      </c>
       <c r="I57" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J57" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K57" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="s">
-        <v>158</v>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -68,6 +68,66 @@
     <t xml:space="preserve">vintage</t>
   </si>
   <si>
+    <t xml:space="preserve">Municipal Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">municipal-services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
+  </si>
+  <si>
     <t xml:space="preserve">Overall Economy</t>
   </si>
   <si>
@@ -86,48 +146,36 @@
     <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
   </si>
   <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total jobs</t>
   </si>
   <si>
     <t xml:space="preserve">jobs-total</t>
   </si>
   <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-03-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal government jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-federal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Commercial bankruptcy rate</t>
   </si>
   <si>
@@ -143,15 +191,63 @@
     <t xml:space="preserve">Q</t>
   </si>
   <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Rolling 12-month total</t>
   </si>
   <si>
     <t xml:space="preserve">rolling-12-sum</t>
   </si>
   <si>
+    <t xml:space="preserve">2025Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household Wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household-wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personal-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024Q4</t>
   </si>
   <si>
@@ -161,6 +257,483 @@
     <t xml:space="preserve">DMV-2026-03-04</t>
   </si>
   <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About the DMV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total-population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total population</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2025-12-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educational attainment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eduatt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Less than high school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">less-than-hs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school or equivalent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">high-school</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Some college or associate's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">some-college-aa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bachelors-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Graduate or professional degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">graduate-degree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High school degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hs-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree or higher, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ba-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of foreign-born population (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">foreign-born</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medicaid-enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State agency reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active listing count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active-listing-count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homes sold above list price (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homes-sold-above-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List-to-sale price ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list-to-sale-ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median days on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-dom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential listing price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-listing-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential sale price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-sale-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median square feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-square-feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median listing price per square foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlpsq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNAP participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snap-participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total air passengers served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-passengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
     <t xml:space="preserve">Federal obligations</t>
   </si>
   <si>
@@ -173,36 +746,24 @@
     <t xml:space="preserve">USASpending</t>
   </si>
   <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
     <t xml:space="preserve">Federal obligations, total</t>
   </si>
   <si>
     <t xml:space="preserve">federal-obligations-total</t>
   </si>
   <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Academic research funding</t>
   </si>
   <si>
@@ -215,378 +776,6 @@
     <t xml:space="preserve">Academic research funding obligated</t>
   </si>
   <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active residential for-sale listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential sale price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-sale-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median days on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List-to-sale price ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list-to-sale-ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homes sold above list price (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homes-sold-above-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
     <t xml:space="preserve">Mass layoff notifications</t>
   </si>
   <si>
@@ -597,213 +786,6 @@
   </si>
   <si>
     <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNAP participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snap-participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2025-12-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-prime consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-nearprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severely credit-constrained consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-subprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">personal-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About the DMV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">about</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">total-population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total population</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Census Bureau and Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">null</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attainment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eduatt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Less than high school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">less-than-hs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school or equivalent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">high-school</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Some college or associate's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">some-college-aa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bachelors-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Graduate or professional degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">graduate-degree</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High school degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hs-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bachelor's degree or higher, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ba-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign-born</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
   </si>
 </sst>
 </file>
@@ -1238,7 +1220,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="s">
         <v>33</v>
@@ -1294,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="s">
         <v>33</v>
@@ -1350,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="s">
         <v>33</v>
@@ -1358,105 +1340,105 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
         <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M5" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="E6" t="s">
+      <c r="H6" t="s">
         <v>51</v>
-      </c>
-      <c r="F6" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" t="s">
-        <v>54</v>
       </c>
       <c r="I6" t="s">
         <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
         <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M6" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N6" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="O6" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1465,54 +1447,54 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" t="s">
         <v>52</v>
       </c>
-      <c r="G7" t="s">
-        <v>57</v>
-      </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I7" t="s">
         <v>26</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="K7" t="s">
         <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N7" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="O7" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1521,307 +1503,307 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="J8" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
       </c>
       <c r="L8" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="N8" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="O8" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
         <v>65</v>
       </c>
-      <c r="F9" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>66</v>
       </c>
-      <c r="H9" t="s">
-        <v>64</v>
-      </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="J9" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K9" t="s">
         <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="N9" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="O9" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="J10" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="L10" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M10" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="O10" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" t="s">
         <v>76</v>
       </c>
-      <c r="F11" t="s">
+      <c r="K11" t="s">
         <v>77</v>
       </c>
-      <c r="G11" t="s">
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N11" t="s">
         <v>78</v>
       </c>
-      <c r="H11" t="s">
+      <c r="O11" t="s">
         <v>79</v>
       </c>
-      <c r="I11" t="s">
-        <v>26</v>
-      </c>
-      <c r="J11" t="s">
-        <v>55</v>
-      </c>
-      <c r="K11" t="s">
-        <v>28</v>
-      </c>
-      <c r="L11" t="s">
-        <v>44</v>
-      </c>
-      <c r="M11" t="s">
-        <v>45</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="s">
         <v>80</v>
-      </c>
-      <c r="O11" t="s">
-        <v>81</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s">
         <v>28</v>
       </c>
       <c r="L12" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M12" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N12" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="O12" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s">
         <v>90</v>
@@ -1833,358 +1815,358 @@
         <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K13" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L13" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="M13" t="s">
+        <v>30</v>
+      </c>
+      <c r="N13" t="s">
         <v>95</v>
       </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
       <c r="O13" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="G14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="H14" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I14" t="s">
         <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L14" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="M14" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" t="s">
         <v>95</v>
       </c>
-      <c r="N14" t="s">
-        <v>80</v>
-      </c>
       <c r="O14" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>102</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H15" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="I15" t="s">
         <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K15" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L15" t="s">
-        <v>94</v>
+        <v>59</v>
       </c>
       <c r="M15" t="s">
+        <v>60</v>
+      </c>
+      <c r="N15" t="s">
         <v>95</v>
       </c>
-      <c r="N15" t="s">
-        <v>80</v>
-      </c>
       <c r="O15" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="D16" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E16" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G16" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I16" t="s">
         <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="K16" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L16" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="M16" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N16" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="O16" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I17" t="s">
         <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K17" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N17" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="O17" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B18" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="H18" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="I18" t="s">
         <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L18" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N18" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="O18" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G19" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="I19" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="J19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K19" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="L19" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="M19" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="N19" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="O19" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2193,54 +2175,54 @@
         <v>0</v>
       </c>
       <c r="R19" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D20" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G20" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="H20" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="I20" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="J20" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="L20" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="M20" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="N20" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2249,54 +2231,54 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="F21" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="I21" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="J21" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K21" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="L21" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="M21" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="N21" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="O21" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2305,54 +2287,54 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>137</v>
       </c>
       <c r="E22" t="s">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="G22" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="H22" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="J22" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K22" t="s">
-        <v>28</v>
+        <v>133</v>
       </c>
       <c r="L22" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
       <c r="M22" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="N22" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="O22" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -2361,42 +2343,42 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B23" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="H23" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="I23" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="J23" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="K23" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s">
         <v>29</v>
@@ -2405,54 +2387,54 @@
         <v>30</v>
       </c>
       <c r="N23" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="O23" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B24" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F24" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G24" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="H24" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="I24" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="J24" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="K24" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="L24" t="s">
         <v>29</v>
@@ -2461,54 +2443,54 @@
         <v>30</v>
       </c>
       <c r="N24" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="O24" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="s">
-        <v>48</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C25" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D25" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" t="s">
         <v>131</v>
       </c>
-      <c r="E25" t="s">
+      <c r="G25" t="s">
+        <v>149</v>
+      </c>
+      <c r="H25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I25" t="s">
         <v>132</v>
       </c>
-      <c r="F25" t="s">
+      <c r="J25" t="s">
+        <v>76</v>
+      </c>
+      <c r="K25" t="s">
         <v>133</v>
-      </c>
-      <c r="G25" t="s">
-        <v>134</v>
-      </c>
-      <c r="H25" t="s">
-        <v>135</v>
-      </c>
-      <c r="I25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" t="s">
-        <v>28</v>
       </c>
       <c r="L25" t="s">
         <v>29</v>
@@ -2517,10 +2499,10 @@
         <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O25" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -2529,42 +2511,42 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C26" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" t="s">
         <v>131</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" t="s">
+        <v>152</v>
+      </c>
+      <c r="I26" t="s">
         <v>132</v>
       </c>
-      <c r="F26" t="s">
+      <c r="J26" t="s">
+        <v>76</v>
+      </c>
+      <c r="K26" t="s">
         <v>133</v>
-      </c>
-      <c r="G26" t="s">
-        <v>139</v>
-      </c>
-      <c r="H26" t="s">
-        <v>140</v>
-      </c>
-      <c r="I26" t="s">
-        <v>26</v>
-      </c>
-      <c r="J26" t="s">
-        <v>55</v>
-      </c>
-      <c r="K26" t="s">
-        <v>28</v>
       </c>
       <c r="L26" t="s">
         <v>29</v>
@@ -2573,10 +2555,10 @@
         <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O26" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
@@ -2585,42 +2567,42 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" t="s">
         <v>130</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>131</v>
       </c>
-      <c r="E27" t="s">
+      <c r="G27" t="s">
+        <v>153</v>
+      </c>
+      <c r="H27" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" t="s">
         <v>132</v>
       </c>
-      <c r="F27" t="s">
+      <c r="J27" t="s">
+        <v>76</v>
+      </c>
+      <c r="K27" t="s">
         <v>133</v>
-      </c>
-      <c r="G27" t="s">
-        <v>141</v>
-      </c>
-      <c r="H27" t="s">
-        <v>142</v>
-      </c>
-      <c r="I27" t="s">
-        <v>26</v>
-      </c>
-      <c r="J27" t="s">
-        <v>55</v>
-      </c>
-      <c r="K27" t="s">
-        <v>28</v>
       </c>
       <c r="L27" t="s">
         <v>29</v>
@@ -2629,10 +2611,10 @@
         <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="O27" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -2641,39 +2623,39 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="D28" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="E28" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="F28" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="G28" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H28" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="K28" t="s">
         <v>28</v>
@@ -2685,122 +2667,122 @@
         <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="O28" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>119</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="C29" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="E29" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="G29" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="H29" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="I29" t="s">
         <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L29" t="s">
-        <v>29</v>
+        <v>167</v>
       </c>
       <c r="M29" t="s">
-        <v>30</v>
+        <v>168</v>
       </c>
       <c r="N29" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="O29" t="s">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="C30" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D30" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="E30" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="F30" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="G30" t="s">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="H30" t="s">
-        <v>148</v>
+        <v>176</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="K30" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L30" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M30" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N30" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="O30" t="s">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2809,54 +2791,54 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="C31" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="D31" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="E31" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="F31" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="G31" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="H31" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K31" t="s">
         <v>28</v>
       </c>
       <c r="L31" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="N31" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="O31" t="s">
-        <v>137</v>
+        <v>186</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2865,89 +2847,89 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>138</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C32" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="F32" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="G32" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="H32" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>27</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
       </c>
       <c r="L32" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="N32" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="O32" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C33" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
+        <v>180</v>
       </c>
       <c r="E33" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="G33" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="H33" t="s">
-        <v>161</v>
+        <v>190</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2959,16 +2941,16 @@
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="M33" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N33" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="O33" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2977,54 +2959,54 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
       <c r="D34" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="E34" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
       <c r="F34" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="G34" t="s">
-        <v>168</v>
+        <v>191</v>
       </c>
       <c r="H34" t="s">
-        <v>169</v>
+        <v>192</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="K34" t="s">
         <v>28</v>
       </c>
       <c r="L34" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="M34" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N34" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="O34" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -3033,98 +3015,98 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="D35" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="E35" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="F35" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="G35" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="H35" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>179</v>
+        <v>29</v>
       </c>
       <c r="M35" t="s">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="N35" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="O35" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>73</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="L36" t="s">
         <v>29</v>
@@ -3133,54 +3115,54 @@
         <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="O36" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="P36" t="n">
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D37" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="E37" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F37" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G37" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="H37" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K37" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="L37" t="s">
         <v>29</v>
@@ -3189,51 +3171,51 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="O37" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>171</v>
+        <v>69</v>
       </c>
       <c r="C38" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="D38" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="E38" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="F38" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="G38" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H38" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
@@ -3245,107 +3227,107 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="O38" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="C39" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F39" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G39" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="H39" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K39" t="s">
         <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M39" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>31</v>
+        <v>185</v>
       </c>
       <c r="O39" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>56</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B40" t="s">
+        <v>69</v>
+      </c>
+      <c r="C40" t="s">
+        <v>193</v>
+      </c>
+      <c r="D40" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" t="s">
         <v>195</v>
       </c>
-      <c r="B40" t="s">
+      <c r="F40" t="s">
         <v>196</v>
       </c>
-      <c r="C40" t="s">
-        <v>197</v>
-      </c>
-      <c r="D40" t="s">
-        <v>198</v>
-      </c>
-      <c r="E40" t="s">
-        <v>199</v>
-      </c>
-      <c r="F40" t="s">
-        <v>200</v>
-      </c>
       <c r="G40" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="H40" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="K40" t="s">
         <v>28</v>
@@ -3357,51 +3339,51 @@
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="O40" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" t="s">
+        <v>193</v>
+      </c>
+      <c r="D41" t="s">
+        <v>194</v>
+      </c>
+      <c r="E41" t="s">
         <v>195</v>
       </c>
-      <c r="B41" t="s">
+      <c r="F41" t="s">
         <v>196</v>
       </c>
-      <c r="C41" t="s">
-        <v>203</v>
-      </c>
-      <c r="D41" t="s">
-        <v>204</v>
-      </c>
-      <c r="E41" t="s">
-        <v>205</v>
-      </c>
-      <c r="F41" t="s">
-        <v>200</v>
-      </c>
       <c r="G41" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="H41" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="K41" t="s">
         <v>28</v>
@@ -3413,54 +3395,54 @@
         <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="O41" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42" t="s">
         <v>195</v>
       </c>
-      <c r="B42" t="s">
+      <c r="F42" t="s">
         <v>196</v>
       </c>
-      <c r="C42" t="s">
-        <v>206</v>
-      </c>
-      <c r="D42" t="s">
-        <v>207</v>
-      </c>
-      <c r="E42" t="s">
-        <v>208</v>
-      </c>
-      <c r="F42" t="s">
-        <v>209</v>
-      </c>
       <c r="G42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I42" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K42" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L42" t="s">
         <v>29</v>
@@ -3469,54 +3451,54 @@
         <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="O42" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>69</v>
       </c>
       <c r="C43" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D43" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="E43" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F43" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="G43" t="s">
+        <v>214</v>
+      </c>
+      <c r="H43" t="s">
         <v>215</v>
       </c>
-      <c r="H43" t="s">
-        <v>216</v>
-      </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="K43" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L43" t="s">
         <v>29</v>
@@ -3525,54 +3507,54 @@
         <v>30</v>
       </c>
       <c r="N43" t="s">
-        <v>212</v>
+        <v>185</v>
       </c>
       <c r="O43" t="s">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="D44" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="E44" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F44" t="s">
-        <v>209</v>
+        <v>158</v>
       </c>
       <c r="G44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I44" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="K44" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="L44" t="s">
         <v>29</v>
@@ -3581,10 +3563,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="O44" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3593,390 +3575,390 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>214</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>195</v>
+        <v>83</v>
       </c>
       <c r="B45" t="s">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="C45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D45" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
+        <v>223</v>
+      </c>
+      <c r="F45" t="s">
+        <v>224</v>
+      </c>
+      <c r="G45" t="s">
         <v>221</v>
       </c>
-      <c r="F45" t="s">
-        <v>41</v>
-      </c>
-      <c r="G45" t="s">
-        <v>219</v>
-      </c>
       <c r="H45" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="I45" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K45" t="s">
         <v>28</v>
       </c>
       <c r="L45" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M45" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="O45" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="P45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>18</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>178</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F46" t="s">
-        <v>162</v>
+        <v>43</v>
       </c>
       <c r="G46" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="H46" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="I46" t="s">
         <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>55</v>
+        <v>231</v>
       </c>
       <c r="K46" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="L46" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="M46" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="N46" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="O46" t="s">
-        <v>164</v>
+        <v>32</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>177</v>
+      </c>
+      <c r="B47" t="s">
+        <v>178</v>
+      </c>
+      <c r="C47" t="s">
+        <v>226</v>
+      </c>
+      <c r="D47" t="s">
         <v>227</v>
       </c>
-      <c r="B47" t="s">
+      <c r="E47" t="s">
         <v>228</v>
       </c>
-      <c r="C47" t="s">
-        <v>229</v>
-      </c>
-      <c r="D47" t="s">
-        <v>230</v>
-      </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H47" t="s">
+        <v>233</v>
+      </c>
+      <c r="I47" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47" t="s">
         <v>231</v>
       </c>
-      <c r="F47" t="s">
-        <v>232</v>
-      </c>
-      <c r="G47" t="s">
-        <v>231</v>
-      </c>
-      <c r="H47" t="s">
-        <v>230</v>
-      </c>
-      <c r="I47" t="s">
-        <v>233</v>
-      </c>
-      <c r="J47" t="s">
-        <v>27</v>
-      </c>
       <c r="K47" t="s">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="L47" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="N47" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O47" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" t="s">
         <v>227</v>
       </c>
-      <c r="B48" t="s">
+      <c r="E48" t="s">
         <v>228</v>
       </c>
-      <c r="C48" t="s">
-        <v>236</v>
-      </c>
-      <c r="D48" t="s">
-        <v>237</v>
-      </c>
-      <c r="E48" t="s">
-        <v>238</v>
-      </c>
       <c r="F48" t="s">
-        <v>232</v>
+        <v>43</v>
       </c>
       <c r="G48" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="H48" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="I48" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="K48" t="s">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="L48" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="M48" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="N48" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O48" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>177</v>
+      </c>
+      <c r="B49" t="s">
+        <v>178</v>
+      </c>
+      <c r="C49" t="s">
+        <v>226</v>
+      </c>
+      <c r="D49" t="s">
         <v>227</v>
       </c>
-      <c r="B49" t="s">
+      <c r="E49" t="s">
         <v>228</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
+        <v>43</v>
+      </c>
+      <c r="G49" t="s">
         <v>236</v>
       </c>
-      <c r="D49" t="s">
+      <c r="H49" t="s">
         <v>237</v>
       </c>
-      <c r="E49" t="s">
-        <v>238</v>
-      </c>
-      <c r="F49" t="s">
-        <v>232</v>
-      </c>
-      <c r="G49" t="s">
-        <v>241</v>
-      </c>
-      <c r="H49" t="s">
-        <v>242</v>
-      </c>
       <c r="I49" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="K49" t="s">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="L49" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="M49" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="N49" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O49" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" t="s">
+        <v>178</v>
+      </c>
+      <c r="C50" t="s">
+        <v>226</v>
+      </c>
+      <c r="D50" t="s">
         <v>227</v>
       </c>
-      <c r="B50" t="s">
+      <c r="E50" t="s">
         <v>228</v>
       </c>
-      <c r="C50" t="s">
-        <v>236</v>
-      </c>
-      <c r="D50" t="s">
-        <v>237</v>
-      </c>
-      <c r="E50" t="s">
+      <c r="F50" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" t="s">
         <v>238</v>
       </c>
-      <c r="F50" t="s">
-        <v>232</v>
-      </c>
-      <c r="G50" t="s">
-        <v>243</v>
-      </c>
       <c r="H50" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I50" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J50" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="K50" t="s">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="L50" t="s">
-        <v>29</v>
+        <v>112</v>
       </c>
       <c r="M50" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="N50" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O50" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="s">
-        <v>214</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>227</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E51" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
+        <v>244</v>
+      </c>
+      <c r="H51" t="s">
         <v>245</v>
       </c>
-      <c r="H51" t="s">
-        <v>246</v>
-      </c>
       <c r="I51" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J51" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K51" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="L51" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M51" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N51" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O51" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3985,54 +3967,54 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>214</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>227</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E52" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F52" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G52" t="s">
+        <v>246</v>
+      </c>
+      <c r="H52" t="s">
         <v>247</v>
       </c>
-      <c r="H52" t="s">
-        <v>248</v>
-      </c>
       <c r="I52" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J52" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K52" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="L52" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M52" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N52" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O52" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4041,54 +4023,54 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>214</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>227</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>228</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D53" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E53" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F53" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G53" t="s">
+        <v>248</v>
+      </c>
+      <c r="H53" t="s">
         <v>249</v>
       </c>
-      <c r="H53" t="s">
-        <v>250</v>
-      </c>
       <c r="I53" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J53" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K53" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="L53" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M53" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N53" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O53" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4097,54 +4079,54 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>214</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>227</v>
+        <v>97</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>98</v>
       </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="E54" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="F54" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="G54" t="s">
+        <v>253</v>
+      </c>
+      <c r="H54" t="s">
         <v>251</v>
       </c>
-      <c r="H54" t="s">
-        <v>252</v>
-      </c>
       <c r="I54" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J54" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="K54" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="L54" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M54" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N54" t="s">
-        <v>235</v>
+        <v>31</v>
       </c>
       <c r="O54" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4153,175 +4135,63 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>214</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="C55" t="s">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="D55" t="s">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="E55" t="s">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="F55" t="s">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="G55" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H55" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I55" t="s">
-        <v>233</v>
+        <v>26</v>
       </c>
       <c r="J55" t="s">
-        <v>127</v>
+        <v>27</v>
       </c>
       <c r="K55" t="s">
-        <v>234</v>
+        <v>28</v>
       </c>
       <c r="L55" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="M55" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="N55" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="O55" t="s">
-        <v>235</v>
+        <v>48</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>153</v>
-      </c>
-      <c r="B56" t="s">
-        <v>154</v>
-      </c>
-      <c r="C56" t="s">
-        <v>255</v>
-      </c>
-      <c r="D56" t="s">
-        <v>256</v>
-      </c>
-      <c r="E56" t="s">
-        <v>257</v>
-      </c>
-      <c r="F56" t="s">
-        <v>258</v>
-      </c>
-      <c r="G56" t="s">
-        <v>255</v>
-      </c>
-      <c r="H56" t="s">
-        <v>259</v>
-      </c>
-      <c r="I56" t="s">
-        <v>26</v>
-      </c>
-      <c r="J56" t="s">
-        <v>27</v>
-      </c>
-      <c r="K56" t="s">
-        <v>28</v>
-      </c>
-      <c r="L56" t="s">
-        <v>29</v>
-      </c>
-      <c r="M56" t="s">
-        <v>30</v>
-      </c>
-      <c r="N56" t="s">
-        <v>201</v>
-      </c>
-      <c r="O56" t="s">
-        <v>202</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>18</v>
-      </c>
-      <c r="B57" t="s">
-        <v>19</v>
-      </c>
-      <c r="C57" t="s">
-        <v>260</v>
-      </c>
-      <c r="D57" t="s">
-        <v>261</v>
-      </c>
-      <c r="E57" t="s">
-        <v>262</v>
-      </c>
-      <c r="F57" t="s">
-        <v>263</v>
-      </c>
-      <c r="G57" t="s">
-        <v>260</v>
-      </c>
-      <c r="H57" t="s">
-        <v>261</v>
-      </c>
-      <c r="I57" t="s">
-        <v>26</v>
-      </c>
-      <c r="J57" t="s">
-        <v>178</v>
-      </c>
-      <c r="K57" t="s">
-        <v>28</v>
-      </c>
-      <c r="L57" t="s">
-        <v>29</v>
-      </c>
-      <c r="M57" t="s">
-        <v>30</v>
-      </c>
-      <c r="N57" t="s">
-        <v>80</v>
-      </c>
-      <c r="O57" t="s">
-        <v>81</v>
-      </c>
-      <c r="P57" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="s">
-        <v>159</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -68,12 +68,471 @@
     <t xml:space="preserve">vintage</t>
   </si>
   <si>
-    <t xml:space="preserve">Municipal Services</t>
+    <t xml:space="preserve">Overall Economy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overall-economy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total nonfarm payroll jobs, measured at location of employment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 12-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-12-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USASpending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-02-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-03-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active-listing-count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-listing-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-sale-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list-to-sale-ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homes-sold-above-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-square-feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlpsq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-dom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total air passengers served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-passengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal Services</t>
   </si>
   <si>
     <t xml:space="preserve">municipal-services</t>
   </si>
   <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
     <t xml:space="preserve">Crime rate</t>
   </si>
   <si>
@@ -86,129 +545,51 @@
     <t xml:space="preserve">Federal Bureau of Investigation</t>
   </si>
   <si>
-    <t xml:space="preserve">Property crimes</t>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
   </si>
   <si>
     <t xml:space="preserve">crime-rate-property</t>
   </si>
   <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overall Economy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overall-economy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total nonfarm payroll jobs, measured at location of employment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal government jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-federal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-05-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 12-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-12-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
+    <t xml:space="preserve">Household Wellbeing</t>
   </si>
   <si>
     <t xml:space="preserve">household-wellbeing</t>
   </si>
   <si>
+    <t xml:space="preserve">Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-prime consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severely credit-constrained consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-subprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-total</t>
+  </si>
+  <si>
     <t xml:space="preserve">Personal bankruptcy rate</t>
   </si>
   <si>
@@ -218,178 +599,31 @@
     <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
   </si>
   <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-03-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
+    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medicaid-enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State agency reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNAP participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snap-participation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
   </si>
   <si>
     <t xml:space="preserve">About the DMV</t>
@@ -422,6 +656,9 @@
     <t xml:space="preserve">DMV-2025-12-11</t>
   </si>
   <si>
+    <t xml:space="preserve">foreign-born</t>
+  </si>
+  <si>
     <t xml:space="preserve">Educational attainment</t>
   </si>
   <si>
@@ -431,361 +668,25 @@
     <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
   </si>
   <si>
-    <t xml:space="preserve">Less than high school</t>
-  </si>
-  <si>
     <t xml:space="preserve">less-than-hs</t>
   </si>
   <si>
-    <t xml:space="preserve">High school or equivalent</t>
-  </si>
-  <si>
     <t xml:space="preserve">high-school</t>
   </si>
   <si>
-    <t xml:space="preserve">Some college or associate's degree</t>
-  </si>
-  <si>
     <t xml:space="preserve">some-college-aa</t>
   </si>
   <si>
-    <t xml:space="preserve">Bachelor's degree</t>
-  </si>
-  <si>
     <t xml:space="preserve">bachelors-degree</t>
   </si>
   <si>
-    <t xml:space="preserve">Graduate or professional degree</t>
-  </si>
-  <si>
     <t xml:space="preserve">graduate-degree</t>
   </si>
   <si>
-    <t xml:space="preserve">High school degree or higher, total</t>
-  </si>
-  <si>
     <t xml:space="preserve">hs-plus</t>
   </si>
   <si>
-    <t xml:space="preserve">Bachelor's degree or higher, total</t>
-  </si>
-  <si>
     <t xml:space="preserve">ba-plus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of foreign-born population (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">foreign-born</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active listing count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listing-count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homes sold above list price (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homes-sold-above-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List-to-sale price ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list-to-sale-ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median days on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential sale price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-sale-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median square feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-square-feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median listing price per square foot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mlpsq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNAP participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snap-participation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals participating in state-offered Supplemental Nutrition Assistance Program (SNAP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
   </si>
 </sst>
 </file>
@@ -1193,37 +1094,37 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>28</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>30</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>31</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="s">
         <v>32</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -1246,40 +1147,40 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>27</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>28</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>29</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>30</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>31</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
         <v>32</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -1302,143 +1203,143 @@
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" t="s">
         <v>26</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>27</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>28</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>29</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>30</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>31</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="s">
         <v>32</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" t="s">
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" t="s">
         <v>39</v>
       </c>
-      <c r="C5" t="s">
+      <c r="J5" t="s">
         <v>40</v>
       </c>
-      <c r="D5" t="s">
+      <c r="K5" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" t="s">
         <v>41</v>
       </c>
-      <c r="E5" t="s">
+      <c r="M5" t="s">
         <v>42</v>
       </c>
-      <c r="F5" t="s">
+      <c r="N5" t="s">
         <v>43</v>
       </c>
-      <c r="G5" t="s">
+      <c r="O5" t="s">
         <v>44</v>
       </c>
-      <c r="H5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" t="s">
-        <v>28</v>
-      </c>
-      <c r="L5" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" t="s">
-        <v>30</v>
-      </c>
-      <c r="N5" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" t="s">
-        <v>48</v>
-      </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
         <v>41</v>
       </c>
-      <c r="E6" t="s">
+      <c r="M6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="N6" t="s">
         <v>51</v>
       </c>
-      <c r="I6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-      <c r="L6" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" t="s">
-        <v>30</v>
-      </c>
-      <c r="N6" t="s">
-        <v>47</v>
-      </c>
       <c r="O6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1447,223 +1348,223 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" t="s">
         <v>41</v>
       </c>
-      <c r="E7" t="s">
+      <c r="M7" t="s">
         <v>42</v>
       </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="N7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O7" t="s">
         <v>52</v>
       </c>
-      <c r="H7" t="s">
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="s">
         <v>53</v>
-      </c>
-      <c r="I7" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L7" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" t="s">
-        <v>30</v>
-      </c>
-      <c r="N7" t="s">
-        <v>47</v>
-      </c>
-      <c r="O7" t="s">
-        <v>48</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
         <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8" t="s">
-        <v>54</v>
       </c>
       <c r="H8" t="s">
         <v>55</v>
       </c>
       <c r="I8" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" t="s">
         <v>27</v>
       </c>
-      <c r="K8" t="s">
-        <v>28</v>
-      </c>
       <c r="L8" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="M8" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="N8" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" t="s">
+        <v>61</v>
+      </c>
+      <c r="M9" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" t="s">
         <v>63</v>
       </c>
-      <c r="B9" t="s">
+      <c r="O9" t="s">
         <v>64</v>
       </c>
-      <c r="C9" t="s">
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="s">
         <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L9" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" t="s">
-        <v>60</v>
-      </c>
-      <c r="N9" t="s">
-        <v>61</v>
-      </c>
-      <c r="O9" t="s">
-        <v>62</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
         <v>69</v>
       </c>
-      <c r="C10" t="s">
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="s">
+        <v>67</v>
+      </c>
+      <c r="I10" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" t="s">
         <v>70</v>
       </c>
-      <c r="D10" t="s">
+      <c r="K10" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" t="s">
+        <v>29</v>
+      </c>
+      <c r="N10" t="s">
         <v>71</v>
       </c>
-      <c r="E10" t="s">
+      <c r="O10" t="s">
         <v>72</v>
       </c>
-      <c r="F10" t="s">
-        <v>73</v>
-      </c>
-      <c r="G10" t="s">
-        <v>74</v>
-      </c>
-      <c r="H10" t="s">
-        <v>75</v>
-      </c>
-      <c r="I10" t="s">
-        <v>58</v>
-      </c>
-      <c r="J10" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O10" t="s">
-        <v>79</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1671,222 +1572,222 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="I11" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="K11" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="L11" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N11" t="s">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I12" t="s">
+        <v>25</v>
+      </c>
+      <c r="J12" t="s">
         <v>26</v>
       </c>
-      <c r="J12" t="s">
-        <v>88</v>
-      </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L12" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M12" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" t="s">
         <v>30</v>
       </c>
-      <c r="N12" t="s">
+      <c r="O12" t="s">
         <v>31</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="s">
         <v>32</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I13" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L13" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M13" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="N13" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O13" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="E14" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="F14" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="G14" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" t="s">
         <v>26</v>
       </c>
-      <c r="J14" t="s">
-        <v>46</v>
-      </c>
       <c r="K14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L14" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="M14" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O14" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1895,334 +1796,334 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" t="s">
+        <v>95</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" t="s">
         <v>97</v>
       </c>
-      <c r="B15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F15" t="s">
-        <v>102</v>
-      </c>
-      <c r="G15" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" t="s">
-        <v>107</v>
-      </c>
-      <c r="I15" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" t="s">
-        <v>28</v>
-      </c>
       <c r="L15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M15" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N15" t="s">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="O15" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="E16" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="K16" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="L16" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="M16" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="N16" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="O16" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F17" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K17" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="L17" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="M17" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="N17" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="O17" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="F18" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="K18" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="L18" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="M18" t="s">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="N18" t="s">
-        <v>114</v>
+        <v>51</v>
       </c>
       <c r="O18" t="s">
-        <v>115</v>
+        <v>52</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="F19" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="H19" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="I19" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="L19" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M19" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N19" t="s">
-        <v>134</v>
+        <v>51</v>
       </c>
       <c r="O19" t="s">
-        <v>134</v>
+        <v>52</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B20" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="F20" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G20" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="H20" t="s">
-        <v>140</v>
+        <v>106</v>
       </c>
       <c r="I20" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K20" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="L20" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M20" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N20" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="O20" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2231,54 +2132,54 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E21" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G21" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="H21" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="I21" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K21" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="L21" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M21" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N21" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="O21" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2287,54 +2188,54 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="F22" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G22" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="H22" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="I22" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K22" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="L22" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M22" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N22" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="O22" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -2343,54 +2244,54 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>103</v>
       </c>
       <c r="E23" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="F23" t="s">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="G23" t="s">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="H23" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="I23" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K23" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="L23" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M23" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N23" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="O23" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2399,183 +2300,183 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="F24" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G24" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="I24" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="K24" t="s">
-        <v>133</v>
+        <v>27</v>
       </c>
       <c r="L24" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="M24" t="s">
+        <v>42</v>
+      </c>
+      <c r="N24" t="s">
         <v>30</v>
       </c>
-      <c r="N24" t="s">
-        <v>134</v>
-      </c>
       <c r="O24" t="s">
-        <v>134</v>
+        <v>31</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>135</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" t="s">
+        <v>122</v>
+      </c>
+      <c r="I25" t="s">
+        <v>39</v>
+      </c>
+      <c r="J25" t="s">
+        <v>123</v>
+      </c>
+      <c r="K25" t="s">
+        <v>97</v>
+      </c>
+      <c r="L25" t="s">
+        <v>28</v>
+      </c>
+      <c r="M25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s">
+        <v>124</v>
+      </c>
+      <c r="O25" t="s">
+        <v>125</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
         <v>126</v>
-      </c>
-      <c r="B25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" t="s">
-        <v>136</v>
-      </c>
-      <c r="D25" t="s">
-        <v>137</v>
-      </c>
-      <c r="E25" t="s">
-        <v>138</v>
-      </c>
-      <c r="F25" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" t="s">
-        <v>149</v>
-      </c>
-      <c r="H25" t="s">
-        <v>150</v>
-      </c>
-      <c r="I25" t="s">
-        <v>132</v>
-      </c>
-      <c r="J25" t="s">
-        <v>76</v>
-      </c>
-      <c r="K25" t="s">
-        <v>133</v>
-      </c>
-      <c r="L25" t="s">
-        <v>29</v>
-      </c>
-      <c r="M25" t="s">
-        <v>30</v>
-      </c>
-      <c r="N25" t="s">
-        <v>134</v>
-      </c>
-      <c r="O25" t="s">
-        <v>134</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G26" t="s">
+        <v>127</v>
+      </c>
+      <c r="H26" t="s">
+        <v>127</v>
+      </c>
+      <c r="I26" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" t="s">
+        <v>97</v>
+      </c>
+      <c r="L26" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>124</v>
+      </c>
+      <c r="O26" t="s">
+        <v>125</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="s">
         <v>126</v>
-      </c>
-      <c r="B26" t="s">
-        <v>127</v>
-      </c>
-      <c r="C26" t="s">
-        <v>136</v>
-      </c>
-      <c r="D26" t="s">
-        <v>137</v>
-      </c>
-      <c r="E26" t="s">
-        <v>138</v>
-      </c>
-      <c r="F26" t="s">
-        <v>131</v>
-      </c>
-      <c r="G26" t="s">
-        <v>151</v>
-      </c>
-      <c r="H26" t="s">
-        <v>152</v>
-      </c>
-      <c r="I26" t="s">
-        <v>132</v>
-      </c>
-      <c r="J26" t="s">
-        <v>76</v>
-      </c>
-      <c r="K26" t="s">
-        <v>133</v>
-      </c>
-      <c r="L26" t="s">
-        <v>29</v>
-      </c>
-      <c r="M26" t="s">
-        <v>30</v>
-      </c>
-      <c r="N26" t="s">
-        <v>134</v>
-      </c>
-      <c r="O26" t="s">
-        <v>134</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
         <v>128</v>
@@ -2590,199 +2491,199 @@
         <v>131</v>
       </c>
       <c r="G27" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="H27" t="s">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="I27" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="K27" t="s">
+        <v>27</v>
+      </c>
+      <c r="L27" t="s">
+        <v>28</v>
+      </c>
+      <c r="M27" t="s">
+        <v>29</v>
+      </c>
+      <c r="N27" t="s">
+        <v>107</v>
+      </c>
+      <c r="O27" t="s">
+        <v>108</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
         <v>133</v>
-      </c>
-      <c r="L27" t="s">
-        <v>29</v>
-      </c>
-      <c r="M27" t="s">
-        <v>30</v>
-      </c>
-      <c r="N27" t="s">
-        <v>134</v>
-      </c>
-      <c r="O27" t="s">
-        <v>134</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="B28" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="C28" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="F28" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="G28" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="H28" t="s">
-        <v>156</v>
+        <v>134</v>
       </c>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" t="s">
         <v>28</v>
       </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>29</v>
       </c>
-      <c r="M28" t="s">
-        <v>30</v>
-      </c>
       <c r="N28" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="O28" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>116</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="D29" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="F29" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="G29" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="H29" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
+        <v>27</v>
+      </c>
+      <c r="L29" t="s">
         <v>28</v>
       </c>
-      <c r="L29" t="s">
-        <v>167</v>
-      </c>
       <c r="M29" t="s">
-        <v>168</v>
+        <v>29</v>
       </c>
       <c r="N29" t="s">
-        <v>169</v>
+        <v>107</v>
       </c>
       <c r="O29" t="s">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F30" t="s">
+        <v>131</v>
+      </c>
+      <c r="G30" t="s">
+        <v>136</v>
+      </c>
+      <c r="H30" t="s">
+        <v>136</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
+      </c>
+      <c r="J30" t="s">
+        <v>40</v>
+      </c>
+      <c r="K30" t="s">
         <v>97</v>
       </c>
-      <c r="B30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C30" t="s">
-        <v>171</v>
-      </c>
-      <c r="D30" t="s">
-        <v>172</v>
-      </c>
-      <c r="E30" t="s">
-        <v>173</v>
-      </c>
-      <c r="F30" t="s">
-        <v>174</v>
-      </c>
-      <c r="G30" t="s">
-        <v>175</v>
-      </c>
-      <c r="H30" t="s">
-        <v>176</v>
-      </c>
-      <c r="I30" t="s">
-        <v>26</v>
-      </c>
-      <c r="J30" t="s">
-        <v>46</v>
-      </c>
-      <c r="K30" t="s">
+      <c r="L30" t="s">
         <v>28</v>
       </c>
-      <c r="L30" t="s">
-        <v>59</v>
-      </c>
       <c r="M30" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N30" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="O30" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2791,54 +2692,54 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="B31" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="C31" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="D31" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="E31" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="F31" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="G31" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="H31" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="K31" t="s">
+        <v>97</v>
+      </c>
+      <c r="L31" t="s">
         <v>28</v>
       </c>
-      <c r="L31" t="s">
-        <v>112</v>
-      </c>
       <c r="M31" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N31" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="O31" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2847,54 +2748,54 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="C32" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="D32" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="E32" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="F32" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="G32" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="H32" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="I32" t="s">
+        <v>25</v>
+      </c>
+      <c r="J32" t="s">
         <v>26</v>
       </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>27</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>28</v>
       </c>
-      <c r="L32" t="s">
-        <v>112</v>
-      </c>
       <c r="M32" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N32" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="O32" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2903,54 +2804,54 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="C33" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="F33" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="G33" t="s">
-        <v>189</v>
+        <v>139</v>
       </c>
       <c r="H33" t="s">
-        <v>190</v>
+        <v>139</v>
       </c>
       <c r="I33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J33" t="s">
+        <v>50</v>
+      </c>
+      <c r="K33" t="s">
         <v>27</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" t="s">
         <v>28</v>
       </c>
-      <c r="L33" t="s">
-        <v>112</v>
-      </c>
       <c r="M33" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N33" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="O33" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2959,54 +2860,54 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
-        <v>178</v>
+        <v>117</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>128</v>
       </c>
       <c r="D34" t="s">
-        <v>180</v>
+        <v>129</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="F34" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="G34" t="s">
-        <v>191</v>
+        <v>140</v>
       </c>
       <c r="H34" t="s">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="I34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J34" t="s">
+        <v>50</v>
+      </c>
+      <c r="K34" t="s">
         <v>27</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
         <v>28</v>
       </c>
-      <c r="L34" t="s">
-        <v>112</v>
-      </c>
       <c r="M34" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N34" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="O34" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -3015,54 +2916,54 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>49</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>117</v>
       </c>
       <c r="C35" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="D35" t="s">
-        <v>194</v>
+        <v>142</v>
       </c>
       <c r="E35" t="s">
-        <v>195</v>
+        <v>143</v>
       </c>
       <c r="F35" t="s">
-        <v>196</v>
+        <v>144</v>
       </c>
       <c r="G35" t="s">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="H35" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="I35" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K35" t="s">
+        <v>27</v>
+      </c>
+      <c r="L35" t="s">
         <v>28</v>
       </c>
-      <c r="L35" t="s">
+      <c r="M35" t="s">
         <v>29</v>
       </c>
-      <c r="M35" t="s">
-        <v>30</v>
-      </c>
       <c r="N35" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="O35" t="s">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -3071,166 +2972,166 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="C36" t="s">
-        <v>193</v>
+        <v>147</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="E36" t="s">
-        <v>195</v>
+        <v>149</v>
       </c>
       <c r="F36" t="s">
-        <v>196</v>
+        <v>121</v>
       </c>
       <c r="G36" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="H36" t="s">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="K36" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="L36" t="s">
+        <v>28</v>
+      </c>
+      <c r="M36" t="s">
         <v>29</v>
       </c>
-      <c r="M36" t="s">
-        <v>30</v>
-      </c>
       <c r="N36" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="O36" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="C37" t="s">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c r="D37" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="E37" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="F37" t="s">
-        <v>196</v>
+        <v>154</v>
       </c>
       <c r="G37" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="H37" t="s">
-        <v>203</v>
+        <v>155</v>
       </c>
       <c r="I37" t="s">
+        <v>25</v>
+      </c>
+      <c r="J37" t="s">
         <v>26</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>27</v>
       </c>
-      <c r="K37" t="s">
-        <v>77</v>
-      </c>
       <c r="L37" t="s">
+        <v>28</v>
+      </c>
+      <c r="M37" t="s">
         <v>29</v>
       </c>
-      <c r="M37" t="s">
-        <v>30</v>
-      </c>
       <c r="N37" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="O37" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>199</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="C38" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="D38" t="s">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="F38" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="G38" t="s">
-        <v>204</v>
+        <v>161</v>
       </c>
       <c r="H38" t="s">
-        <v>205</v>
+        <v>161</v>
       </c>
       <c r="I38" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="K38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L38" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M38" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N38" t="s">
-        <v>185</v>
+        <v>63</v>
       </c>
       <c r="O38" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3239,54 +3140,54 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>145</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="E39" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F39" t="s">
-        <v>196</v>
+        <v>59</v>
       </c>
       <c r="G39" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="H39" t="s">
-        <v>207</v>
+        <v>163</v>
       </c>
       <c r="I39" t="s">
+        <v>25</v>
+      </c>
+      <c r="J39" t="s">
         <v>26</v>
       </c>
-      <c r="J39" t="s">
-        <v>108</v>
-      </c>
       <c r="K39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L39" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="M39" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="N39" t="s">
-        <v>185</v>
+        <v>63</v>
       </c>
       <c r="O39" t="s">
-        <v>186</v>
+        <v>64</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3295,278 +3196,278 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s">
-        <v>194</v>
+        <v>167</v>
       </c>
       <c r="E40" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="F40" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="G40" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="H40" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="I40" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="K40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L40" t="s">
-        <v>29</v>
+        <v>171</v>
       </c>
       <c r="M40" t="s">
-        <v>30</v>
+        <v>172</v>
       </c>
       <c r="N40" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="O40" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>199</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="C41" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E41" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F41" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G41" t="s">
-        <v>210</v>
+        <v>177</v>
       </c>
       <c r="H41" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="I41" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="K41" t="s">
+        <v>27</v>
+      </c>
+      <c r="L41" t="s">
         <v>28</v>
       </c>
-      <c r="L41" t="s">
+      <c r="M41" t="s">
         <v>29</v>
       </c>
-      <c r="M41" t="s">
-        <v>30</v>
-      </c>
       <c r="N41" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="O41" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="C42" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="E42" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F42" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="G42" t="s">
-        <v>212</v>
+        <v>178</v>
       </c>
       <c r="H42" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="I42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J42" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="K42" t="s">
+        <v>27</v>
+      </c>
+      <c r="L42" t="s">
         <v>28</v>
       </c>
-      <c r="L42" t="s">
+      <c r="M42" t="s">
         <v>29</v>
       </c>
-      <c r="M42" t="s">
-        <v>30</v>
-      </c>
       <c r="N42" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="O42" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>173</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>174</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="F43" t="s">
-        <v>217</v>
+        <v>176</v>
       </c>
       <c r="G43" t="s">
-        <v>214</v>
+        <v>179</v>
       </c>
       <c r="H43" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="I43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J43" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="K43" t="s">
+        <v>27</v>
+      </c>
+      <c r="L43" t="s">
         <v>28</v>
       </c>
-      <c r="L43" t="s">
+      <c r="M43" t="s">
         <v>29</v>
       </c>
-      <c r="M43" t="s">
-        <v>30</v>
-      </c>
       <c r="N43" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="O43" t="s">
-        <v>186</v>
+        <v>52</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>199</v>
+        <v>53</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>180</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="C44" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="D44" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="E44" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="F44" t="s">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="G44" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="H44" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="I44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J44" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="K44" t="s">
+        <v>97</v>
+      </c>
+      <c r="L44" t="s">
         <v>28</v>
       </c>
-      <c r="L44" t="s">
+      <c r="M44" t="s">
         <v>29</v>
       </c>
-      <c r="M44" t="s">
-        <v>30</v>
-      </c>
       <c r="N44" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="O44" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3575,222 +3476,222 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>105</v>
+        <v>32</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="D45" t="s">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
-        <v>223</v>
+        <v>184</v>
       </c>
       <c r="F45" t="s">
-        <v>224</v>
+        <v>185</v>
       </c>
       <c r="G45" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="H45" t="s">
-        <v>225</v>
+        <v>189</v>
       </c>
       <c r="I45" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J45" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s">
+        <v>97</v>
+      </c>
+      <c r="L45" t="s">
         <v>28</v>
       </c>
-      <c r="L45" t="s">
+      <c r="M45" t="s">
         <v>29</v>
       </c>
-      <c r="M45" t="s">
-        <v>30</v>
-      </c>
       <c r="N45" t="s">
-        <v>169</v>
+        <v>124</v>
       </c>
       <c r="O45" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="D46" t="s">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="E46" t="s">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>185</v>
       </c>
       <c r="G46" t="s">
-        <v>229</v>
+        <v>190</v>
       </c>
       <c r="H46" t="s">
-        <v>230</v>
+        <v>191</v>
       </c>
       <c r="I46" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J46" t="s">
-        <v>231</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L46" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M46" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N46" t="s">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="O46" t="s">
+        <v>125</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="s">
         <v>32</v>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1</v>
-      </c>
-      <c r="R46" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="E47" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="F47" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" t="s">
+        <v>193</v>
+      </c>
+      <c r="H47" t="s">
+        <v>193</v>
+      </c>
+      <c r="I47" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" t="s">
+        <v>40</v>
+      </c>
+      <c r="K47" t="s">
+        <v>27</v>
+      </c>
+      <c r="L47" t="s">
+        <v>41</v>
+      </c>
+      <c r="M47" t="s">
+        <v>42</v>
+      </c>
+      <c r="N47" t="s">
         <v>43</v>
       </c>
-      <c r="G47" t="s">
-        <v>232</v>
-      </c>
-      <c r="H47" t="s">
-        <v>233</v>
-      </c>
-      <c r="I47" t="s">
-        <v>26</v>
-      </c>
-      <c r="J47" t="s">
-        <v>231</v>
-      </c>
-      <c r="K47" t="s">
-        <v>77</v>
-      </c>
-      <c r="L47" t="s">
-        <v>112</v>
-      </c>
-      <c r="M47" t="s">
-        <v>113</v>
-      </c>
-      <c r="N47" t="s">
-        <v>31</v>
-      </c>
       <c r="O47" t="s">
+        <v>44</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" t="s">
         <v>32</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B48" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C48" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="D48" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="E48" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="G48" t="s">
-        <v>234</v>
+        <v>196</v>
       </c>
       <c r="H48" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="I48" t="s">
+        <v>25</v>
+      </c>
+      <c r="J48" t="s">
         <v>26</v>
       </c>
-      <c r="J48" t="s">
-        <v>231</v>
-      </c>
       <c r="K48" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="L48" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M48" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N48" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="O48" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3799,54 +3700,54 @@
         <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B49" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C49" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D49" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="E49" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>198</v>
       </c>
       <c r="G49" t="s">
-        <v>236</v>
+        <v>202</v>
       </c>
       <c r="H49" t="s">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="I49" t="s">
+        <v>25</v>
+      </c>
+      <c r="J49" t="s">
         <v>26</v>
       </c>
-      <c r="J49" t="s">
-        <v>231</v>
-      </c>
       <c r="K49" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="L49" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M49" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N49" t="s">
-        <v>31</v>
+        <v>199</v>
       </c>
       <c r="O49" t="s">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3855,110 +3756,110 @@
         <v>1</v>
       </c>
       <c r="R49" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="D50" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="E50" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="F50" t="s">
-        <v>43</v>
+        <v>209</v>
       </c>
       <c r="G50" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="H50" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="I50" t="s">
+        <v>210</v>
+      </c>
+      <c r="J50" t="s">
         <v>26</v>
       </c>
-      <c r="J50" t="s">
-        <v>231</v>
-      </c>
       <c r="K50" t="s">
-        <v>77</v>
+        <v>211</v>
       </c>
       <c r="L50" t="s">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M50" t="s">
-        <v>113</v>
+        <v>29</v>
       </c>
       <c r="N50" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="O50" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>49</v>
+        <v>213</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="F51" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="G51" t="s">
-        <v>244</v>
+        <v>214</v>
       </c>
       <c r="H51" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="I51" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="J51" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="K51" t="s">
+        <v>211</v>
+      </c>
+      <c r="L51" t="s">
         <v>28</v>
       </c>
-      <c r="L51" t="s">
-        <v>59</v>
-      </c>
       <c r="M51" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N51" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="O51" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3967,54 +3868,54 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="C52" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="D52" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="E52" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="F52" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="G52" t="s">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="H52" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="I52" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="J52" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="K52" t="s">
+        <v>211</v>
+      </c>
+      <c r="L52" t="s">
         <v>28</v>
       </c>
-      <c r="L52" t="s">
-        <v>59</v>
-      </c>
       <c r="M52" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N52" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="O52" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4023,54 +3924,54 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
       <c r="C53" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="D53" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="E53" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="F53" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="G53" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="H53" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="J53" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="K53" t="s">
+        <v>211</v>
+      </c>
+      <c r="L53" t="s">
         <v>28</v>
       </c>
-      <c r="L53" t="s">
-        <v>59</v>
-      </c>
       <c r="M53" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N53" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="O53" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4079,54 +3980,54 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>97</v>
+        <v>204</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>205</v>
       </c>
       <c r="C54" t="s">
-        <v>250</v>
+        <v>215</v>
       </c>
       <c r="D54" t="s">
-        <v>251</v>
+        <v>216</v>
       </c>
       <c r="E54" t="s">
-        <v>252</v>
+        <v>217</v>
       </c>
       <c r="F54" t="s">
-        <v>243</v>
+        <v>209</v>
       </c>
       <c r="G54" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="H54" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="I54" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="J54" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="K54" t="s">
+        <v>211</v>
+      </c>
+      <c r="L54" t="s">
         <v>28</v>
       </c>
-      <c r="L54" t="s">
-        <v>59</v>
-      </c>
       <c r="M54" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N54" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
       <c r="O54" t="s">
-        <v>32</v>
+        <v>212</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4135,63 +4036,231 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>33</v>
+        <v>213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="C55" t="s">
-        <v>254</v>
+        <v>215</v>
       </c>
       <c r="D55" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="E55" t="s">
-        <v>256</v>
+        <v>217</v>
       </c>
       <c r="F55" t="s">
-        <v>257</v>
+        <v>209</v>
       </c>
       <c r="G55" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="H55" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="I55" t="s">
-        <v>26</v>
+        <v>210</v>
       </c>
       <c r="J55" t="s">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="K55" t="s">
+        <v>211</v>
+      </c>
+      <c r="L55" t="s">
         <v>28</v>
       </c>
-      <c r="L55" t="s">
-        <v>59</v>
-      </c>
       <c r="M55" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="N55" t="s">
-        <v>47</v>
+        <v>212</v>
       </c>
       <c r="O55" t="s">
-        <v>48</v>
+        <v>212</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>49</v>
+        <v>213</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>204</v>
+      </c>
+      <c r="B56" t="s">
+        <v>205</v>
+      </c>
+      <c r="C56" t="s">
+        <v>215</v>
+      </c>
+      <c r="D56" t="s">
+        <v>216</v>
+      </c>
+      <c r="E56" t="s">
+        <v>217</v>
+      </c>
+      <c r="F56" t="s">
+        <v>209</v>
+      </c>
+      <c r="G56" t="s">
+        <v>222</v>
+      </c>
+      <c r="H56" t="s">
+        <v>222</v>
+      </c>
+      <c r="I56" t="s">
+        <v>210</v>
+      </c>
+      <c r="J56" t="s">
+        <v>123</v>
+      </c>
+      <c r="K56" t="s">
+        <v>211</v>
+      </c>
+      <c r="L56" t="s">
+        <v>28</v>
+      </c>
+      <c r="M56" t="s">
+        <v>29</v>
+      </c>
+      <c r="N56" t="s">
+        <v>212</v>
+      </c>
+      <c r="O56" t="s">
+        <v>212</v>
+      </c>
+      <c r="P56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>204</v>
+      </c>
+      <c r="B57" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" t="s">
+        <v>215</v>
+      </c>
+      <c r="D57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E57" t="s">
+        <v>217</v>
+      </c>
+      <c r="F57" t="s">
+        <v>209</v>
+      </c>
+      <c r="G57" t="s">
+        <v>223</v>
+      </c>
+      <c r="H57" t="s">
+        <v>223</v>
+      </c>
+      <c r="I57" t="s">
+        <v>210</v>
+      </c>
+      <c r="J57" t="s">
+        <v>123</v>
+      </c>
+      <c r="K57" t="s">
+        <v>211</v>
+      </c>
+      <c r="L57" t="s">
+        <v>28</v>
+      </c>
+      <c r="M57" t="s">
+        <v>29</v>
+      </c>
+      <c r="N57" t="s">
+        <v>212</v>
+      </c>
+      <c r="O57" t="s">
+        <v>212</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>204</v>
+      </c>
+      <c r="B58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C58" t="s">
+        <v>215</v>
+      </c>
+      <c r="D58" t="s">
+        <v>216</v>
+      </c>
+      <c r="E58" t="s">
+        <v>217</v>
+      </c>
+      <c r="F58" t="s">
+        <v>209</v>
+      </c>
+      <c r="G58" t="s">
+        <v>224</v>
+      </c>
+      <c r="H58" t="s">
+        <v>224</v>
+      </c>
+      <c r="I58" t="s">
+        <v>210</v>
+      </c>
+      <c r="J58" t="s">
+        <v>123</v>
+      </c>
+      <c r="K58" t="s">
+        <v>211</v>
+      </c>
+      <c r="L58" t="s">
+        <v>28</v>
+      </c>
+      <c r="M58" t="s">
+        <v>29</v>
+      </c>
+      <c r="N58" t="s">
+        <v>212</v>
+      </c>
+      <c r="O58" t="s">
+        <v>212</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="s">
+        <v>213</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -86,6 +86,9 @@
     <t xml:space="preserve">Lightcast and U.S. Bureau of Labor Statistics</t>
   </si>
   <si>
+    <t xml:space="preserve">Total jobs</t>
+  </si>
+  <si>
     <t xml:space="preserve">jobs-total</t>
   </si>
   <si>
@@ -113,9 +116,15 @@
     <t xml:space="preserve">DMV-2026-05-01</t>
   </si>
   <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
     <t xml:space="preserve">jobs-private</t>
   </si>
   <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
     <t xml:space="preserve">jobs-federal</t>
   </si>
   <si>
@@ -161,6 +170,9 @@
     <t xml:space="preserve">USASpending</t>
   </si>
   <si>
+    <t xml:space="preserve">Federal obligations, total</t>
+  </si>
+  <si>
     <t xml:space="preserve">federal-obligations-total</t>
   </si>
   <si>
@@ -176,9 +188,15 @@
     <t xml:space="preserve">DMV-2026-04-01</t>
   </si>
   <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
     <t xml:space="preserve">federal-obligations-grants</t>
   </si>
   <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
     <t xml:space="preserve">federal-obligations-contracts</t>
   </si>
   <si>
@@ -194,6 +212,9 @@
     <t xml:space="preserve">DataFy</t>
   </si>
   <si>
+    <t xml:space="preserve">Resident spending, total</t>
+  </si>
+  <si>
     <t xml:space="preserve">resident-spending-total</t>
   </si>
   <si>
@@ -248,6 +269,9 @@
     <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
   </si>
   <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
     <t xml:space="preserve">Utility patents</t>
   </si>
   <si>
@@ -260,6 +284,9 @@
     <t xml:space="preserve">United States Patent and Trademark Office</t>
   </si>
   <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
     <t xml:space="preserve">patents-filed</t>
   </si>
   <si>
@@ -275,12 +302,18 @@
     <t xml:space="preserve">Crunchbase</t>
   </si>
   <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
     <t xml:space="preserve">venture-capital-volume</t>
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-02-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
     <t xml:space="preserve">venture-capital-deals</t>
   </si>
   <si>
@@ -299,6 +332,9 @@
     <t xml:space="preserve">Percentage of labor force not currently employed  </t>
   </si>
   <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
     <t xml:space="preserve">unempr-sa-total</t>
   </si>
   <si>
@@ -308,15 +344,27 @@
     <t xml:space="preserve">pct_diff</t>
   </si>
   <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
     <t xml:space="preserve">unempr-sa-white</t>
   </si>
   <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
     <t xml:space="preserve">unempr-sa-poc</t>
   </si>
   <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
     <t xml:space="preserve">unempr-sa-male</t>
   </si>
   <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
     <t xml:space="preserve">unempr-sa-female</t>
   </si>
   <si>
@@ -332,6 +380,9 @@
     <t xml:space="preserve">Lightcast</t>
   </si>
   <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
     <t xml:space="preserve">unique-postings-total</t>
   </si>
   <si>
@@ -341,12 +392,21 @@
     <t xml:space="preserve">2026M3</t>
   </si>
   <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
     <t xml:space="preserve">unique-postings-private</t>
   </si>
   <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
     <t xml:space="preserve">unique-postings-public</t>
   </si>
   <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
     <t xml:space="preserve">unique-postings-internships</t>
   </si>
   <si>
@@ -380,6 +440,9 @@
     <t xml:space="preserve">CoStar</t>
   </si>
   <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
     <t xml:space="preserve">commercial-occupancy-office</t>
   </si>
   <si>
@@ -395,6 +458,9 @@
     <t xml:space="preserve">DMV-2026-03-04</t>
   </si>
   <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
     <t xml:space="preserve">commercial-occupancy-retail</t>
   </si>
   <si>
@@ -410,30 +476,54 @@
     <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
   </si>
   <si>
+    <t xml:space="preserve">Active listing count</t>
+  </si>
+  <si>
     <t xml:space="preserve">active-listing-count</t>
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-04-27</t>
   </si>
   <si>
+    <t xml:space="preserve">Median residential listing price</t>
+  </si>
+  <si>
     <t xml:space="preserve">median-listing-price</t>
   </si>
   <si>
+    <t xml:space="preserve">Median residential sale price</t>
+  </si>
+  <si>
     <t xml:space="preserve">median-sale-price</t>
   </si>
   <si>
+    <t xml:space="preserve">List-to-sale price ratio</t>
+  </si>
+  <si>
     <t xml:space="preserve">list-to-sale-ratio</t>
   </si>
   <si>
+    <t xml:space="preserve">Homes sold above list price (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">homes-sold-above-list</t>
   </si>
   <si>
+    <t xml:space="preserve">Median square feet</t>
+  </si>
+  <si>
     <t xml:space="preserve">median-square-feet</t>
   </si>
   <si>
+    <t xml:space="preserve">Median listing price per square foot</t>
+  </si>
+  <si>
     <t xml:space="preserve">mlpsq</t>
   </si>
   <si>
+    <t xml:space="preserve">Median days on market</t>
+  </si>
+  <si>
     <t xml:space="preserve">median-dom</t>
   </si>
   <si>
@@ -497,6 +587,9 @@
     <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
   </si>
   <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
     <t xml:space="preserve">visitor-spending-total</t>
   </si>
   <si>
@@ -524,6 +617,9 @@
     <t xml:space="preserve">U.S. Federal Transit Administration</t>
   </si>
   <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
     <t xml:space="preserve">transit-vrm</t>
   </si>
   <si>
@@ -545,12 +641,21 @@
     <t xml:space="preserve">Federal Bureau of Investigation</t>
   </si>
   <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
     <t xml:space="preserve">crime-rate-total</t>
   </si>
   <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
     <t xml:space="preserve">crime-rate-violent</t>
   </si>
   <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
     <t xml:space="preserve">crime-rate-property</t>
   </si>
   <si>
@@ -656,6 +761,9 @@
     <t xml:space="preserve">DMV-2025-12-11</t>
   </si>
   <si>
+    <t xml:space="preserve">Share of foreign-born population (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">foreign-born</t>
   </si>
   <si>
@@ -668,22 +776,43 @@
     <t xml:space="preserve">Educational attaintment for population aged 25 and older</t>
   </si>
   <si>
+    <t xml:space="preserve">Less than high school</t>
+  </si>
+  <si>
     <t xml:space="preserve">less-than-hs</t>
   </si>
   <si>
+    <t xml:space="preserve">High school or equivalent</t>
+  </si>
+  <si>
     <t xml:space="preserve">high-school</t>
   </si>
   <si>
+    <t xml:space="preserve">Some college or associate's degree</t>
+  </si>
+  <si>
     <t xml:space="preserve">some-college-aa</t>
   </si>
   <si>
+    <t xml:space="preserve">Bachelor's degree</t>
+  </si>
+  <si>
     <t xml:space="preserve">bachelors-degree</t>
   </si>
   <si>
+    <t xml:space="preserve">Graduate or professional degree</t>
+  </si>
+  <si>
     <t xml:space="preserve">graduate-degree</t>
   </si>
   <si>
+    <t xml:space="preserve">High school degree or higher, total</t>
+  </si>
+  <si>
     <t xml:space="preserve">hs-plus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bachelor's degree or higher, total</t>
   </si>
   <si>
     <t xml:space="preserve">ba-plus</t>
@@ -1094,28 +1223,28 @@
         <v>24</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -1124,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -1147,40 +1276,40 @@
         <v>23</v>
       </c>
       <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>30</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="O3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="s">
         <v>33</v>
-      </c>
-      <c r="H3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
@@ -1203,31 +1332,31 @@
         <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -1236,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -1247,43 +1376,43 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
         <v>38</v>
       </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
       <c r="H5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1292,7 +1421,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -1303,43 +1432,43 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>52</v>
+      </c>
+      <c r="H6" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" t="s">
         <v>45</v>
       </c>
-      <c r="D6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>41</v>
-      </c>
-      <c r="M6" t="s">
-        <v>42</v>
-      </c>
       <c r="N6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1348,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
@@ -1359,43 +1488,43 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
+        <v>44</v>
+      </c>
+      <c r="M7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I7" t="s">
-        <v>25</v>
-      </c>
-      <c r="J7" t="s">
-        <v>50</v>
-      </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" t="s">
-        <v>41</v>
-      </c>
-      <c r="M7" t="s">
-        <v>42</v>
-      </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1404,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8">
@@ -1415,43 +1544,43 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="N8" t="s">
         <v>55</v>
       </c>
-      <c r="H8" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" t="s">
-        <v>50</v>
-      </c>
-      <c r="K8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L8" t="s">
-        <v>41</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" t="s">
-        <v>51</v>
-      </c>
       <c r="O8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1460,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1471,43 +1600,43 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J9" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L9" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="O9" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
@@ -1516,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -1527,99 +1656,99 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="H10" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N10" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O10" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="s">
         <v>72</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
@@ -1628,54 +1757,54 @@
         <v>0</v>
       </c>
       <c r="R11" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="H12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1684,54 +1813,54 @@
         <v>0</v>
       </c>
       <c r="R12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="H13" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J13" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L13" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1740,54 +1869,54 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="F14" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G14" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="I14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L14" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1796,54 +1925,54 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B15" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E15" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F15" t="s">
         <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="H15" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K15" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L15" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M15" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O15" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1852,54 +1981,54 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F16" t="s">
         <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="H16" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K16" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M16" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N16" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O16" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -1908,54 +2037,54 @@
         <v>1</v>
       </c>
       <c r="R16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
         <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K17" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L17" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -1964,54 +2093,54 @@
         <v>1</v>
       </c>
       <c r="R17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
         <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H18" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K18" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M18" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N18" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -2020,54 +2149,54 @@
         <v>1</v>
       </c>
       <c r="R18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="F19" t="s">
         <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K19" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L19" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M19" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N19" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2076,54 +2205,54 @@
         <v>1</v>
       </c>
       <c r="R19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F20" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G20" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H20" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="I20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L20" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M20" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N20" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O20" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2132,54 +2261,54 @@
         <v>0</v>
       </c>
       <c r="R20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D21" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F21" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G21" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="I21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L21" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M21" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N21" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O21" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2188,54 +2317,54 @@
         <v>0</v>
       </c>
       <c r="R21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F22" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H22" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="I22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J22" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L22" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M22" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N22" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O22" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -2244,54 +2373,54 @@
         <v>0</v>
       </c>
       <c r="R22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G23" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="H23" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="I23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L23" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M23" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N23" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O23" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2300,54 +2429,54 @@
         <v>0</v>
       </c>
       <c r="R23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B24" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="F24" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="G24" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L24" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M24" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2356,54 +2485,54 @@
         <v>1</v>
       </c>
       <c r="R24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="E25" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F25" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="G25" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="H25" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="I25" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J25" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K25" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N25" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="O25" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -2412,54 +2541,54 @@
         <v>0</v>
       </c>
       <c r="R25" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C26" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="D26" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F26" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="G26" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="H26" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="I26" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K26" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="O26" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2468,54 +2597,54 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F27" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G27" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="H27" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="I27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O27" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P27" t="n">
         <v>1</v>
@@ -2524,54 +2653,54 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E28" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F28" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G28" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="H28" t="s">
-        <v>134</v>
+        <v>158</v>
       </c>
       <c r="I28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O28" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2580,54 +2709,54 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E29" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F29" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G29" t="s">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="I29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L29" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N29" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O29" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2636,54 +2765,54 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E30" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F30" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="I30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K30" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L30" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O30" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2692,54 +2821,54 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D31" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F31" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G31" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="H31" t="s">
-        <v>137</v>
+        <v>164</v>
       </c>
       <c r="I31" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K31" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L31" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M31" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O31" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2748,54 +2877,54 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D32" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F32" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G32" t="s">
-        <v>138</v>
+        <v>165</v>
       </c>
       <c r="H32" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O32" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2804,54 +2933,54 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D33" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F33" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G33" t="s">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="H33" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M33" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N33" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O33" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2860,54 +2989,54 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B34" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E34" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="F34" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="G34" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="H34" t="s">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="I34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L34" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N34" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O34" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -2916,54 +3045,54 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
-        <v>141</v>
+        <v>171</v>
       </c>
       <c r="D35" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="E35" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="F35" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G35" t="s">
-        <v>142</v>
+        <v>171</v>
       </c>
       <c r="H35" t="s">
-        <v>142</v>
+        <v>172</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M35" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N35" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="O35" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -2972,54 +3101,54 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>133</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C36" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="D36" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="E36" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="F36" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="G36" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="H36" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="K36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M36" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O36" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3028,54 +3157,54 @@
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="D37" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>183</v>
       </c>
       <c r="F37" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="G37" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="H37" t="s">
-        <v>155</v>
+        <v>185</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M37" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="O37" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3084,54 +3213,54 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C38" t="s">
-        <v>158</v>
+        <v>188</v>
       </c>
       <c r="D38" t="s">
-        <v>159</v>
+        <v>189</v>
       </c>
       <c r="E38" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="F38" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G38" t="s">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="H38" t="s">
-        <v>161</v>
+        <v>192</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L38" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M38" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N38" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="O38" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3140,54 +3269,54 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="B39" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="D39" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="E39" t="s">
-        <v>162</v>
+        <v>193</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G39" t="s">
-        <v>163</v>
+        <v>193</v>
       </c>
       <c r="H39" t="s">
-        <v>163</v>
+        <v>194</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="M39" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="N39" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="O39" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3196,54 +3325,54 @@
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="D40" t="s">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="E40" t="s">
-        <v>168</v>
+        <v>199</v>
       </c>
       <c r="F40" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="G40" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="H40" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
       <c r="I40" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L40" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
       <c r="M40" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="N40" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="O40" t="s">
-        <v>157</v>
+        <v>187</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -3252,54 +3381,54 @@
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E41" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="G41" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
       <c r="H41" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="I41" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L41" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M41" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O41" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3308,54 +3437,54 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D42" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E42" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="G42" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="H42" t="s">
-        <v>178</v>
+        <v>212</v>
       </c>
       <c r="I42" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L42" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M42" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O42" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3364,54 +3493,54 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>164</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
-        <v>165</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="E43" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
       <c r="F43" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
       <c r="G43" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="H43" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="I43" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M43" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N43" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="O43" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3420,54 +3549,54 @@
         <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B44" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C44" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D44" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E44" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="F44" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="G44" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
       <c r="H44" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="I44" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K44" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="O44" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3476,54 +3605,54 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C45" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E45" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="F45" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="G45" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="H45" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="I45" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K45" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M45" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="O45" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3532,54 +3661,54 @@
         <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B46" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C46" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="D46" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="E46" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="F46" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="G46" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="H46" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="I46" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K46" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="L46" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M46" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="O46" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3588,54 +3717,54 @@
         <v>1</v>
       </c>
       <c r="R46" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B47" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C47" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="D47" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="E47" t="s">
-        <v>194</v>
+        <v>229</v>
       </c>
       <c r="F47" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G47" t="s">
-        <v>193</v>
+        <v>227</v>
       </c>
       <c r="H47" t="s">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="I47" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J47" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L47" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M47" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="N47" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="O47" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3644,54 +3773,54 @@
         <v>1</v>
       </c>
       <c r="R47" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B48" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C48" t="s">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="D48" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s">
-        <v>197</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="G48" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="H48" t="s">
-        <v>196</v>
+        <v>231</v>
       </c>
       <c r="I48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M48" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="O48" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3700,54 +3829,54 @@
         <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="C49" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="E49" t="s">
-        <v>203</v>
+        <v>238</v>
       </c>
       <c r="F49" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="G49" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="H49" t="s">
-        <v>202</v>
+        <v>237</v>
       </c>
       <c r="I49" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L49" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>199</v>
+        <v>234</v>
       </c>
       <c r="O49" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3756,54 +3885,54 @@
         <v>1</v>
       </c>
       <c r="R49" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C50" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="D50" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="E50" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="F50" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G50" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="H50" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="I50" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J50" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K50" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L50" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M50" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O50" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3812,54 +3941,54 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="D51" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="E51" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="F51" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G51" t="s">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="H51" t="s">
-        <v>214</v>
+        <v>250</v>
       </c>
       <c r="I51" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J51" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K51" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M51" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O51" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3868,54 +3997,54 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B52" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C52" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D52" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E52" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F52" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G52" t="s">
-        <v>218</v>
+        <v>254</v>
       </c>
       <c r="H52" t="s">
-        <v>218</v>
+        <v>255</v>
       </c>
       <c r="I52" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J52" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L52" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O52" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -3924,54 +4053,54 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B53" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C53" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D53" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E53" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F53" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G53" t="s">
-        <v>219</v>
+        <v>256</v>
       </c>
       <c r="H53" t="s">
-        <v>219</v>
+        <v>257</v>
       </c>
       <c r="I53" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J53" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L53" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M53" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O53" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -3980,54 +4109,54 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B54" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C54" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D54" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E54" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F54" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G54" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="H54" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="I54" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J54" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K54" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M54" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O54" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4036,54 +4165,54 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B55" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C55" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D55" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E55" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F55" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G55" t="s">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="H55" t="s">
-        <v>221</v>
+        <v>261</v>
       </c>
       <c r="I55" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J55" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K55" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M55" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N55" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O55" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4092,54 +4221,54 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D56" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E56" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F56" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G56" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="H56" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="I56" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J56" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K56" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M56" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N56" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O56" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4148,54 +4277,54 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B57" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C57" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D57" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E57" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F57" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G57" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="H57" t="s">
-        <v>223</v>
+        <v>265</v>
       </c>
       <c r="I57" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J57" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K57" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M57" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O57" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -4204,54 +4333,54 @@
         <v>0</v>
       </c>
       <c r="R57" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>204</v>
+        <v>239</v>
       </c>
       <c r="B58" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="D58" t="s">
-        <v>216</v>
+        <v>252</v>
       </c>
       <c r="E58" t="s">
-        <v>217</v>
+        <v>253</v>
       </c>
       <c r="F58" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="G58" t="s">
-        <v>224</v>
+        <v>266</v>
       </c>
       <c r="H58" t="s">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="I58" t="s">
-        <v>210</v>
+        <v>245</v>
       </c>
       <c r="J58" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="K58" t="s">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="L58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N58" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="O58" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
@@ -4260,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="R58" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
   </si>
   <si>
     <t xml:space="preserve">Unemployment rate, workers of color</t>
@@ -2216,31 +2222,31 @@
         <v>102</v>
       </c>
       <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" t="s">
         <v>118</v>
       </c>
-      <c r="D20" t="s">
+      <c r="H20" t="s">
         <v>119</v>
-      </c>
-      <c r="E20" t="s">
-        <v>120</v>
-      </c>
-      <c r="F20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" t="s">
-        <v>123</v>
       </c>
       <c r="I20" t="s">
         <v>26</v>
       </c>
       <c r="J20" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K20" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L20" t="s">
         <v>68</v>
@@ -2249,16 +2255,16 @@
         <v>69</v>
       </c>
       <c r="N20" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="O20" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="s">
         <v>33</v>
@@ -2272,22 +2278,22 @@
         <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I21" t="s">
         <v>26</v>
@@ -2305,10 +2311,10 @@
         <v>69</v>
       </c>
       <c r="N21" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O21" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2328,16 +2334,16 @@
         <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G22" t="s">
         <v>128</v>
@@ -2361,10 +2367,10 @@
         <v>69</v>
       </c>
       <c r="N22" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O22" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -2384,16 +2390,16 @@
         <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F23" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G23" t="s">
         <v>130</v>
@@ -2417,10 +2423,10 @@
         <v>69</v>
       </c>
       <c r="N23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2440,16 +2446,16 @@
         <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E24" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="F24" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G24" t="s">
         <v>132</v>
@@ -2467,22 +2473,22 @@
         <v>28</v>
       </c>
       <c r="L24" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="M24" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="N24" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="O24" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="s">
         <v>33</v>
@@ -2490,90 +2496,90 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" t="s">
+        <v>134</v>
+      </c>
+      <c r="D25" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" t="s">
         <v>136</v>
       </c>
-      <c r="B25" t="s">
+      <c r="F25" t="s">
         <v>137</v>
       </c>
-      <c r="C25" t="s">
-        <v>138</v>
-      </c>
-      <c r="D25" t="s">
-        <v>139</v>
-      </c>
-      <c r="E25" t="s">
-        <v>140</v>
-      </c>
-      <c r="F25" t="s">
-        <v>141</v>
-      </c>
       <c r="G25" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="H25" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="I25" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J25" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="K25" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L25" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M25" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N25" t="s">
-        <v>145</v>
+        <v>31</v>
       </c>
       <c r="O25" t="s">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="s">
-        <v>147</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C26" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F26" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G26" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H26" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K26" t="s">
         <v>109</v>
@@ -2585,10 +2591,10 @@
         <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O26" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2597,42 +2603,42 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B27" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" t="s">
+        <v>142</v>
+      </c>
+      <c r="F27" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" t="s">
         <v>150</v>
       </c>
-      <c r="D27" t="s">
+      <c r="H27" t="s">
         <v>151</v>
       </c>
-      <c r="E27" t="s">
-        <v>152</v>
-      </c>
-      <c r="F27" t="s">
-        <v>153</v>
-      </c>
-      <c r="G27" t="s">
-        <v>154</v>
-      </c>
-      <c r="H27" t="s">
-        <v>155</v>
-      </c>
       <c r="I27" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J27" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K27" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L27" t="s">
         <v>29</v>
@@ -2641,51 +2647,51 @@
         <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="O27" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D28" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E28" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G28" t="s">
+        <v>156</v>
+      </c>
+      <c r="H28" t="s">
         <v>157</v>
-      </c>
-      <c r="H28" t="s">
-        <v>158</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K28" t="s">
         <v>28</v>
@@ -2697,10 +2703,10 @@
         <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2709,27 +2715,27 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C29" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E29" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F29" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G29" t="s">
         <v>159</v>
@@ -2753,10 +2759,10 @@
         <v>30</v>
       </c>
       <c r="N29" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O29" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2765,27 +2771,27 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C30" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D30" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E30" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G30" t="s">
         <v>161</v>
@@ -2797,10 +2803,10 @@
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K30" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L30" t="s">
         <v>29</v>
@@ -2809,10 +2815,10 @@
         <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O30" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2821,27 +2827,27 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D31" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E31" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G31" t="s">
         <v>163</v>
@@ -2853,7 +2859,7 @@
         <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="K31" t="s">
         <v>109</v>
@@ -2865,10 +2871,10 @@
         <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O31" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2877,27 +2883,27 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D32" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E32" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F32" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G32" t="s">
         <v>165</v>
@@ -2909,10 +2915,10 @@
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K32" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L32" t="s">
         <v>29</v>
@@ -2921,10 +2927,10 @@
         <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O32" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P32" t="n">
         <v>1</v>
@@ -2933,27 +2939,27 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G33" t="s">
         <v>167</v>
@@ -2965,7 +2971,7 @@
         <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
@@ -2977,10 +2983,10 @@
         <v>30</v>
       </c>
       <c r="N33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -2989,27 +2995,27 @@
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C34" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D34" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E34" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F34" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G34" t="s">
         <v>169</v>
@@ -3033,10 +3039,10 @@
         <v>30</v>
       </c>
       <c r="N34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -3045,27 +3051,27 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B35" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="E35" t="s">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="F35" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="G35" t="s">
         <v>171</v>
@@ -3089,10 +3095,10 @@
         <v>30</v>
       </c>
       <c r="N35" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O35" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -3101,39 +3107,39 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>138</v>
+      </c>
+      <c r="B36" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" t="s">
+        <v>173</v>
+      </c>
+      <c r="D36" t="s">
+        <v>174</v>
+      </c>
+      <c r="E36" t="s">
         <v>175</v>
       </c>
-      <c r="B36" t="s">
+      <c r="F36" t="s">
         <v>176</v>
       </c>
-      <c r="C36" t="s">
-        <v>177</v>
-      </c>
-      <c r="D36" t="s">
-        <v>178</v>
-      </c>
-      <c r="E36" t="s">
-        <v>179</v>
-      </c>
-      <c r="F36" t="s">
-        <v>141</v>
-      </c>
       <c r="G36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="H36" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>180</v>
+        <v>54</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
@@ -3145,51 +3151,51 @@
         <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="O36" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C37" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" t="s">
         <v>181</v>
       </c>
-      <c r="D37" t="s">
-        <v>182</v>
-      </c>
-      <c r="E37" t="s">
-        <v>183</v>
-      </c>
       <c r="F37" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="G37" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H37" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>27</v>
+        <v>182</v>
       </c>
       <c r="K37" t="s">
         <v>28</v>
@@ -3201,10 +3207,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>186</v>
+        <v>55</v>
       </c>
       <c r="O37" t="s">
-        <v>187</v>
+        <v>56</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
@@ -3213,80 +3219,80 @@
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C38" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E38" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="G38" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H38" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
       </c>
       <c r="L38" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M38" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="O38" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C39" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D39" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E39" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F39" t="s">
         <v>65</v>
@@ -3301,7 +3307,7 @@
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K39" t="s">
         <v>28</v>
@@ -3330,134 +3336,134 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" t="s">
         <v>195</v>
       </c>
-      <c r="B40" t="s">
+      <c r="D40" t="s">
         <v>196</v>
       </c>
-      <c r="C40" t="s">
-        <v>197</v>
-      </c>
-      <c r="D40" t="s">
-        <v>198</v>
-      </c>
       <c r="E40" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F40" t="s">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="G40" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H40" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="K40" t="s">
         <v>28</v>
       </c>
       <c r="L40" t="s">
-        <v>203</v>
+        <v>68</v>
       </c>
       <c r="M40" t="s">
-        <v>204</v>
+        <v>69</v>
       </c>
       <c r="N40" t="s">
-        <v>186</v>
+        <v>70</v>
       </c>
       <c r="O40" t="s">
-        <v>187</v>
+        <v>71</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="D41" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E41" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F41" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G41" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H41" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="K41" t="s">
         <v>28</v>
       </c>
       <c r="L41" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="M41" t="s">
-        <v>30</v>
+        <v>206</v>
       </c>
       <c r="N41" t="s">
-        <v>55</v>
+        <v>188</v>
       </c>
       <c r="O41" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
       <c r="P41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D42" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F42" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G42" t="s">
         <v>211</v>
@@ -3498,22 +3504,22 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G43" t="s">
         <v>213</v>
@@ -3554,37 +3560,37 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>197</v>
+      </c>
+      <c r="B44" t="s">
+        <v>198</v>
+      </c>
+      <c r="C44" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" t="s">
+        <v>208</v>
+      </c>
+      <c r="E44" t="s">
+        <v>209</v>
+      </c>
+      <c r="F44" t="s">
+        <v>210</v>
+      </c>
+      <c r="G44" t="s">
         <v>215</v>
       </c>
-      <c r="B44" t="s">
+      <c r="H44" t="s">
         <v>216</v>
-      </c>
-      <c r="C44" t="s">
-        <v>217</v>
-      </c>
-      <c r="D44" t="s">
-        <v>218</v>
-      </c>
-      <c r="E44" t="s">
-        <v>219</v>
-      </c>
-      <c r="F44" t="s">
-        <v>220</v>
-      </c>
-      <c r="G44" t="s">
-        <v>221</v>
-      </c>
-      <c r="H44" t="s">
-        <v>222</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="K44" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L44" t="s">
         <v>29</v>
@@ -3593,10 +3599,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="O44" t="s">
-        <v>146</v>
+        <v>56</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3605,27 +3611,27 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C45" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F45" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G45" t="s">
         <v>223</v>
@@ -3649,10 +3655,10 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3666,22 +3672,22 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B46" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D46" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E46" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F46" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G46" t="s">
         <v>225</v>
@@ -3705,10 +3711,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O46" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3722,22 +3728,22 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B47" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D47" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="E47" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="F47" t="s">
-        <v>41</v>
+        <v>222</v>
       </c>
       <c r="G47" t="s">
         <v>227</v>
@@ -3746,25 +3752,25 @@
         <v>228</v>
       </c>
       <c r="I47" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J47" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K47" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L47" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M47" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="O47" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3778,49 +3784,49 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B48" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C48" t="s">
+        <v>229</v>
+      </c>
+      <c r="D48" t="s">
         <v>230</v>
       </c>
-      <c r="D48" t="s">
+      <c r="E48" t="s">
         <v>231</v>
       </c>
-      <c r="E48" t="s">
-        <v>232</v>
-      </c>
       <c r="F48" t="s">
-        <v>233</v>
+        <v>41</v>
       </c>
       <c r="G48" t="s">
+        <v>229</v>
+      </c>
+      <c r="H48" t="s">
         <v>230</v>
       </c>
-      <c r="H48" t="s">
-        <v>231</v>
-      </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J48" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K48" t="s">
         <v>28</v>
       </c>
       <c r="L48" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M48" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N48" t="s">
-        <v>234</v>
+        <v>46</v>
       </c>
       <c r="O48" t="s">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3829,33 +3835,33 @@
         <v>1</v>
       </c>
       <c r="R48" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B49" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D49" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E49" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F49" t="s">
+        <v>235</v>
+      </c>
+      <c r="G49" t="s">
+        <v>232</v>
+      </c>
+      <c r="H49" t="s">
         <v>233</v>
-      </c>
-      <c r="G49" t="s">
-        <v>236</v>
-      </c>
-      <c r="H49" t="s">
-        <v>237</v>
       </c>
       <c r="I49" t="s">
         <v>26</v>
@@ -3873,10 +3879,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O49" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3890,37 +3896,37 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>217</v>
+      </c>
+      <c r="B50" t="s">
+        <v>218</v>
+      </c>
+      <c r="C50" t="s">
+        <v>238</v>
+      </c>
+      <c r="D50" t="s">
         <v>239</v>
       </c>
-      <c r="B50" t="s">
+      <c r="E50" t="s">
         <v>240</v>
       </c>
-      <c r="C50" t="s">
-        <v>241</v>
-      </c>
-      <c r="D50" t="s">
-        <v>242</v>
-      </c>
-      <c r="E50" t="s">
-        <v>243</v>
-      </c>
       <c r="F50" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G50" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H50" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I50" t="s">
-        <v>245</v>
+        <v>26</v>
       </c>
       <c r="J50" t="s">
         <v>27</v>
       </c>
       <c r="K50" t="s">
-        <v>246</v>
+        <v>28</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3929,54 +3935,54 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="O50" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="s">
-        <v>248</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C51" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D51" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E51" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F51" t="s">
+        <v>246</v>
+      </c>
+      <c r="G51" t="s">
+        <v>245</v>
+      </c>
+      <c r="H51" t="s">
         <v>244</v>
       </c>
-      <c r="G51" t="s">
-        <v>249</v>
-      </c>
-      <c r="H51" t="s">
-        <v>250</v>
-      </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J51" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="K51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3985,10 +3991,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O51" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3997,42 +4003,42 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B52" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C52" t="s">
+        <v>243</v>
+      </c>
+      <c r="D52" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" t="s">
+        <v>245</v>
+      </c>
+      <c r="F52" t="s">
+        <v>246</v>
+      </c>
+      <c r="G52" t="s">
         <v>251</v>
       </c>
-      <c r="D52" t="s">
+      <c r="H52" t="s">
         <v>252</v>
       </c>
-      <c r="E52" t="s">
-        <v>253</v>
-      </c>
-      <c r="F52" t="s">
-        <v>244</v>
-      </c>
-      <c r="G52" t="s">
-        <v>254</v>
-      </c>
-      <c r="H52" t="s">
-        <v>255</v>
-      </c>
       <c r="I52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J52" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K52" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4041,10 +4047,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4053,27 +4059,27 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C53" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D53" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E53" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F53" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G53" t="s">
         <v>256</v>
@@ -4082,13 +4088,13 @@
         <v>257</v>
       </c>
       <c r="I53" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J53" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K53" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4097,10 +4103,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O53" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4109,27 +4115,27 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C54" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E54" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F54" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G54" t="s">
         <v>258</v>
@@ -4138,13 +4144,13 @@
         <v>259</v>
       </c>
       <c r="I54" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J54" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4153,10 +4159,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O54" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4165,27 +4171,27 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C55" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D55" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E55" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F55" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G55" t="s">
         <v>260</v>
@@ -4194,13 +4200,13 @@
         <v>261</v>
       </c>
       <c r="I55" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J55" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K55" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L55" t="s">
         <v>29</v>
@@ -4209,10 +4215,10 @@
         <v>30</v>
       </c>
       <c r="N55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4221,27 +4227,27 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C56" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D56" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E56" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F56" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G56" t="s">
         <v>262</v>
@@ -4250,13 +4256,13 @@
         <v>263</v>
       </c>
       <c r="I56" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J56" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K56" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L56" t="s">
         <v>29</v>
@@ -4265,10 +4271,10 @@
         <v>30</v>
       </c>
       <c r="N56" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O56" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4277,27 +4283,27 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B57" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C57" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D57" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E57" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F57" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G57" t="s">
         <v>264</v>
@@ -4306,13 +4312,13 @@
         <v>265</v>
       </c>
       <c r="I57" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J57" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K57" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L57" t="s">
         <v>29</v>
@@ -4321,10 +4327,10 @@
         <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O57" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -4333,27 +4339,27 @@
         <v>0</v>
       </c>
       <c r="R57" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C58" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D58" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F58" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G58" t="s">
         <v>266</v>
@@ -4362,13 +4368,13 @@
         <v>267</v>
       </c>
       <c r="I58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="J58" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K58" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="L58" t="s">
         <v>29</v>
@@ -4377,19 +4383,75 @@
         <v>30</v>
       </c>
       <c r="N58" t="s">
+        <v>249</v>
+      </c>
+      <c r="O58" t="s">
+        <v>249</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>241</v>
+      </c>
+      <c r="B59" t="s">
+        <v>242</v>
+      </c>
+      <c r="C59" t="s">
+        <v>253</v>
+      </c>
+      <c r="D59" t="s">
+        <v>254</v>
+      </c>
+      <c r="E59" t="s">
+        <v>255</v>
+      </c>
+      <c r="F59" t="s">
+        <v>246</v>
+      </c>
+      <c r="G59" t="s">
+        <v>268</v>
+      </c>
+      <c r="H59" t="s">
+        <v>269</v>
+      </c>
+      <c r="I59" t="s">
         <v>247</v>
       </c>
-      <c r="O58" t="s">
-        <v>247</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="s">
+      <c r="J59" t="s">
+        <v>146</v>
+      </c>
+      <c r="K59" t="s">
         <v>248</v>
+      </c>
+      <c r="L59" t="s">
+        <v>29</v>
+      </c>
+      <c r="M59" t="s">
+        <v>30</v>
+      </c>
+      <c r="N59" t="s">
+        <v>249</v>
+      </c>
+      <c r="O59" t="s">
+        <v>249</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="s">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -308,424 +308,430 @@
     <t xml:space="preserve">venture-capital-volume</t>
   </si>
   <si>
+    <t xml:space="preserve">DMV-2026-05-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-03-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active listing count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">active-listing-count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential listing price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-listing-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median residential sale price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-sale-price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">List-to-sale price ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list-to-sale-ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homes sold above list price (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">homes-sold-above-list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median square feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-square-feet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median listing price per square foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mlpsq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mspsq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median days on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-dom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total air passengers served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-passengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">municipal-services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household Wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household-wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-prime consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severely credit-constrained consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-subprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personal-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medicaid-enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State agency reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M10</t>
+  </si>
+  <si>
     <t xml:space="preserve">DMV-2026-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-03-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active listing count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listing-count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential sale price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-sale-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List-to-sale price ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list-to-sale-ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homes sold above list price (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homes-sold-above-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median square feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-square-feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median listing price per square foot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mlpsq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median days on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-prime consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-nearprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severely credit-constrained consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-subprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">personal-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
   </si>
   <si>
     <t xml:space="preserve">SNAP participation</t>
@@ -1863,10 +1869,10 @@
         <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="O13" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1919,10 +1925,10 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="O14" t="s">
-        <v>79</v>
+        <v>32</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1975,10 +1981,10 @@
         <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="O15" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1987,7 +1993,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16">
@@ -3074,10 +3080,10 @@
         <v>155</v>
       </c>
       <c r="G35" t="s">
+        <v>169</v>
+      </c>
+      <c r="H35" t="s">
         <v>171</v>
-      </c>
-      <c r="H35" t="s">
-        <v>172</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
@@ -3118,22 +3124,22 @@
         <v>139</v>
       </c>
       <c r="C36" t="s">
+        <v>152</v>
+      </c>
+      <c r="D36" t="s">
+        <v>153</v>
+      </c>
+      <c r="E36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F36" t="s">
+        <v>155</v>
+      </c>
+      <c r="G36" t="s">
+        <v>172</v>
+      </c>
+      <c r="H36" t="s">
         <v>173</v>
-      </c>
-      <c r="D36" t="s">
-        <v>174</v>
-      </c>
-      <c r="E36" t="s">
-        <v>175</v>
-      </c>
-      <c r="F36" t="s">
-        <v>176</v>
-      </c>
-      <c r="G36" t="s">
-        <v>173</v>
-      </c>
-      <c r="H36" t="s">
-        <v>174</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
@@ -3168,34 +3174,34 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>138</v>
+      </c>
+      <c r="B37" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" t="s">
         <v>177</v>
       </c>
-      <c r="B37" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" t="s">
-        <v>179</v>
-      </c>
-      <c r="D37" t="s">
-        <v>180</v>
-      </c>
-      <c r="E37" t="s">
-        <v>181</v>
-      </c>
-      <c r="F37" t="s">
-        <v>143</v>
-      </c>
       <c r="G37" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H37" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="K37" t="s">
         <v>28</v>
@@ -3207,51 +3213,51 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="O37" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E38" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F38" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
       <c r="G38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H38" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
@@ -3263,10 +3269,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>188</v>
+        <v>55</v>
       </c>
       <c r="O38" t="s">
-        <v>189</v>
+        <v>56</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -3275,95 +3281,95 @@
         <v>0</v>
       </c>
       <c r="R38" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C39" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D39" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E39" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F39" t="s">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="G39" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="H39" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K39" t="s">
         <v>28</v>
       </c>
       <c r="L39" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M39" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>70</v>
+        <v>189</v>
       </c>
       <c r="O39" t="s">
-        <v>71</v>
+        <v>190</v>
       </c>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
       </c>
       <c r="R39" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C40" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="D40" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="E40" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F40" t="s">
         <v>65</v>
       </c>
       <c r="G40" t="s">
+        <v>194</v>
+      </c>
+      <c r="H40" t="s">
         <v>195</v>
-      </c>
-      <c r="H40" t="s">
-        <v>196</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K40" t="s">
         <v>28</v>
@@ -3392,140 +3398,140 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" t="s">
+        <v>179</v>
+      </c>
+      <c r="C41" t="s">
+        <v>196</v>
+      </c>
+      <c r="D41" t="s">
         <v>197</v>
       </c>
-      <c r="B41" t="s">
-        <v>198</v>
-      </c>
-      <c r="C41" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" t="s">
-        <v>200</v>
-      </c>
       <c r="E41" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F41" t="s">
-        <v>202</v>
+        <v>65</v>
       </c>
       <c r="G41" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="H41" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="K41" t="s">
         <v>28</v>
       </c>
       <c r="L41" t="s">
-        <v>205</v>
+        <v>68</v>
       </c>
       <c r="M41" t="s">
-        <v>206</v>
+        <v>69</v>
       </c>
       <c r="N41" t="s">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="O41" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B42" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C42" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="D42" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E42" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="F42" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G42" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="H42" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>43</v>
+        <v>77</v>
       </c>
       <c r="K42" t="s">
         <v>28</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>206</v>
       </c>
       <c r="M42" t="s">
-        <v>30</v>
+        <v>207</v>
       </c>
       <c r="N42" t="s">
-        <v>55</v>
+        <v>189</v>
       </c>
       <c r="O42" t="s">
-        <v>56</v>
+        <v>190</v>
       </c>
       <c r="P42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C43" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G43" t="s">
+        <v>212</v>
+      </c>
+      <c r="H43" t="s">
         <v>213</v>
-      </c>
-      <c r="H43" t="s">
-        <v>214</v>
       </c>
       <c r="I43" t="s">
         <v>26</v>
@@ -3560,28 +3566,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B44" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C44" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D44" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G44" t="s">
+        <v>214</v>
+      </c>
+      <c r="H44" t="s">
         <v>215</v>
-      </c>
-      <c r="H44" t="s">
-        <v>216</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3616,37 +3622,37 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B45" t="s">
+        <v>199</v>
+      </c>
+      <c r="C45" t="s">
+        <v>208</v>
+      </c>
+      <c r="D45" t="s">
+        <v>209</v>
+      </c>
+      <c r="E45" t="s">
+        <v>210</v>
+      </c>
+      <c r="F45" t="s">
+        <v>211</v>
+      </c>
+      <c r="G45" t="s">
+        <v>216</v>
+      </c>
+      <c r="H45" t="s">
         <v>217</v>
-      </c>
-      <c r="B45" t="s">
-        <v>218</v>
-      </c>
-      <c r="C45" t="s">
-        <v>219</v>
-      </c>
-      <c r="D45" t="s">
-        <v>220</v>
-      </c>
-      <c r="E45" t="s">
-        <v>221</v>
-      </c>
-      <c r="F45" t="s">
-        <v>222</v>
-      </c>
-      <c r="G45" t="s">
-        <v>223</v>
-      </c>
-      <c r="H45" t="s">
-        <v>224</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="K45" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L45" t="s">
         <v>29</v>
@@ -3655,10 +3661,10 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>147</v>
+        <v>55</v>
       </c>
       <c r="O45" t="s">
-        <v>148</v>
+        <v>56</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3667,33 +3673,33 @@
         <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B46" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D46" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F46" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G46" t="s">
+        <v>224</v>
+      </c>
+      <c r="H46" t="s">
         <v>225</v>
-      </c>
-      <c r="H46" t="s">
-        <v>226</v>
       </c>
       <c r="I46" t="s">
         <v>26</v>
@@ -3728,28 +3734,28 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C47" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E47" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G47" t="s">
+        <v>226</v>
+      </c>
+      <c r="H47" t="s">
         <v>227</v>
-      </c>
-      <c r="H47" t="s">
-        <v>228</v>
       </c>
       <c r="I47" t="s">
         <v>26</v>
@@ -3784,49 +3790,49 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B48" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C48" t="s">
+        <v>220</v>
+      </c>
+      <c r="D48" t="s">
+        <v>221</v>
+      </c>
+      <c r="E48" t="s">
+        <v>222</v>
+      </c>
+      <c r="F48" t="s">
+        <v>223</v>
+      </c>
+      <c r="G48" t="s">
+        <v>228</v>
+      </c>
+      <c r="H48" t="s">
         <v>229</v>
       </c>
-      <c r="D48" t="s">
-        <v>230</v>
-      </c>
-      <c r="E48" t="s">
-        <v>231</v>
-      </c>
-      <c r="F48" t="s">
-        <v>41</v>
-      </c>
-      <c r="G48" t="s">
-        <v>229</v>
-      </c>
-      <c r="H48" t="s">
-        <v>230</v>
-      </c>
       <c r="I48" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J48" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K48" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L48" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M48" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>46</v>
+        <v>147</v>
       </c>
       <c r="O48" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3840,49 +3846,49 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B49" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C49" t="s">
+        <v>230</v>
+      </c>
+      <c r="D49" t="s">
+        <v>231</v>
+      </c>
+      <c r="E49" t="s">
         <v>232</v>
       </c>
-      <c r="D49" t="s">
-        <v>233</v>
-      </c>
-      <c r="E49" t="s">
-        <v>234</v>
-      </c>
       <c r="F49" t="s">
-        <v>235</v>
+        <v>41</v>
       </c>
       <c r="G49" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H49" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I49" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J49" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K49" t="s">
         <v>28</v>
       </c>
       <c r="L49" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M49" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N49" t="s">
-        <v>236</v>
+        <v>46</v>
       </c>
       <c r="O49" t="s">
-        <v>237</v>
+        <v>47</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3891,33 +3897,33 @@
         <v>1</v>
       </c>
       <c r="R49" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C50" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D50" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="E50" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F50" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G50" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="H50" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I50" t="s">
         <v>26</v>
@@ -3935,10 +3941,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3947,42 +3953,42 @@
         <v>1</v>
       </c>
       <c r="R50" t="s">
-        <v>98</v>
+        <v>239</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" t="s">
+        <v>219</v>
+      </c>
+      <c r="C51" t="s">
+        <v>240</v>
+      </c>
+      <c r="D51" t="s">
         <v>241</v>
       </c>
-      <c r="B51" t="s">
+      <c r="E51" t="s">
         <v>242</v>
       </c>
-      <c r="C51" t="s">
-        <v>243</v>
-      </c>
-      <c r="D51" t="s">
-        <v>244</v>
-      </c>
-      <c r="E51" t="s">
-        <v>245</v>
-      </c>
       <c r="F51" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="G51" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="H51" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="I51" t="s">
-        <v>247</v>
+        <v>26</v>
       </c>
       <c r="J51" t="s">
         <v>27</v>
       </c>
       <c r="K51" t="s">
-        <v>248</v>
+        <v>28</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3991,54 +3997,54 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="O51" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B52" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C52" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D52" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F52" t="s">
+        <v>248</v>
+      </c>
+      <c r="G52" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" t="s">
         <v>246</v>
       </c>
-      <c r="G52" t="s">
-        <v>251</v>
-      </c>
-      <c r="H52" t="s">
-        <v>252</v>
-      </c>
       <c r="I52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J52" t="s">
-        <v>146</v>
+        <v>27</v>
       </c>
       <c r="K52" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4047,10 +4053,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O52" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4059,42 +4065,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B53" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C53" t="s">
+        <v>245</v>
+      </c>
+      <c r="D53" t="s">
+        <v>246</v>
+      </c>
+      <c r="E53" t="s">
+        <v>247</v>
+      </c>
+      <c r="F53" t="s">
+        <v>248</v>
+      </c>
+      <c r="G53" t="s">
         <v>253</v>
       </c>
-      <c r="D53" t="s">
+      <c r="H53" t="s">
         <v>254</v>
       </c>
-      <c r="E53" t="s">
-        <v>255</v>
-      </c>
-      <c r="F53" t="s">
-        <v>246</v>
-      </c>
-      <c r="G53" t="s">
-        <v>256</v>
-      </c>
-      <c r="H53" t="s">
-        <v>257</v>
-      </c>
       <c r="I53" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J53" t="s">
         <v>146</v>
       </c>
       <c r="K53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4103,10 +4109,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O53" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4115,27 +4121,27 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B54" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C54" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D54" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E54" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F54" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G54" t="s">
         <v>258</v>
@@ -4144,13 +4150,13 @@
         <v>259</v>
       </c>
       <c r="I54" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J54" t="s">
         <v>146</v>
       </c>
       <c r="K54" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4159,10 +4165,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O54" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4171,27 +4177,27 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C55" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D55" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E55" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F55" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G55" t="s">
         <v>260</v>
@@ -4200,13 +4206,13 @@
         <v>261</v>
       </c>
       <c r="I55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J55" t="s">
         <v>146</v>
       </c>
       <c r="K55" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L55" t="s">
         <v>29</v>
@@ -4215,10 +4221,10 @@
         <v>30</v>
       </c>
       <c r="N55" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O55" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P55" t="n">
         <v>1</v>
@@ -4227,27 +4233,27 @@
         <v>0</v>
       </c>
       <c r="R55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B56" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C56" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E56" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F56" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G56" t="s">
         <v>262</v>
@@ -4256,13 +4262,13 @@
         <v>263</v>
       </c>
       <c r="I56" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J56" t="s">
         <v>146</v>
       </c>
       <c r="K56" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L56" t="s">
         <v>29</v>
@@ -4271,10 +4277,10 @@
         <v>30</v>
       </c>
       <c r="N56" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O56" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -4283,27 +4289,27 @@
         <v>0</v>
       </c>
       <c r="R56" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B57" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C57" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D57" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E57" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F57" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G57" t="s">
         <v>264</v>
@@ -4312,13 +4318,13 @@
         <v>265</v>
       </c>
       <c r="I57" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J57" t="s">
         <v>146</v>
       </c>
       <c r="K57" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L57" t="s">
         <v>29</v>
@@ -4327,10 +4333,10 @@
         <v>30</v>
       </c>
       <c r="N57" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O57" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P57" t="n">
         <v>1</v>
@@ -4339,27 +4345,27 @@
         <v>0</v>
       </c>
       <c r="R57" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B58" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C58" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E58" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F58" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G58" t="s">
         <v>266</v>
@@ -4368,13 +4374,13 @@
         <v>267</v>
       </c>
       <c r="I58" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J58" t="s">
         <v>146</v>
       </c>
       <c r="K58" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L58" t="s">
         <v>29</v>
@@ -4383,10 +4389,10 @@
         <v>30</v>
       </c>
       <c r="N58" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="O58" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="P58" t="n">
         <v>1</v>
@@ -4395,27 +4401,27 @@
         <v>0</v>
       </c>
       <c r="R58" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B59" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C59" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E59" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F59" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G59" t="s">
         <v>268</v>
@@ -4424,13 +4430,13 @@
         <v>269</v>
       </c>
       <c r="I59" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J59" t="s">
         <v>146</v>
       </c>
       <c r="K59" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L59" t="s">
         <v>29</v>
@@ -4439,19 +4445,75 @@
         <v>30</v>
       </c>
       <c r="N59" t="s">
+        <v>251</v>
+      </c>
+      <c r="O59" t="s">
+        <v>251</v>
+      </c>
+      <c r="P59" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>243</v>
+      </c>
+      <c r="B60" t="s">
+        <v>244</v>
+      </c>
+      <c r="C60" t="s">
+        <v>255</v>
+      </c>
+      <c r="D60" t="s">
+        <v>256</v>
+      </c>
+      <c r="E60" t="s">
+        <v>257</v>
+      </c>
+      <c r="F60" t="s">
+        <v>248</v>
+      </c>
+      <c r="G60" t="s">
+        <v>270</v>
+      </c>
+      <c r="H60" t="s">
+        <v>271</v>
+      </c>
+      <c r="I60" t="s">
         <v>249</v>
       </c>
-      <c r="O59" t="s">
-        <v>249</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="s">
+      <c r="J60" t="s">
+        <v>146</v>
+      </c>
+      <c r="K60" t="s">
         <v>250</v>
+      </c>
+      <c r="L60" t="s">
+        <v>29</v>
+      </c>
+      <c r="M60" t="s">
+        <v>30</v>
+      </c>
+      <c r="N60" t="s">
+        <v>251</v>
+      </c>
+      <c r="O60" t="s">
+        <v>251</v>
+      </c>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">level</t>
   </si>
   <si>
-    <t xml:space="preserve">2025M2</t>
+    <t xml:space="preserve">2024M2</t>
   </si>
   <si>
     <t xml:space="preserve">2026M2</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">rolling-12-sum</t>
   </si>
   <si>
-    <t xml:space="preserve">2025Q1</t>
+    <t xml:space="preserve">2024Q1</t>
   </si>
   <si>
     <t xml:space="preserve">2026Q1</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">unique-postings-total</t>
   </si>
   <si>
-    <t xml:space="preserve">2025M3</t>
+    <t xml:space="preserve">2024M3</t>
   </si>
   <si>
     <t xml:space="preserve">2026M3</t>
@@ -482,60 +482,27 @@
     <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
   </si>
   <si>
-    <t xml:space="preserve">Active listing count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">active-listing-count</t>
+    <t xml:space="preserve">Median sale price per square foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mspsq</t>
   </si>
   <si>
     <t xml:space="preserve">DMV-2026-04-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Median residential listing price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-listing-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median residential sale price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-sale-price</t>
-  </si>
-  <si>
-    <t xml:space="preserve">List-to-sale price ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">list-to-sale-ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Homes sold above list price (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">homes-sold-above-list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median square feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-square-feet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median listing price per square foot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mlpsq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mspsq</t>
-  </si>
-  <si>
     <t xml:space="preserve">Median days on market</t>
   </si>
   <si>
     <t xml:space="preserve">median-dom</t>
   </si>
   <si>
+    <t xml:space="preserve">Number of pending sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pending-sales</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observed rental index</t>
   </si>
   <si>
@@ -581,7 +548,7 @@
     <t xml:space="preserve">air-passengers</t>
   </si>
   <si>
-    <t xml:space="preserve">2025M1</t>
+    <t xml:space="preserve">2024M1</t>
   </si>
   <si>
     <t xml:space="preserve">2026M1</t>
@@ -2697,7 +2664,7 @@
         <v>26</v>
       </c>
       <c r="J28" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K28" t="s">
         <v>28</v>
@@ -2753,7 +2720,7 @@
         <v>26</v>
       </c>
       <c r="J29" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="K29" t="s">
         <v>28</v>
@@ -2809,7 +2776,7 @@
         <v>26</v>
       </c>
       <c r="J30" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K30" t="s">
         <v>28</v>
@@ -2844,16 +2811,16 @@
         <v>139</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F31" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="G31" t="s">
         <v>163</v>
@@ -2865,10 +2832,10 @@
         <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L31" t="s">
         <v>29</v>
@@ -2894,37 +2861,37 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C32" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="D32" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="E32" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="F32" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="G32" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="H32" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="K32" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L32" t="s">
         <v>29</v>
@@ -2933,45 +2900,45 @@
         <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="O32" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="E33" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="G33" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="H33" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2989,45 +2956,45 @@
         <v>30</v>
       </c>
       <c r="N33" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="O33" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
       </c>
       <c r="R33" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C34" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D34" t="s">
-        <v>153</v>
+        <v>181</v>
       </c>
       <c r="E34" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="F34" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="H34" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
@@ -3039,16 +3006,16 @@
         <v>28</v>
       </c>
       <c r="L34" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M34" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="N34" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="O34" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="P34" t="n">
         <v>1</v>
@@ -3057,54 +3024,54 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="D35" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="E35" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="F35" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="H35" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M35" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="N35" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="O35" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="P35" t="n">
         <v>1</v>
@@ -3113,95 +3080,95 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>158</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="C36" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="D36" t="s">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="E36" t="s">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="F36" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="G36" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="H36" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>54</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>195</v>
       </c>
       <c r="M36" t="s">
-        <v>30</v>
+        <v>196</v>
       </c>
       <c r="N36" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
       <c r="O36" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s">
-        <v>139</v>
+        <v>188</v>
       </c>
       <c r="C37" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="E37" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="F37" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="H37" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
       </c>
       <c r="J37" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="K37" t="s">
         <v>28</v>
@@ -3213,51 +3180,51 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>126</v>
+        <v>55</v>
       </c>
       <c r="O37" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C38" t="s">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="F38" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="G38" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="H38" t="s">
-        <v>181</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>183</v>
+        <v>43</v>
       </c>
       <c r="K38" t="s">
         <v>28</v>
@@ -3275,45 +3242,45 @@
         <v>56</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B39" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C39" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="D39" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="E39" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F39" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="H39" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K39" t="s">
         <v>28</v>
@@ -3325,184 +3292,184 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="O39" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="B40" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E40" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="F40" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="G40" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="H40" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
       </c>
       <c r="J40" t="s">
-        <v>54</v>
+        <v>108</v>
       </c>
       <c r="K40" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L40" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M40" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="O40" t="s">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>178</v>
+        <v>207</v>
       </c>
       <c r="B41" t="s">
-        <v>179</v>
+        <v>208</v>
       </c>
       <c r="C41" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D41" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="E41" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F41" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="G41" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="H41" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
       </c>
       <c r="J41" t="s">
-        <v>27</v>
+        <v>108</v>
       </c>
       <c r="K41" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="M41" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>70</v>
+        <v>147</v>
       </c>
       <c r="O41" t="s">
-        <v>71</v>
+        <v>148</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B42" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C42" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="F42" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="G42" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="H42" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
       </c>
       <c r="J42" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="K42" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L42" t="s">
-        <v>206</v>
+        <v>29</v>
       </c>
       <c r="M42" t="s">
-        <v>207</v>
+        <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>189</v>
+        <v>147</v>
       </c>
       <c r="O42" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="s">
         <v>33</v>
@@ -3510,31 +3477,31 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B43" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C43" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D43" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E43" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F43" t="s">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="H43" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="I43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J43" t="s">
         <v>43</v>
@@ -3543,16 +3510,16 @@
         <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M43" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N43" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O43" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3561,39 +3528,39 @@
         <v>1</v>
       </c>
       <c r="R43" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="D44" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E44" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F44" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="G44" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="H44" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
       </c>
       <c r="J44" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K44" t="s">
         <v>28</v>
@@ -3605,10 +3572,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="O44" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3617,39 +3584,39 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="D45" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="E45" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="F45" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="G45" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="H45" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
       </c>
       <c r="J45" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K45" t="s">
         <v>28</v>
@@ -3661,10 +3628,10 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>55</v>
+        <v>226</v>
       </c>
       <c r="O45" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3673,42 +3640,42 @@
         <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>57</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B46" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C46" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E46" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F46" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G46" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="H46" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="I46" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
       <c r="J46" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="K46" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3717,54 +3684,54 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="O46" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B47" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C47" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="D47" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="E47" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="F47" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G47" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="H47" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="I47" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
       <c r="J47" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="K47" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3773,54 +3740,54 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="O47" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B48" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C48" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="D48" t="s">
-        <v>221</v>
+        <v>245</v>
       </c>
       <c r="E48" t="s">
-        <v>222</v>
+        <v>246</v>
       </c>
       <c r="F48" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G48" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="H48" t="s">
-        <v>229</v>
+        <v>248</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
       <c r="J48" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="K48" t="s">
-        <v>109</v>
+        <v>239</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3829,110 +3796,110 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>147</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s">
-        <v>148</v>
+        <v>240</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C49" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="D49" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="E49" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="F49" t="s">
-        <v>41</v>
+        <v>237</v>
       </c>
       <c r="G49" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="H49" t="s">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="I49" t="s">
-        <v>42</v>
+        <v>238</v>
       </c>
       <c r="J49" t="s">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="K49" t="s">
-        <v>28</v>
+        <v>239</v>
       </c>
       <c r="L49" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M49" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="O49" t="s">
-        <v>47</v>
+        <v>240</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B50" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C50" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D50" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="E50" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G50" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="H50" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="I50" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
       <c r="J50" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K50" t="s">
-        <v>28</v>
+        <v>239</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3941,54 +3908,54 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O50" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="C51" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="D51" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="F51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G51" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="H51" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="I51" t="s">
-        <v>26</v>
+        <v>238</v>
       </c>
       <c r="J51" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K51" t="s">
-        <v>28</v>
+        <v>239</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3997,54 +3964,54 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O51" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s">
+        <v>233</v>
+      </c>
+      <c r="C52" t="s">
         <v>244</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>245</v>
       </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>246</v>
       </c>
-      <c r="E52" t="s">
-        <v>247</v>
-      </c>
       <c r="F52" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G52" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="H52" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="I52" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="J52" t="s">
-        <v>27</v>
+        <v>146</v>
       </c>
       <c r="K52" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4053,10 +4020,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="O52" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4065,42 +4032,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" t="s">
         <v>244</v>
       </c>
-      <c r="C53" t="s">
+      <c r="D53" t="s">
         <v>245</v>
       </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>246</v>
       </c>
-      <c r="E53" t="s">
-        <v>247</v>
-      </c>
       <c r="F53" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G53" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H53" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="I53" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="J53" t="s">
         <v>146</v>
       </c>
       <c r="K53" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4109,10 +4076,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="O53" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4121,42 +4088,42 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="B54" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" t="s">
         <v>244</v>
       </c>
-      <c r="C54" t="s">
-        <v>255</v>
-      </c>
       <c r="D54" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="E54" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F54" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G54" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H54" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I54" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="J54" t="s">
         <v>146</v>
       </c>
       <c r="K54" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4165,10 +4132,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="O54" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4177,343 +4144,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>243</v>
-      </c>
-      <c r="B55" t="s">
-        <v>244</v>
-      </c>
-      <c r="C55" t="s">
-        <v>255</v>
-      </c>
-      <c r="D55" t="s">
-        <v>256</v>
-      </c>
-      <c r="E55" t="s">
-        <v>257</v>
-      </c>
-      <c r="F55" t="s">
-        <v>248</v>
-      </c>
-      <c r="G55" t="s">
-        <v>260</v>
-      </c>
-      <c r="H55" t="s">
-        <v>261</v>
-      </c>
-      <c r="I55" t="s">
-        <v>249</v>
-      </c>
-      <c r="J55" t="s">
-        <v>146</v>
-      </c>
-      <c r="K55" t="s">
-        <v>250</v>
-      </c>
-      <c r="L55" t="s">
-        <v>29</v>
-      </c>
-      <c r="M55" t="s">
-        <v>30</v>
-      </c>
-      <c r="N55" t="s">
-        <v>251</v>
-      </c>
-      <c r="O55" t="s">
-        <v>251</v>
-      </c>
-      <c r="P55" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>243</v>
-      </c>
-      <c r="B56" t="s">
-        <v>244</v>
-      </c>
-      <c r="C56" t="s">
-        <v>255</v>
-      </c>
-      <c r="D56" t="s">
-        <v>256</v>
-      </c>
-      <c r="E56" t="s">
-        <v>257</v>
-      </c>
-      <c r="F56" t="s">
-        <v>248</v>
-      </c>
-      <c r="G56" t="s">
-        <v>262</v>
-      </c>
-      <c r="H56" t="s">
-        <v>263</v>
-      </c>
-      <c r="I56" t="s">
-        <v>249</v>
-      </c>
-      <c r="J56" t="s">
-        <v>146</v>
-      </c>
-      <c r="K56" t="s">
-        <v>250</v>
-      </c>
-      <c r="L56" t="s">
-        <v>29</v>
-      </c>
-      <c r="M56" t="s">
-        <v>30</v>
-      </c>
-      <c r="N56" t="s">
-        <v>251</v>
-      </c>
-      <c r="O56" t="s">
-        <v>251</v>
-      </c>
-      <c r="P56" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>243</v>
-      </c>
-      <c r="B57" t="s">
-        <v>244</v>
-      </c>
-      <c r="C57" t="s">
-        <v>255</v>
-      </c>
-      <c r="D57" t="s">
-        <v>256</v>
-      </c>
-      <c r="E57" t="s">
-        <v>257</v>
-      </c>
-      <c r="F57" t="s">
-        <v>248</v>
-      </c>
-      <c r="G57" t="s">
-        <v>264</v>
-      </c>
-      <c r="H57" t="s">
-        <v>265</v>
-      </c>
-      <c r="I57" t="s">
-        <v>249</v>
-      </c>
-      <c r="J57" t="s">
-        <v>146</v>
-      </c>
-      <c r="K57" t="s">
-        <v>250</v>
-      </c>
-      <c r="L57" t="s">
-        <v>29</v>
-      </c>
-      <c r="M57" t="s">
-        <v>30</v>
-      </c>
-      <c r="N57" t="s">
-        <v>251</v>
-      </c>
-      <c r="O57" t="s">
-        <v>251</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>243</v>
-      </c>
-      <c r="B58" t="s">
-        <v>244</v>
-      </c>
-      <c r="C58" t="s">
-        <v>255</v>
-      </c>
-      <c r="D58" t="s">
-        <v>256</v>
-      </c>
-      <c r="E58" t="s">
-        <v>257</v>
-      </c>
-      <c r="F58" t="s">
-        <v>248</v>
-      </c>
-      <c r="G58" t="s">
-        <v>266</v>
-      </c>
-      <c r="H58" t="s">
-        <v>267</v>
-      </c>
-      <c r="I58" t="s">
-        <v>249</v>
-      </c>
-      <c r="J58" t="s">
-        <v>146</v>
-      </c>
-      <c r="K58" t="s">
-        <v>250</v>
-      </c>
-      <c r="L58" t="s">
-        <v>29</v>
-      </c>
-      <c r="M58" t="s">
-        <v>30</v>
-      </c>
-      <c r="N58" t="s">
-        <v>251</v>
-      </c>
-      <c r="O58" t="s">
-        <v>251</v>
-      </c>
-      <c r="P58" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>243</v>
-      </c>
-      <c r="B59" t="s">
-        <v>244</v>
-      </c>
-      <c r="C59" t="s">
-        <v>255</v>
-      </c>
-      <c r="D59" t="s">
-        <v>256</v>
-      </c>
-      <c r="E59" t="s">
-        <v>257</v>
-      </c>
-      <c r="F59" t="s">
-        <v>248</v>
-      </c>
-      <c r="G59" t="s">
-        <v>268</v>
-      </c>
-      <c r="H59" t="s">
-        <v>269</v>
-      </c>
-      <c r="I59" t="s">
-        <v>249</v>
-      </c>
-      <c r="J59" t="s">
-        <v>146</v>
-      </c>
-      <c r="K59" t="s">
-        <v>250</v>
-      </c>
-      <c r="L59" t="s">
-        <v>29</v>
-      </c>
-      <c r="M59" t="s">
-        <v>30</v>
-      </c>
-      <c r="N59" t="s">
-        <v>251</v>
-      </c>
-      <c r="O59" t="s">
-        <v>251</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>243</v>
-      </c>
-      <c r="B60" t="s">
-        <v>244</v>
-      </c>
-      <c r="C60" t="s">
-        <v>255</v>
-      </c>
-      <c r="D60" t="s">
-        <v>256</v>
-      </c>
-      <c r="E60" t="s">
-        <v>257</v>
-      </c>
-      <c r="F60" t="s">
-        <v>248</v>
-      </c>
-      <c r="G60" t="s">
-        <v>270</v>
-      </c>
-      <c r="H60" t="s">
-        <v>271</v>
-      </c>
-      <c r="I60" t="s">
-        <v>249</v>
-      </c>
-      <c r="J60" t="s">
-        <v>146</v>
-      </c>
-      <c r="K60" t="s">
-        <v>250</v>
-      </c>
-      <c r="L60" t="s">
-        <v>29</v>
-      </c>
-      <c r="M60" t="s">
-        <v>30</v>
-      </c>
-      <c r="N60" t="s">
-        <v>251</v>
-      </c>
-      <c r="O60" t="s">
-        <v>251</v>
-      </c>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -107,558 +107,543 @@
     <t xml:space="preserve">level</t>
   </si>
   <si>
+    <t xml:space="preserve">2024M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 12-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-12-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USASpending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
     <t xml:space="preserve">2024M2</t>
   </si>
   <si>
     <t xml:space="preserve">2026M2</t>
   </si>
   <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median sale price per square foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mspsq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median days on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-dom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of pending sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pending-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total air passengers served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-passengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">municipal-services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household Wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household-wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-prime consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q4</t>
+  </si>
+  <si>
     <t xml:space="preserve">DMV-2026-05-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Private sector jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal government jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-federal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 12-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-12-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-05-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-03-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median sale price per square foot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mspsq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median days on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of pending sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pending-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-prime consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-nearprime</t>
-  </si>
-  <si>
     <t xml:space="preserve">Severely credit-constrained consumers</t>
   </si>
   <si>
@@ -690,15 +675,6 @@
   </si>
   <si>
     <t xml:space="preserve">State agency reporting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-02-09</t>
   </si>
   <si>
     <t xml:space="preserve">SNAP participation</t>
@@ -1624,7 +1600,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -1635,28 +1611,28 @@
         <v>19</v>
       </c>
       <c r="C10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" t="s">
         <v>73</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>74</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>75</v>
       </c>
-      <c r="F10" t="s">
-        <v>76</v>
-      </c>
       <c r="G10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" t="s">
         <v>73</v>
-      </c>
-      <c r="H10" t="s">
-        <v>74</v>
       </c>
       <c r="I10" t="s">
         <v>26</v>
       </c>
       <c r="J10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K10" t="s">
         <v>28</v>
@@ -1668,11 +1644,11 @@
         <v>30</v>
       </c>
       <c r="N10" t="s">
+        <v>77</v>
+      </c>
+      <c r="O10" t="s">
         <v>78</v>
       </c>
-      <c r="O10" t="s">
-        <v>79</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1680,33 +1656,33 @@
         <v>0</v>
       </c>
       <c r="R10" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" t="s">
         <v>80</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>81</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>82</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>84</v>
       </c>
       <c r="F11" t="s">
         <v>51</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s">
         <v>26</v>
@@ -1741,28 +1717,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
         <v>80</v>
       </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
       <c r="C12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
         <v>86</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>87</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>88</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>89</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>90</v>
-      </c>
-      <c r="H12" t="s">
-        <v>91</v>
       </c>
       <c r="I12" t="s">
         <v>26</v>
@@ -1780,10 +1756,10 @@
         <v>45</v>
       </c>
       <c r="N12" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="O12" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="P12" t="n">
         <v>1</v>
@@ -1797,28 +1773,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
         <v>80</v>
       </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I13" t="s">
         <v>26</v>
@@ -1836,10 +1812,10 @@
         <v>45</v>
       </c>
       <c r="N13" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="O13" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="P13" t="n">
         <v>1</v>
@@ -1848,27 +1824,27 @@
         <v>0</v>
       </c>
       <c r="R13" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" t="s">
         <v>80</v>
       </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G14" t="s">
         <v>99</v>
@@ -1892,10 +1868,10 @@
         <v>45</v>
       </c>
       <c r="N14" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="O14" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
@@ -1904,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -1948,10 +1924,10 @@
         <v>69</v>
       </c>
       <c r="N15" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="O15" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1960,7 +1936,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -2004,10 +1980,10 @@
         <v>69</v>
       </c>
       <c r="N16" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O16" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P16" t="n">
         <v>1</v>
@@ -2060,10 +2036,10 @@
         <v>69</v>
       </c>
       <c r="N17" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O17" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
@@ -2116,10 +2092,10 @@
         <v>69</v>
       </c>
       <c r="N18" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O18" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -2172,10 +2148,10 @@
         <v>69</v>
       </c>
       <c r="N19" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O19" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P19" t="n">
         <v>1</v>
@@ -2228,10 +2204,10 @@
         <v>69</v>
       </c>
       <c r="N20" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O20" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
@@ -2284,10 +2260,10 @@
         <v>69</v>
       </c>
       <c r="N21" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="O21" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="P21" t="n">
         <v>1</v>
@@ -2319,10 +2295,10 @@
         <v>123</v>
       </c>
       <c r="G22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I22" t="s">
         <v>26</v>
@@ -2340,10 +2316,10 @@
         <v>69</v>
       </c>
       <c r="N22" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="O22" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="P22" t="n">
         <v>1</v>
@@ -2375,10 +2351,10 @@
         <v>123</v>
       </c>
       <c r="G23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="I23" t="s">
         <v>26</v>
@@ -2396,10 +2372,10 @@
         <v>69</v>
       </c>
       <c r="N23" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="O23" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
@@ -2431,10 +2407,10 @@
         <v>123</v>
       </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I24" t="s">
         <v>26</v>
@@ -2452,10 +2428,10 @@
         <v>69</v>
       </c>
       <c r="N24" t="s">
-        <v>126</v>
+        <v>31</v>
       </c>
       <c r="O24" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
@@ -2475,22 +2451,22 @@
         <v>102</v>
       </c>
       <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>133</v>
+      </c>
+      <c r="E25" t="s">
         <v>134</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
         <v>135</v>
       </c>
-      <c r="E25" t="s">
-        <v>136</v>
-      </c>
-      <c r="F25" t="s">
-        <v>137</v>
-      </c>
       <c r="G25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I25" t="s">
         <v>26</v>
@@ -2508,10 +2484,10 @@
         <v>45</v>
       </c>
       <c r="N25" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="O25" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
@@ -2525,34 +2501,34 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" t="s">
         <v>138</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" t="s">
         <v>139</v>
       </c>
-      <c r="C26" t="s">
+      <c r="E26" t="s">
         <v>140</v>
       </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>141</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>142</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>143</v>
-      </c>
-      <c r="G26" t="s">
-        <v>144</v>
-      </c>
-      <c r="H26" t="s">
-        <v>145</v>
       </c>
       <c r="I26" t="s">
         <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K26" t="s">
         <v>109</v>
@@ -2564,10 +2540,10 @@
         <v>30</v>
       </c>
       <c r="N26" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="O26" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
@@ -2576,39 +2552,39 @@
         <v>0</v>
       </c>
       <c r="R26" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C27" t="s">
         <v>138</v>
       </c>
-      <c r="B27" t="s">
+      <c r="D27" t="s">
         <v>139</v>
       </c>
-      <c r="C27" t="s">
+      <c r="E27" t="s">
         <v>140</v>
       </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
         <v>141</v>
       </c>
-      <c r="E27" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" t="s">
-        <v>143</v>
-      </c>
       <c r="G27" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H27" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I27" t="s">
         <v>42</v>
       </c>
       <c r="J27" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K27" t="s">
         <v>109</v>
@@ -2620,10 +2596,10 @@
         <v>30</v>
       </c>
       <c r="N27" t="s">
-        <v>147</v>
+        <v>46</v>
       </c>
       <c r="O27" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2632,33 +2608,33 @@
         <v>0</v>
       </c>
       <c r="R27" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C28" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" t="s">
+        <v>149</v>
+      </c>
+      <c r="F28" t="s">
+        <v>150</v>
+      </c>
+      <c r="G28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H28" t="s">
         <v>152</v>
-      </c>
-      <c r="D28" t="s">
-        <v>153</v>
-      </c>
-      <c r="E28" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" t="s">
-        <v>157</v>
       </c>
       <c r="I28" t="s">
         <v>26</v>
@@ -2676,10 +2652,10 @@
         <v>30</v>
       </c>
       <c r="N28" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="O28" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="P28" t="n">
         <v>1</v>
@@ -2688,33 +2664,33 @@
         <v>0</v>
       </c>
       <c r="R28" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D29" t="s">
+        <v>148</v>
+      </c>
+      <c r="E29" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" t="s">
+        <v>150</v>
+      </c>
+      <c r="G29" t="s">
         <v>153</v>
       </c>
-      <c r="E29" t="s">
+      <c r="H29" t="s">
         <v>154</v>
-      </c>
-      <c r="F29" t="s">
-        <v>155</v>
-      </c>
-      <c r="G29" t="s">
-        <v>159</v>
-      </c>
-      <c r="H29" t="s">
-        <v>160</v>
       </c>
       <c r="I29" t="s">
         <v>26</v>
@@ -2732,10 +2708,10 @@
         <v>30</v>
       </c>
       <c r="N29" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="O29" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="P29" t="n">
         <v>1</v>
@@ -2744,33 +2720,33 @@
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D30" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E30" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F30" t="s">
+        <v>150</v>
+      </c>
+      <c r="G30" t="s">
         <v>155</v>
       </c>
-      <c r="G30" t="s">
-        <v>161</v>
-      </c>
       <c r="H30" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I30" t="s">
         <v>26</v>
@@ -2788,10 +2764,10 @@
         <v>30</v>
       </c>
       <c r="N30" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="O30" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="P30" t="n">
         <v>1</v>
@@ -2800,33 +2776,33 @@
         <v>0</v>
       </c>
       <c r="R30" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D31" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E31" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F31" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="H31" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I31" t="s">
         <v>26</v>
@@ -2844,10 +2820,10 @@
         <v>30</v>
       </c>
       <c r="N31" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="O31" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
@@ -2856,39 +2832,39 @@
         <v>0</v>
       </c>
       <c r="R31" t="s">
-        <v>158</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B32" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D32" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G32" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="H32" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -2900,10 +2876,10 @@
         <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="O32" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -2912,33 +2888,33 @@
         <v>0</v>
       </c>
       <c r="R32" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" t="s">
         <v>167</v>
       </c>
-      <c r="B33" t="s">
+      <c r="D33" t="s">
         <v>168</v>
       </c>
-      <c r="C33" t="s">
-        <v>173</v>
-      </c>
-      <c r="D33" t="s">
-        <v>174</v>
-      </c>
       <c r="E33" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G33" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="H33" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
@@ -2956,10 +2932,10 @@
         <v>30</v>
       </c>
       <c r="N33" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="O33" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -2973,28 +2949,28 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="D34" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="E34" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F34" t="s">
         <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="H34" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
@@ -3024,33 +3000,33 @@
         <v>0</v>
       </c>
       <c r="R34" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B35" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="D35" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="E35" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F35" t="s">
         <v>65</v>
       </c>
       <c r="G35" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="H35" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
@@ -3080,54 +3056,54 @@
         <v>0</v>
       </c>
       <c r="R35" t="s">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C36" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="D36" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="F36" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="G36" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="H36" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M36" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s">
-        <v>178</v>
+        <v>91</v>
       </c>
       <c r="O36" t="s">
-        <v>179</v>
+        <v>92</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
@@ -3141,28 +3117,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D37" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E37" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G37" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="H37" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
@@ -3197,28 +3173,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F38" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="G38" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H38" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3253,28 +3229,28 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" t="s">
+        <v>192</v>
+      </c>
+      <c r="G39" t="s">
         <v>197</v>
       </c>
-      <c r="D39" t="s">
+      <c r="H39" t="s">
         <v>198</v>
-      </c>
-      <c r="E39" t="s">
-        <v>199</v>
-      </c>
-      <c r="F39" t="s">
-        <v>200</v>
-      </c>
-      <c r="G39" t="s">
-        <v>205</v>
-      </c>
-      <c r="H39" t="s">
-        <v>206</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -3309,28 +3285,28 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C40" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D40" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E40" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F40" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="G40" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="H40" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3348,10 +3324,10 @@
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="O40" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3360,33 +3336,33 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>33</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C41" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D41" t="s">
+        <v>202</v>
+      </c>
+      <c r="E41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="s">
+        <v>204</v>
+      </c>
+      <c r="G41" t="s">
         <v>210</v>
       </c>
-      <c r="E41" t="s">
+      <c r="H41" t="s">
         <v>211</v>
-      </c>
-      <c r="F41" t="s">
-        <v>212</v>
-      </c>
-      <c r="G41" t="s">
-        <v>215</v>
-      </c>
-      <c r="H41" t="s">
-        <v>216</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3404,10 +3380,10 @@
         <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="O41" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3416,33 +3392,33 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>33</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C42" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="D42" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="E42" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F42" t="s">
+        <v>204</v>
+      </c>
+      <c r="G42" t="s">
         <v>212</v>
       </c>
-      <c r="G42" t="s">
-        <v>217</v>
-      </c>
       <c r="H42" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
@@ -3460,10 +3436,10 @@
         <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="O42" t="s">
-        <v>148</v>
+        <v>208</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3472,33 +3448,33 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>33</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C43" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D43" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="E43" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="H43" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -3533,28 +3509,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B44" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C44" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D44" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="E44" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F44" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G44" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3572,10 +3548,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>226</v>
+        <v>55</v>
       </c>
       <c r="O44" t="s">
-        <v>227</v>
+        <v>56</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3584,33 +3560,33 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>228</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="C45" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="D45" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="E45" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="F45" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G45" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="H45" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3628,10 +3604,10 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>226</v>
+        <v>91</v>
       </c>
       <c r="O45" t="s">
-        <v>227</v>
+        <v>92</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
@@ -3640,42 +3616,42 @@
         <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>228</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B46" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C46" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="D46" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E46" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="F46" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G46" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="H46" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I46" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J46" t="s">
         <v>27</v>
       </c>
       <c r="K46" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3684,10 +3660,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O46" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3696,42 +3672,42 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B47" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C47" t="s">
+        <v>226</v>
+      </c>
+      <c r="D47" t="s">
+        <v>227</v>
+      </c>
+      <c r="E47" t="s">
+        <v>228</v>
+      </c>
+      <c r="F47" t="s">
+        <v>229</v>
+      </c>
+      <c r="G47" t="s">
         <v>234</v>
       </c>
-      <c r="D47" t="s">
+      <c r="H47" t="s">
         <v>235</v>
       </c>
-      <c r="E47" t="s">
-        <v>236</v>
-      </c>
-      <c r="F47" t="s">
-        <v>237</v>
-      </c>
-      <c r="G47" t="s">
-        <v>242</v>
-      </c>
-      <c r="H47" t="s">
-        <v>243</v>
-      </c>
       <c r="I47" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J47" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K47" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3740,10 +3716,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O47" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3752,42 +3728,42 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D48" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E48" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F48" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G48" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="H48" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="I48" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K48" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3796,10 +3772,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O48" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3808,42 +3784,42 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C49" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D49" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E49" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F49" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G49" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="H49" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="I49" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J49" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3852,10 +3828,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O49" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3864,42 +3840,42 @@
         <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B50" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C50" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" t="s">
+        <v>237</v>
+      </c>
+      <c r="E50" t="s">
+        <v>238</v>
+      </c>
+      <c r="F50" t="s">
+        <v>229</v>
+      </c>
+      <c r="G50" t="s">
+        <v>243</v>
+      </c>
+      <c r="H50" t="s">
         <v>244</v>
       </c>
-      <c r="D50" t="s">
-        <v>245</v>
-      </c>
-      <c r="E50" t="s">
-        <v>246</v>
-      </c>
-      <c r="F50" t="s">
-        <v>237</v>
-      </c>
-      <c r="G50" t="s">
-        <v>251</v>
-      </c>
-      <c r="H50" t="s">
-        <v>252</v>
-      </c>
       <c r="I50" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J50" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K50" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3908,10 +3884,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O50" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3920,42 +3896,42 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B51" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C51" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D51" t="s">
+        <v>237</v>
+      </c>
+      <c r="E51" t="s">
+        <v>238</v>
+      </c>
+      <c r="F51" t="s">
+        <v>229</v>
+      </c>
+      <c r="G51" t="s">
         <v>245</v>
       </c>
-      <c r="E51" t="s">
+      <c r="H51" t="s">
         <v>246</v>
       </c>
-      <c r="F51" t="s">
-        <v>237</v>
-      </c>
-      <c r="G51" t="s">
-        <v>253</v>
-      </c>
-      <c r="H51" t="s">
-        <v>254</v>
-      </c>
       <c r="I51" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J51" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K51" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3964,10 +3940,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O51" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3976,42 +3952,42 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B52" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D52" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E52" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F52" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G52" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="H52" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="I52" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J52" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4020,10 +3996,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O52" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4032,42 +4008,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C53" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D53" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E53" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F53" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G53" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="H53" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="I53" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4076,10 +4052,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O53" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4088,42 +4064,42 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="B54" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="C54" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="D54" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="E54" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="F54" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G54" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="H54" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="I54" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="J54" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K54" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4132,10 +4108,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="O54" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4144,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -597,6 +597,12 @@
   </si>
   <si>
     <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M9</t>
   </si>
   <si>
     <t xml:space="preserve">Violent crimes</t>
@@ -3156,10 +3162,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="O37" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3168,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="R37" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38">
@@ -3191,10 +3197,10 @@
         <v>192</v>
       </c>
       <c r="G38" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H38" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3212,10 +3218,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="O38" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3224,7 +3230,7 @@
         <v>1</v>
       </c>
       <c r="R38" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -3247,10 +3253,10 @@
         <v>192</v>
       </c>
       <c r="G39" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H39" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
@@ -3268,10 +3274,10 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="O39" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3280,33 +3286,33 @@
         <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E40" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G40" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H40" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3324,10 +3330,10 @@
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O40" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3336,33 +3342,33 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D41" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E41" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G41" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H41" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3380,10 +3386,10 @@
         <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O41" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3392,33 +3398,33 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D42" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E42" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F42" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G42" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H42" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I42" t="s">
         <v>26</v>
@@ -3436,10 +3442,10 @@
         <v>30</v>
       </c>
       <c r="N42" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="O42" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3448,33 +3454,33 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D43" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F43" t="s">
         <v>41</v>
       </c>
       <c r="G43" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H43" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I43" t="s">
         <v>42</v>
@@ -3509,28 +3515,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E44" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44" t="s">
+        <v>222</v>
+      </c>
+      <c r="G44" t="s">
         <v>219</v>
       </c>
-      <c r="F44" t="s">
+      <c r="H44" t="s">
         <v>220</v>
-      </c>
-      <c r="G44" t="s">
-        <v>217</v>
-      </c>
-      <c r="H44" t="s">
-        <v>218</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3565,28 +3571,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" t="s">
+        <v>225</v>
+      </c>
+      <c r="F45" t="s">
         <v>222</v>
       </c>
-      <c r="E45" t="s">
+      <c r="G45" t="s">
         <v>223</v>
       </c>
-      <c r="F45" t="s">
-        <v>220</v>
-      </c>
-      <c r="G45" t="s">
-        <v>221</v>
-      </c>
       <c r="H45" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="I45" t="s">
         <v>26</v>
@@ -3621,37 +3627,37 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D46" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E46" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
+        <v>231</v>
+      </c>
+      <c r="G46" t="s">
+        <v>230</v>
+      </c>
+      <c r="H46" t="s">
         <v>229</v>
       </c>
-      <c r="G46" t="s">
-        <v>228</v>
-      </c>
-      <c r="H46" t="s">
-        <v>227</v>
-      </c>
       <c r="I46" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J46" t="s">
         <v>27</v>
       </c>
       <c r="K46" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3660,10 +3666,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O46" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3672,42 +3678,42 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B47" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D47" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E47" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F47" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G47" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="H47" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I47" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J47" t="s">
         <v>144</v>
       </c>
       <c r="K47" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3716,10 +3722,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O47" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3728,42 +3734,42 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B48" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C48" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D48" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E48" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F48" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G48" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H48" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="I48" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J48" t="s">
         <v>144</v>
       </c>
       <c r="K48" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3772,10 +3778,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O48" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3784,42 +3790,42 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C49" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D49" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F49" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H49" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="I49" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J49" t="s">
         <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3828,10 +3834,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O49" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3840,42 +3846,42 @@
         <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E50" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F50" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G50" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="I50" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J50" t="s">
         <v>144</v>
       </c>
       <c r="K50" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3884,10 +3890,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O50" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3896,42 +3902,42 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B51" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C51" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E51" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F51" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H51" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I51" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J51" t="s">
         <v>144</v>
       </c>
       <c r="K51" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3940,10 +3946,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O51" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3952,42 +3958,42 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C52" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E52" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F52" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H52" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I52" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J52" t="s">
         <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -3996,10 +4002,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O52" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4008,42 +4014,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B53" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D53" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E53" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F53" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G53" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I53" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J53" t="s">
         <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4052,10 +4058,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O53" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4064,42 +4070,42 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C54" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E54" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F54" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G54" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="I54" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J54" t="s">
         <v>144</v>
       </c>
       <c r="K54" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L54" t="s">
         <v>29</v>
@@ -4108,10 +4114,10 @@
         <v>30</v>
       </c>
       <c r="N54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="O54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P54" t="n">
         <v>1</v>
@@ -4120,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="R54" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -503,18 +503,6 @@
     <t xml:space="preserve">destination-travel</t>
   </si>
   <si>
-    <t xml:space="preserve">Hotel revenue per available room</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hotel-revpar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied </t>
-  </si>
-  <si>
-    <t xml:space="preserve">$0.[00]</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total air passengers served</t>
   </si>
   <si>
@@ -597,12 +585,6 @@
   </si>
   <si>
     <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M9</t>
   </si>
   <si>
     <t xml:space="preserve">Violent crimes</t>
@@ -2858,19 +2840,19 @@
         <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="G32" t="s">
         <v>163</v>
       </c>
       <c r="H32" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="I32" t="s">
         <v>26</v>
       </c>
       <c r="J32" t="s">
-        <v>166</v>
+        <v>27</v>
       </c>
       <c r="K32" t="s">
         <v>28</v>
@@ -2882,10 +2864,10 @@
         <v>30</v>
       </c>
       <c r="N32" t="s">
-        <v>31</v>
+        <v>91</v>
       </c>
       <c r="O32" t="s">
-        <v>32</v>
+        <v>92</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -2905,46 +2887,46 @@
         <v>162</v>
       </c>
       <c r="C33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="G33" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I33" t="s">
         <v>26</v>
       </c>
       <c r="J33" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="K33" t="s">
         <v>28</v>
       </c>
       <c r="L33" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M33" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="N33" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="O33" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -2961,28 +2943,28 @@
         <v>162</v>
       </c>
       <c r="C34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E34" t="s">
         <v>173</v>
-      </c>
-      <c r="E34" t="s">
-        <v>174</v>
       </c>
       <c r="F34" t="s">
         <v>65</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H34" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I34" t="s">
         <v>26</v>
       </c>
       <c r="J34" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K34" t="s">
         <v>28</v>
@@ -3011,10 +2993,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="C35" t="s">
         <v>177</v>
@@ -3023,40 +3005,40 @@
         <v>178</v>
       </c>
       <c r="E35" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F35" t="s">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H35" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="M35" t="s">
-        <v>69</v>
+        <v>184</v>
       </c>
       <c r="N35" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="O35" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -3067,55 +3049,55 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C36" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D36" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E36" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F36" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="G36" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="H36" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>187</v>
+        <v>29</v>
       </c>
       <c r="M36" t="s">
-        <v>188</v>
+        <v>30</v>
       </c>
       <c r="N36" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="O36" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="s">
         <v>33</v>
@@ -3123,28 +3105,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B37" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D37" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E37" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" t="s">
+        <v>188</v>
+      </c>
+      <c r="G37" t="s">
         <v>191</v>
       </c>
-      <c r="F37" t="s">
+      <c r="H37" t="s">
         <v>192</v>
-      </c>
-      <c r="G37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H37" t="s">
-        <v>194</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
@@ -3162,10 +3144,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="O37" t="s">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3179,28 +3161,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E38" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F38" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="G38" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="H38" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3218,10 +3200,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="O38" t="s">
-        <v>196</v>
+        <v>56</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3235,37 +3217,37 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B39" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="C39" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="D39" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E39" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F39" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="H39" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="K39" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="L39" t="s">
         <v>29</v>
@@ -3274,10 +3256,10 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="O39" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3286,33 +3268,33 @@
         <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>33</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C40" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D40" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E40" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F40" t="s">
+        <v>200</v>
+      </c>
+      <c r="G40" t="s">
         <v>206</v>
       </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>207</v>
-      </c>
-      <c r="H40" t="s">
-        <v>208</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3330,10 +3312,10 @@
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O40" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3342,33 +3324,33 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C41" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="D41" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E41" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F41" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="G41" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="H41" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3386,10 +3368,10 @@
         <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="O41" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3398,54 +3380,54 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B42" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C42" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D42" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="E42" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="F42" t="s">
-        <v>206</v>
+        <v>41</v>
       </c>
       <c r="G42" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="H42" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="I42" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J42" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="K42" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L42" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M42" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N42" t="s">
-        <v>209</v>
+        <v>46</v>
       </c>
       <c r="O42" t="s">
-        <v>210</v>
+        <v>47</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3454,54 +3436,54 @@
         <v>1</v>
       </c>
       <c r="R42" t="s">
-        <v>211</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B43" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C43" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" t="s">
+        <v>214</v>
+      </c>
+      <c r="E43" t="s">
+        <v>215</v>
+      </c>
+      <c r="F43" t="s">
         <v>216</v>
       </c>
-      <c r="D43" t="s">
-        <v>217</v>
-      </c>
-      <c r="E43" t="s">
-        <v>218</v>
-      </c>
-      <c r="F43" t="s">
-        <v>41</v>
-      </c>
       <c r="G43" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H43" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="J43" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="M43" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="N43" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O43" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3515,28 +3497,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C44" t="s">
+        <v>217</v>
+      </c>
+      <c r="D44" t="s">
+        <v>218</v>
+      </c>
+      <c r="E44" t="s">
         <v>219</v>
       </c>
-      <c r="D44" t="s">
-        <v>220</v>
-      </c>
-      <c r="E44" t="s">
-        <v>221</v>
-      </c>
       <c r="F44" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G44" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="H44" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3554,10 +3536,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O44" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3571,37 +3553,37 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="C45" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" t="s">
         <v>223</v>
       </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>224</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>225</v>
       </c>
-      <c r="F45" t="s">
-        <v>222</v>
-      </c>
       <c r="G45" t="s">
+        <v>224</v>
+      </c>
+      <c r="H45" t="s">
         <v>223</v>
       </c>
-      <c r="H45" t="s">
-        <v>224</v>
-      </c>
       <c r="I45" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="J45" t="s">
         <v>27</v>
       </c>
       <c r="K45" t="s">
-        <v>28</v>
+        <v>227</v>
       </c>
       <c r="L45" t="s">
         <v>29</v>
@@ -3610,54 +3592,54 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>91</v>
+        <v>228</v>
       </c>
       <c r="O45" t="s">
-        <v>92</v>
+        <v>228</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="s">
-        <v>33</v>
+        <v>229</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C46" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="D46" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E46" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F46" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G46" t="s">
         <v>230</v>
       </c>
       <c r="H46" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I46" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="J46" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="K46" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3666,10 +3648,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O46" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3678,42 +3660,42 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>220</v>
+      </c>
+      <c r="B47" t="s">
+        <v>221</v>
+      </c>
+      <c r="C47" t="s">
+        <v>232</v>
+      </c>
+      <c r="D47" t="s">
+        <v>233</v>
+      </c>
+      <c r="E47" t="s">
+        <v>234</v>
+      </c>
+      <c r="F47" t="s">
+        <v>225</v>
+      </c>
+      <c r="G47" t="s">
+        <v>235</v>
+      </c>
+      <c r="H47" t="s">
+        <v>236</v>
+      </c>
+      <c r="I47" t="s">
         <v>226</v>
-      </c>
-      <c r="B47" t="s">
-        <v>227</v>
-      </c>
-      <c r="C47" t="s">
-        <v>228</v>
-      </c>
-      <c r="D47" t="s">
-        <v>229</v>
-      </c>
-      <c r="E47" t="s">
-        <v>230</v>
-      </c>
-      <c r="F47" t="s">
-        <v>231</v>
-      </c>
-      <c r="G47" t="s">
-        <v>236</v>
-      </c>
-      <c r="H47" t="s">
-        <v>237</v>
-      </c>
-      <c r="I47" t="s">
-        <v>232</v>
       </c>
       <c r="J47" t="s">
         <v>144</v>
       </c>
       <c r="K47" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3722,10 +3704,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O47" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3734,42 +3716,42 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>220</v>
+      </c>
+      <c r="B48" t="s">
+        <v>221</v>
+      </c>
+      <c r="C48" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" t="s">
+        <v>233</v>
+      </c>
+      <c r="E48" t="s">
+        <v>234</v>
+      </c>
+      <c r="F48" t="s">
+        <v>225</v>
+      </c>
+      <c r="G48" t="s">
+        <v>237</v>
+      </c>
+      <c r="H48" t="s">
+        <v>238</v>
+      </c>
+      <c r="I48" t="s">
         <v>226</v>
-      </c>
-      <c r="B48" t="s">
-        <v>227</v>
-      </c>
-      <c r="C48" t="s">
-        <v>238</v>
-      </c>
-      <c r="D48" t="s">
-        <v>239</v>
-      </c>
-      <c r="E48" t="s">
-        <v>240</v>
-      </c>
-      <c r="F48" t="s">
-        <v>231</v>
-      </c>
-      <c r="G48" t="s">
-        <v>241</v>
-      </c>
-      <c r="H48" t="s">
-        <v>242</v>
-      </c>
-      <c r="I48" t="s">
-        <v>232</v>
       </c>
       <c r="J48" t="s">
         <v>144</v>
       </c>
       <c r="K48" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3778,10 +3760,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O48" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3790,42 +3772,42 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>220</v>
+      </c>
+      <c r="B49" t="s">
+        <v>221</v>
+      </c>
+      <c r="C49" t="s">
+        <v>232</v>
+      </c>
+      <c r="D49" t="s">
+        <v>233</v>
+      </c>
+      <c r="E49" t="s">
+        <v>234</v>
+      </c>
+      <c r="F49" t="s">
+        <v>225</v>
+      </c>
+      <c r="G49" t="s">
+        <v>239</v>
+      </c>
+      <c r="H49" t="s">
+        <v>240</v>
+      </c>
+      <c r="I49" t="s">
         <v>226</v>
-      </c>
-      <c r="B49" t="s">
-        <v>227</v>
-      </c>
-      <c r="C49" t="s">
-        <v>238</v>
-      </c>
-      <c r="D49" t="s">
-        <v>239</v>
-      </c>
-      <c r="E49" t="s">
-        <v>240</v>
-      </c>
-      <c r="F49" t="s">
-        <v>231</v>
-      </c>
-      <c r="G49" t="s">
-        <v>243</v>
-      </c>
-      <c r="H49" t="s">
-        <v>244</v>
-      </c>
-      <c r="I49" t="s">
-        <v>232</v>
       </c>
       <c r="J49" t="s">
         <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3834,10 +3816,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O49" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3846,42 +3828,42 @@
         <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>220</v>
+      </c>
+      <c r="B50" t="s">
+        <v>221</v>
+      </c>
+      <c r="C50" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" t="s">
+        <v>233</v>
+      </c>
+      <c r="E50" t="s">
+        <v>234</v>
+      </c>
+      <c r="F50" t="s">
+        <v>225</v>
+      </c>
+      <c r="G50" t="s">
+        <v>241</v>
+      </c>
+      <c r="H50" t="s">
+        <v>242</v>
+      </c>
+      <c r="I50" t="s">
         <v>226</v>
-      </c>
-      <c r="B50" t="s">
-        <v>227</v>
-      </c>
-      <c r="C50" t="s">
-        <v>238</v>
-      </c>
-      <c r="D50" t="s">
-        <v>239</v>
-      </c>
-      <c r="E50" t="s">
-        <v>240</v>
-      </c>
-      <c r="F50" t="s">
-        <v>231</v>
-      </c>
-      <c r="G50" t="s">
-        <v>245</v>
-      </c>
-      <c r="H50" t="s">
-        <v>246</v>
-      </c>
-      <c r="I50" t="s">
-        <v>232</v>
       </c>
       <c r="J50" t="s">
         <v>144</v>
       </c>
       <c r="K50" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3890,10 +3872,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O50" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3902,42 +3884,42 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" t="s">
+        <v>221</v>
+      </c>
+      <c r="C51" t="s">
+        <v>232</v>
+      </c>
+      <c r="D51" t="s">
+        <v>233</v>
+      </c>
+      <c r="E51" t="s">
+        <v>234</v>
+      </c>
+      <c r="F51" t="s">
+        <v>225</v>
+      </c>
+      <c r="G51" t="s">
+        <v>243</v>
+      </c>
+      <c r="H51" t="s">
+        <v>244</v>
+      </c>
+      <c r="I51" t="s">
         <v>226</v>
-      </c>
-      <c r="B51" t="s">
-        <v>227</v>
-      </c>
-      <c r="C51" t="s">
-        <v>238</v>
-      </c>
-      <c r="D51" t="s">
-        <v>239</v>
-      </c>
-      <c r="E51" t="s">
-        <v>240</v>
-      </c>
-      <c r="F51" t="s">
-        <v>231</v>
-      </c>
-      <c r="G51" t="s">
-        <v>247</v>
-      </c>
-      <c r="H51" t="s">
-        <v>248</v>
-      </c>
-      <c r="I51" t="s">
-        <v>232</v>
       </c>
       <c r="J51" t="s">
         <v>144</v>
       </c>
       <c r="K51" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3946,10 +3928,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O51" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3958,42 +3940,42 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>220</v>
+      </c>
+      <c r="B52" t="s">
+        <v>221</v>
+      </c>
+      <c r="C52" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" t="s">
+        <v>233</v>
+      </c>
+      <c r="E52" t="s">
+        <v>234</v>
+      </c>
+      <c r="F52" t="s">
+        <v>225</v>
+      </c>
+      <c r="G52" t="s">
+        <v>245</v>
+      </c>
+      <c r="H52" t="s">
+        <v>246</v>
+      </c>
+      <c r="I52" t="s">
         <v>226</v>
-      </c>
-      <c r="B52" t="s">
-        <v>227</v>
-      </c>
-      <c r="C52" t="s">
-        <v>238</v>
-      </c>
-      <c r="D52" t="s">
-        <v>239</v>
-      </c>
-      <c r="E52" t="s">
-        <v>240</v>
-      </c>
-      <c r="F52" t="s">
-        <v>231</v>
-      </c>
-      <c r="G52" t="s">
-        <v>249</v>
-      </c>
-      <c r="H52" t="s">
-        <v>250</v>
-      </c>
-      <c r="I52" t="s">
-        <v>232</v>
       </c>
       <c r="J52" t="s">
         <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -4002,10 +3984,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O52" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -4014,42 +3996,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>220</v>
+      </c>
+      <c r="B53" t="s">
+        <v>221</v>
+      </c>
+      <c r="C53" t="s">
+        <v>232</v>
+      </c>
+      <c r="D53" t="s">
+        <v>233</v>
+      </c>
+      <c r="E53" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" t="s">
+        <v>225</v>
+      </c>
+      <c r="G53" t="s">
+        <v>247</v>
+      </c>
+      <c r="H53" t="s">
+        <v>248</v>
+      </c>
+      <c r="I53" t="s">
         <v>226</v>
-      </c>
-      <c r="B53" t="s">
-        <v>227</v>
-      </c>
-      <c r="C53" t="s">
-        <v>238</v>
-      </c>
-      <c r="D53" t="s">
-        <v>239</v>
-      </c>
-      <c r="E53" t="s">
-        <v>240</v>
-      </c>
-      <c r="F53" t="s">
-        <v>231</v>
-      </c>
-      <c r="G53" t="s">
-        <v>251</v>
-      </c>
-      <c r="H53" t="s">
-        <v>252</v>
-      </c>
-      <c r="I53" t="s">
-        <v>232</v>
       </c>
       <c r="J53" t="s">
         <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4058,10 +4040,10 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="O53" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="P53" t="n">
         <v>1</v>
@@ -4070,63 +4052,7 @@
         <v>0</v>
       </c>
       <c r="R53" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>226</v>
-      </c>
-      <c r="B54" t="s">
-        <v>227</v>
-      </c>
-      <c r="C54" t="s">
-        <v>238</v>
-      </c>
-      <c r="D54" t="s">
-        <v>239</v>
-      </c>
-      <c r="E54" t="s">
-        <v>240</v>
-      </c>
-      <c r="F54" t="s">
-        <v>231</v>
-      </c>
-      <c r="G54" t="s">
-        <v>253</v>
-      </c>
-      <c r="H54" t="s">
-        <v>254</v>
-      </c>
-      <c r="I54" t="s">
-        <v>232</v>
-      </c>
-      <c r="J54" t="s">
-        <v>144</v>
-      </c>
-      <c r="K54" t="s">
-        <v>233</v>
-      </c>
-      <c r="L54" t="s">
-        <v>29</v>
-      </c>
-      <c r="M54" t="s">
-        <v>30</v>
-      </c>
-      <c r="N54" t="s">
-        <v>234</v>
-      </c>
-      <c r="O54" t="s">
-        <v>234</v>
-      </c>
-      <c r="P54" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>

--- a/input-data/metadata.xlsx
+++ b/input-data/metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="256">
   <si>
     <t xml:space="preserve">topic.name</t>
   </si>
@@ -113,556 +113,577 @@
     <t xml:space="preserve">2026M4</t>
   </si>
   <si>
+    <t xml:space="preserve">DMV-2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal government jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jobs-federal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">business-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administrative Office of the United States Courts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 12-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-12-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026Q1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USASpending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$123k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025M12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-grants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations, contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">federal-obligations-contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataFy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resident spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">resident-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer prices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cpi-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">innovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">research-hd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Academic research funding obligated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States Patent and Trademark Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utility patent applications filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patents-filed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crunchbase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital volume ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Venture capital deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">venture-capital-deals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Market &amp; Workforce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">labor-market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[00]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pct_diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, white workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, black workers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, workers of color</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-poc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, men</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unemployment rate, female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unempr-sa-female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Job postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-fte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightcast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-private</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public sector job postings, full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-public</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internship postings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique-postings-internships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass layoff notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">warn-notices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WarnTracker.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Estate &amp; Housing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial occupancy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CoStar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied office space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.[0]%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied retail space (% SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">commercial-occupancy-retail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">home-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residential home sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median sale price per square foot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mspsq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median days on market</t>
+  </si>
+  <si>
+    <t xml:space="preserve">median-dom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of pending sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pending-sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observed rental index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rent-index</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zillow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination &amp; Travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">destination-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total air passengers served</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-travel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air-passengers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visitor spending, total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">visitor-spending-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overnight visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">overnight-visitors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue per available room</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hotel-revpar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hotel revenue generated by available rooms/units over a given period, whether or not they are occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$0.[00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Municipal Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">municipal-services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transit ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-ridership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U.S. Federal Transit Administration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trips per vehicle revenue mile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transit-vrm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolling 3-month total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rolling-3-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crime rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Bureau of Investigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all major crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Violent crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-violent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property crimes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">crime-rate-property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Household Wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">household-wellbeing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Credit-constrained population rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Near-prime consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-nearprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025Q4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DMV-2026-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Severely credit-constrained consumers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-subprime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total, all credit-constrained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit-constrained-total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personal bankruptcy rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">personal-bankruptcy-rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">medicaid-enrollment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State agency reporting</t>
+  </si>
+  <si>
     <t xml:space="preserve">DMV-2026-06-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal government jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jobs-federal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">business-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Administrative Office of the United States Courts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 12-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-12-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026Q1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legally-binding funds committed to recipients through federally-awarded grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">USASpending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">$123k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025M12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-grants</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations, contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">federal-obligations-contracts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV residents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DataFy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resident spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">resident-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-mean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer prices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cpi-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexed change in the price of a fixed basket of goods for urban consumers, indexed to 1984 levels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Labor Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">innovation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">research-hd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal obligations to institutions of higher education made for research-based grants, contracts, loans, and cooperative agreements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Academic research funding obligated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filed and granted applications for patents covering new inventions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States Patent and Trademark Office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utility patent applications filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">patents-filed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026M2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital investment in startup firms through seed rounds, individual “angel” contributions, or convertible notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crunchbase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital volume ($)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-volume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Venture capital deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">venture-capital-deals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor Market &amp; Workforce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">labor-market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percentage of labor force not currently employed  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[00]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pct_diff</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, white workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-white</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, black workers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-black</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, workers of color</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-poc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, men</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unemployment rate, female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unempr-sa-female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Job postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-fte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of online job advertisements posted by employers, deduplicated for cross-posted listings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightcast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Private sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-private</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public sector job postings, full-time</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-public</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Internship postings</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique-postings-internships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mass layoff notifications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">warn-notices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notifications for closures or layoffs by qualified employers under the Worker Adjustment and Retraining Notification Act</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WarnTracker.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real Estate &amp; Housing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">real-estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Commercial occupancy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of total square footage zoned as office or retail space that is currently occupied</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CoStar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied office space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.[0]%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Occupied retail space (% SF)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">commercial-occupancy-retail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">home-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residential home sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Realtor.com Economic Research and Redfin Data Center</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median sale price per square foot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mspsq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median days on market</t>
-  </si>
-  <si>
-    <t xml:space="preserve">median-dom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of pending sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pending-sales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observed rental index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rent-index</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow inflation-adjusted observed rental index (ZORI), all homes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zillow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Destination &amp; Travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">destination-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total air passengers served</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-travel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total passengers enplaned and deplaned on scheduled services at airports in a given market, excluding connecting flights</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Bureau of Transportation Statistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air-passengers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spending at brick-and-mortar retailers by DMV visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitor spending, total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">visitor-spending-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Overnight visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">overnight-visitors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Municipal Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">municipal-services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transit ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-ridership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of passengers traveling on public transportation vehicles, including buses, trains, and ferries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">U.S. Federal Transit Administration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trips per vehicle revenue mile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">transit-vrm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rolling 3-month total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rolling-3-sum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crime rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Number of major criminal incidents reported per 100,000 people, year to date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Bureau of Investigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all major crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Violent crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-violent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Property crimes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">crime-rate-property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Household Wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">household-wellbeing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Credit-constrained population rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Share of consumers with an Equifax risk score below 660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federal Reserve Bank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Near-prime consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-nearprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025Q4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DMV-2026-05-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Severely credit-constrained consumers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-subprime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total, all credit-constrained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">credit-constrained-total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personal bankruptcy rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">personal-bankruptcy-rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-business bankruptcy cases filed per 100,000 people</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicaid/CHIP enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">medicaid-enrollment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total number of individuals enrolled in state-offered Medicaid and Children’s Health Insurance Program (CHIP) services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">State agency reporting</t>
   </si>
   <si>
     <t xml:space="preserve">SNAP participation</t>
@@ -2993,49 +3014,49 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" t="s">
         <v>175</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" t="s">
         <v>176</v>
       </c>
-      <c r="C35" t="s">
+      <c r="E35" t="s">
         <v>177</v>
       </c>
-      <c r="D35" t="s">
-        <v>178</v>
-      </c>
-      <c r="E35" t="s">
-        <v>179</v>
-      </c>
       <c r="F35" t="s">
-        <v>180</v>
+        <v>141</v>
       </c>
       <c r="G35" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H35" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I35" t="s">
         <v>26</v>
       </c>
       <c r="J35" t="s">
-        <v>76</v>
+        <v>178</v>
       </c>
       <c r="K35" t="s">
         <v>28</v>
       </c>
       <c r="L35" t="s">
-        <v>183</v>
+        <v>29</v>
       </c>
       <c r="M35" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="N35" t="s">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="O35" t="s">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -3049,55 +3070,55 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D36" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" t="s">
+        <v>183</v>
+      </c>
+      <c r="F36" t="s">
+        <v>184</v>
+      </c>
+      <c r="G36" t="s">
         <v>185</v>
       </c>
-      <c r="D36" t="s">
+      <c r="H36" t="s">
         <v>186</v>
-      </c>
-      <c r="E36" t="s">
-        <v>187</v>
-      </c>
-      <c r="F36" t="s">
-        <v>188</v>
-      </c>
-      <c r="G36" t="s">
-        <v>189</v>
-      </c>
-      <c r="H36" t="s">
-        <v>190</v>
       </c>
       <c r="I36" t="s">
         <v>26</v>
       </c>
       <c r="J36" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="K36" t="s">
         <v>28</v>
       </c>
       <c r="L36" t="s">
-        <v>29</v>
+        <v>187</v>
       </c>
       <c r="M36" t="s">
-        <v>30</v>
+        <v>188</v>
       </c>
       <c r="N36" t="s">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O36" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="s">
         <v>33</v>
@@ -3105,28 +3126,28 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E37" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G37" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H37" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I37" t="s">
         <v>26</v>
@@ -3144,10 +3165,10 @@
         <v>30</v>
       </c>
       <c r="N37" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="O37" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="P37" t="n">
         <v>1</v>
@@ -3161,28 +3182,28 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C38" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F38" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="G38" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H38" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I38" t="s">
         <v>26</v>
@@ -3200,10 +3221,10 @@
         <v>30</v>
       </c>
       <c r="N38" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="O38" t="s">
-        <v>56</v>
+        <v>196</v>
       </c>
       <c r="P38" t="n">
         <v>1</v>
@@ -3217,37 +3238,37 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>195</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
       <c r="C39" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D39" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E39" t="s">
+        <v>191</v>
+      </c>
+      <c r="F39" t="s">
+        <v>192</v>
+      </c>
+      <c r="G39" t="s">
         <v>199</v>
       </c>
-      <c r="F39" t="s">
+      <c r="H39" t="s">
         <v>200</v>
-      </c>
-      <c r="G39" t="s">
-        <v>201</v>
-      </c>
-      <c r="H39" t="s">
-        <v>202</v>
       </c>
       <c r="I39" t="s">
         <v>26</v>
       </c>
       <c r="J39" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="K39" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="L39" t="s">
         <v>29</v>
@@ -3256,10 +3277,10 @@
         <v>30</v>
       </c>
       <c r="N39" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="O39" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
@@ -3268,33 +3289,33 @@
         <v>1</v>
       </c>
       <c r="R39" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D40" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E40" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F40" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G40" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H40" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I40" t="s">
         <v>26</v>
@@ -3312,10 +3333,10 @@
         <v>30</v>
       </c>
       <c r="N40" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="O40" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -3324,33 +3345,33 @@
         <v>1</v>
       </c>
       <c r="R40" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D41" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E41" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="G41" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="H41" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="I41" t="s">
         <v>26</v>
@@ -3368,10 +3389,10 @@
         <v>30</v>
       </c>
       <c r="N41" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="O41" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="P41" t="n">
         <v>1</v>
@@ -3380,110 +3401,110 @@
         <v>1</v>
       </c>
       <c r="R41" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C42" t="s">
+        <v>203</v>
+      </c>
+      <c r="D42" t="s">
+        <v>204</v>
+      </c>
+      <c r="E42" t="s">
+        <v>205</v>
+      </c>
+      <c r="F42" t="s">
+        <v>206</v>
+      </c>
+      <c r="G42" t="s">
+        <v>214</v>
+      </c>
+      <c r="H42" t="s">
+        <v>215</v>
+      </c>
+      <c r="I42" t="s">
+        <v>26</v>
+      </c>
+      <c r="J42" t="s">
+        <v>108</v>
+      </c>
+      <c r="K42" t="s">
+        <v>109</v>
+      </c>
+      <c r="L42" t="s">
+        <v>29</v>
+      </c>
+      <c r="M42" t="s">
+        <v>30</v>
+      </c>
+      <c r="N42" t="s">
+        <v>209</v>
+      </c>
+      <c r="O42" t="s">
         <v>210</v>
       </c>
-      <c r="D42" t="s">
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" t="s">
         <v>211</v>
-      </c>
-      <c r="E42" t="s">
-        <v>212</v>
-      </c>
-      <c r="F42" t="s">
-        <v>41</v>
-      </c>
-      <c r="G42" t="s">
-        <v>210</v>
-      </c>
-      <c r="H42" t="s">
-        <v>211</v>
-      </c>
-      <c r="I42" t="s">
-        <v>42</v>
-      </c>
-      <c r="J42" t="s">
-        <v>43</v>
-      </c>
-      <c r="K42" t="s">
-        <v>28</v>
-      </c>
-      <c r="L42" t="s">
-        <v>44</v>
-      </c>
-      <c r="M42" t="s">
-        <v>45</v>
-      </c>
-      <c r="N42" t="s">
-        <v>46</v>
-      </c>
-      <c r="O42" t="s">
-        <v>47</v>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1</v>
-      </c>
-      <c r="R42" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C43" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E43" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F43" t="s">
+        <v>41</v>
+      </c>
+      <c r="G43" t="s">
         <v>216</v>
       </c>
-      <c r="G43" t="s">
-        <v>213</v>
-      </c>
       <c r="H43" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="I43" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="J43" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="K43" t="s">
         <v>28</v>
       </c>
       <c r="L43" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="M43" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="N43" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O43" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="P43" t="n">
         <v>1</v>
@@ -3497,28 +3518,28 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C44" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E44" t="s">
+        <v>221</v>
+      </c>
+      <c r="F44" t="s">
+        <v>222</v>
+      </c>
+      <c r="G44" t="s">
         <v>219</v>
       </c>
-      <c r="F44" t="s">
-        <v>216</v>
-      </c>
-      <c r="G44" t="s">
-        <v>217</v>
-      </c>
       <c r="H44" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="I44" t="s">
         <v>26</v>
@@ -3536,10 +3557,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="O44" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="P44" t="n">
         <v>1</v>
@@ -3548,42 +3569,42 @@
         <v>1</v>
       </c>
       <c r="R44" t="s">
-        <v>33</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="B45" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="C45" t="s">
+        <v>224</v>
+      </c>
+      <c r="D45" t="s">
+        <v>225</v>
+      </c>
+      <c r="E45" t="s">
+        <v>226</v>
+      </c>
+      <c r="F45" t="s">
         <v>222</v>
-      </c>
-      <c r="D45" t="s">
-        <v>223</v>
-      </c>
-      <c r="E45" t="s">
-        <v>224</v>
-      </c>
-      <c r="F45" t="s">
-        <v>225</v>
       </c>
       <c r="G45" t="s">
         <v>224</v>
       </c>
       <c r="H45" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I45" t="s">
-        <v>226</v>
+        <v>26</v>
       </c>
       <c r="J45" t="s">
         <v>27</v>
       </c>
       <c r="K45" t="s">
-        <v>227</v>
+        <v>28</v>
       </c>
       <c r="L45" t="s">
         <v>29</v>
@@ -3592,54 +3613,54 @@
         <v>30</v>
       </c>
       <c r="N45" t="s">
-        <v>228</v>
+        <v>91</v>
       </c>
       <c r="O45" t="s">
-        <v>228</v>
+        <v>92</v>
       </c>
       <c r="P45" t="n">
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="s">
-        <v>229</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B46" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="F46" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G46" t="s">
+        <v>231</v>
+      </c>
+      <c r="H46" t="s">
         <v>230</v>
       </c>
-      <c r="H46" t="s">
-        <v>231</v>
-      </c>
       <c r="I46" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="J46" t="s">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="K46" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L46" t="s">
         <v>29</v>
@@ -3648,10 +3669,10 @@
         <v>30</v>
       </c>
       <c r="N46" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O46" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P46" t="n">
         <v>1</v>
@@ -3660,42 +3681,42 @@
         <v>0</v>
       </c>
       <c r="R46" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
+        <v>229</v>
+      </c>
+      <c r="D47" t="s">
+        <v>230</v>
+      </c>
+      <c r="E47" t="s">
+        <v>231</v>
+      </c>
+      <c r="F47" t="s">
         <v>232</v>
       </c>
-      <c r="D47" t="s">
+      <c r="G47" t="s">
+        <v>237</v>
+      </c>
+      <c r="H47" t="s">
+        <v>238</v>
+      </c>
+      <c r="I47" t="s">
         <v>233</v>
-      </c>
-      <c r="E47" t="s">
-        <v>234</v>
-      </c>
-      <c r="F47" t="s">
-        <v>225</v>
-      </c>
-      <c r="G47" t="s">
-        <v>235</v>
-      </c>
-      <c r="H47" t="s">
-        <v>236</v>
-      </c>
-      <c r="I47" t="s">
-        <v>226</v>
       </c>
       <c r="J47" t="s">
         <v>144</v>
       </c>
       <c r="K47" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L47" t="s">
         <v>29</v>
@@ -3704,10 +3725,10 @@
         <v>30</v>
       </c>
       <c r="N47" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O47" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P47" t="n">
         <v>1</v>
@@ -3716,42 +3737,42 @@
         <v>0</v>
       </c>
       <c r="R47" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C48" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" t="s">
+        <v>241</v>
+      </c>
+      <c r="F48" t="s">
         <v>232</v>
       </c>
-      <c r="D48" t="s">
+      <c r="G48" t="s">
+        <v>242</v>
+      </c>
+      <c r="H48" t="s">
+        <v>243</v>
+      </c>
+      <c r="I48" t="s">
         <v>233</v>
-      </c>
-      <c r="E48" t="s">
-        <v>234</v>
-      </c>
-      <c r="F48" t="s">
-        <v>225</v>
-      </c>
-      <c r="G48" t="s">
-        <v>237</v>
-      </c>
-      <c r="H48" t="s">
-        <v>238</v>
-      </c>
-      <c r="I48" t="s">
-        <v>226</v>
       </c>
       <c r="J48" t="s">
         <v>144</v>
       </c>
       <c r="K48" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L48" t="s">
         <v>29</v>
@@ -3760,10 +3781,10 @@
         <v>30</v>
       </c>
       <c r="N48" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O48" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P48" t="n">
         <v>1</v>
@@ -3772,42 +3793,42 @@
         <v>0</v>
       </c>
       <c r="R48" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" t="s">
+        <v>240</v>
+      </c>
+      <c r="E49" t="s">
+        <v>241</v>
+      </c>
+      <c r="F49" t="s">
         <v>232</v>
       </c>
-      <c r="D49" t="s">
+      <c r="G49" t="s">
+        <v>244</v>
+      </c>
+      <c r="H49" t="s">
+        <v>245</v>
+      </c>
+      <c r="I49" t="s">
         <v>233</v>
-      </c>
-      <c r="E49" t="s">
-        <v>234</v>
-      </c>
-      <c r="F49" t="s">
-        <v>225</v>
-      </c>
-      <c r="G49" t="s">
-        <v>239</v>
-      </c>
-      <c r="H49" t="s">
-        <v>240</v>
-      </c>
-      <c r="I49" t="s">
-        <v>226</v>
       </c>
       <c r="J49" t="s">
         <v>144</v>
       </c>
       <c r="K49" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L49" t="s">
         <v>29</v>
@@ -3816,10 +3837,10 @@
         <v>30</v>
       </c>
       <c r="N49" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O49" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -3828,42 +3849,42 @@
         <v>0</v>
       </c>
       <c r="R49" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B50" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" t="s">
+        <v>240</v>
+      </c>
+      <c r="E50" t="s">
+        <v>241</v>
+      </c>
+      <c r="F50" t="s">
         <v>232</v>
       </c>
-      <c r="D50" t="s">
+      <c r="G50" t="s">
+        <v>246</v>
+      </c>
+      <c r="H50" t="s">
+        <v>247</v>
+      </c>
+      <c r="I50" t="s">
         <v>233</v>
-      </c>
-      <c r="E50" t="s">
-        <v>234</v>
-      </c>
-      <c r="F50" t="s">
-        <v>225</v>
-      </c>
-      <c r="G50" t="s">
-        <v>241</v>
-      </c>
-      <c r="H50" t="s">
-        <v>242</v>
-      </c>
-      <c r="I50" t="s">
-        <v>226</v>
       </c>
       <c r="J50" t="s">
         <v>144</v>
       </c>
       <c r="K50" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L50" t="s">
         <v>29</v>
@@ -3872,10 +3893,10 @@
         <v>30</v>
       </c>
       <c r="N50" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O50" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P50" t="n">
         <v>1</v>
@@ -3884,42 +3905,42 @@
         <v>0</v>
       </c>
       <c r="R50" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B51" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" t="s">
+        <v>241</v>
+      </c>
+      <c r="F51" t="s">
         <v>232</v>
       </c>
-      <c r="D51" t="s">
+      <c r="G51" t="s">
+        <v>248</v>
+      </c>
+      <c r="H51" t="s">
+        <v>249</v>
+      </c>
+      <c r="I51" t="s">
         <v>233</v>
-      </c>
-      <c r="E51" t="s">
-        <v>234</v>
-      </c>
-      <c r="F51" t="s">
-        <v>225</v>
-      </c>
-      <c r="G51" t="s">
-        <v>243</v>
-      </c>
-      <c r="H51" t="s">
-        <v>244</v>
-      </c>
-      <c r="I51" t="s">
-        <v>226</v>
       </c>
       <c r="J51" t="s">
         <v>144</v>
       </c>
       <c r="K51" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L51" t="s">
         <v>29</v>
@@ -3928,10 +3949,10 @@
         <v>30</v>
       </c>
       <c r="N51" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O51" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P51" t="n">
         <v>1</v>
@@ -3940,42 +3961,42 @@
         <v>0</v>
       </c>
       <c r="R51" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B52" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C52" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" t="s">
+        <v>240</v>
+      </c>
+      <c r="E52" t="s">
+        <v>241</v>
+      </c>
+      <c r="F52" t="s">
         <v>232</v>
       </c>
-      <c r="D52" t="s">
+      <c r="G52" t="s">
+        <v>250</v>
+      </c>
+      <c r="H52" t="s">
+        <v>251</v>
+      </c>
+      <c r="I52" t="s">
         <v>233</v>
-      </c>
-      <c r="E52" t="s">
-        <v>234</v>
-      </c>
-      <c r="F52" t="s">
-        <v>225</v>
-      </c>
-      <c r="G52" t="s">
-        <v>245</v>
-      </c>
-      <c r="H52" t="s">
-        <v>246</v>
-      </c>
-      <c r="I52" t="s">
-        <v>226</v>
       </c>
       <c r="J52" t="s">
         <v>144</v>
       </c>
       <c r="K52" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L52" t="s">
         <v>29</v>
@@ -3984,10 +4005,10 @@
         <v>30</v>
       </c>
       <c r="N52" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="O52" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
@@ -3996,42 +4017,42 @@
         <v>0</v>
       </c>
       <c r="R52" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B53" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C53" t="s">
+        <v>239</v>
+      </c>
+      <c r="D53" t="s">
+        <v>240</v>
+      </c>
+      <c r="E53" t="s">
+        <v>241</v>
+      </c>
+      <c r="F53" t="s">
         <v>232</v>
       </c>
-      <c r="D53" t="s">
+      <c r="G53" t="s">
+        <v>252</v>
+      </c>
+      <c r="H53" t="s">
+        <v>253</v>
+      </c>
+      <c r="I53" t="s">
         <v>233</v>
-      </c>
-      <c r="E53" t="s">
-        <v>234</v>
-      </c>
-      <c r="F53" t="s">
-        <v>225</v>
-      </c>
-      <c r="G53" t="s">
-        <v>247</v>
-      </c>
-      <c r="H53" t="s">
-        <v>248</v>
-      </c>
-      <c r="I53" t="s">
-        <v>226</v>
       </c>
       <c r="J53" t="s">
         <v>144</v>
       </c>
       <c r="K53" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="L53" t="s">
         <v>29</v>
@@ -4040,19 +4061,75 @@
         <v>30</v>
       </c>
       <c r="N53" t="s">
+        <v>235</v>
+      </c>
+      <c r="O53" t="s">
+        <v>235</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>227</v>
+      </c>
+      <c r="B54" t="s">
         <v>228</v>
       </c>
-      <c r="O53" t="s">
-        <v>228</v>
-      </c>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="s">
-        <v>229</v>
+      <c r="C54" t="s">
+        <v>239</v>
+      </c>
+      <c r="D54" t="s">
+        <v>240</v>
+      </c>
+      <c r="E54" t="s">
+        <v>241</v>
+      </c>
+      <c r="F54" t="s">
+        <v>232</v>
+      </c>
+      <c r="G54" t="s">
+        <v>254</v>
+      </c>
+      <c r="H54" t="s">
+        <v>255</v>
+      </c>
+      <c r="I54" t="s">
+        <v>233</v>
+      </c>
+      <c r="J54" t="s">
+        <v>144</v>
+      </c>
+      <c r="K54" t="s">
+        <v>234</v>
+      </c>
+      <c r="L54" t="s">
+        <v>29</v>
+      </c>
+      <c r="M54" t="s">
+        <v>30</v>
+      </c>
+      <c r="N54" t="s">
+        <v>235</v>
+      </c>
+      <c r="O54" t="s">
+        <v>235</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
